--- a/www/terminologies/CodeSystem-tre-r347-activite-sanitaire-diverse-regulee.xlsx
+++ b/www/terminologies/CodeSystem-tre-r347-activite-sanitaire-diverse-regulee.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1449" uniqueCount="950">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1516" uniqueCount="997">
   <si>
     <t>Property</t>
   </si>
@@ -37,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260505120000</t>
+    <t>20260629120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -67,7 +67,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-05T12:00:00+01:00</t>
+    <t>2026-06-29T12:00:00.000+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -124,1860 +124,1965 @@
     <t>Count</t>
   </si>
   <si>
+    <t>478</t>
+  </si>
+  <si>
+    <t>Code</t>
+  </si>
+  <si>
+    <t>Uri</t>
+  </si>
+  <si>
+    <t>Type</t>
+  </si>
+  <si>
+    <t>parent</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/concept-properties#parent</t>
+  </si>
+  <si>
+    <t>An immediate parent of the concept in the hierarchy</t>
+  </si>
+  <si>
+    <t>code</t>
+  </si>
+  <si>
+    <t>dateValid</t>
+  </si>
+  <si>
+    <t>https://smt.esante.gouv.fr/fhir/concept-properties#dateValid</t>
+  </si>
+  <si>
+    <t>date de validité d'un code concept</t>
+  </si>
+  <si>
+    <t>dateTime</t>
+  </si>
+  <si>
+    <t>dateMaj</t>
+  </si>
+  <si>
+    <t>https://smt.esante.gouv.fr/fhir/concept-properties#dateMaj</t>
+  </si>
+  <si>
+    <t>Date de mise à jour d'un code concept</t>
+  </si>
+  <si>
+    <t>dateFin</t>
+  </si>
+  <si>
+    <t>https://smt.esante.gouv.fr/fhir/concept-properties#dateFin</t>
+  </si>
+  <si>
+    <t>Date de fin d'exploitation d'un code concept</t>
+  </si>
+  <si>
+    <t>status</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/concept-properties#status</t>
+  </si>
+  <si>
+    <t>A code that indicates the status of the concept. Typical values are active, experimental, deprecated, and retired</t>
+  </si>
+  <si>
+    <t>deprecationDate</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/concept-properties#deprecationDate</t>
+  </si>
+  <si>
+    <t>The date at which a concept was deprecated. Concepts that are deprecated but not inactive can still be used, but their use is discouraged, and they should be expected to be made inactive in a future release. Property type is dateTime. Note that the status property may also be used to indicate that a concept is deprecated</t>
+  </si>
+  <si>
+    <t>retirementDate</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/concept-properties#retirementDate</t>
+  </si>
+  <si>
+    <t>The date at which a concept was retired</t>
+  </si>
+  <si>
+    <t>niveau</t>
+  </si>
+  <si>
+    <t>https://smt.esante.gouv.fr/fhir/concept-properties#niveau</t>
+  </si>
+  <si>
+    <t>Permet d'indiquer le niveau hiérarchique du code</t>
+  </si>
+  <si>
+    <t>integer</t>
+  </si>
+  <si>
+    <t>Level</t>
+  </si>
+  <si>
+    <t>Display</t>
+  </si>
+  <si>
+    <t>Definition</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>0200</t>
+  </si>
+  <si>
+    <t>Hospitalisation</t>
+  </si>
+  <si>
+    <t>0300</t>
+  </si>
+  <si>
+    <t>Disciplines Spécifiques</t>
+  </si>
+  <si>
+    <t>0400</t>
+  </si>
+  <si>
+    <t>Disciplines Médico-Techniques</t>
+  </si>
+  <si>
+    <t>0500</t>
+  </si>
+  <si>
+    <t>Accueil et Réception des Urgences</t>
+  </si>
+  <si>
+    <t>0600</t>
+  </si>
+  <si>
+    <t>Autres Disciplines Sanitaires</t>
+  </si>
+  <si>
+    <t>0800</t>
+  </si>
+  <si>
+    <t>Lutte contre les Toxicomanies</t>
+  </si>
+  <si>
+    <t>0210</t>
+  </si>
+  <si>
+    <t>Médecine</t>
+  </si>
+  <si>
+    <t>0220</t>
+  </si>
+  <si>
+    <t>Chirurgie</t>
+  </si>
+  <si>
+    <t>0230</t>
+  </si>
+  <si>
+    <t>Gynécologie Obstétrique</t>
+  </si>
+  <si>
+    <t>0240</t>
+  </si>
+  <si>
+    <t>Neuro-chirurgie</t>
+  </si>
+  <si>
+    <t>0260</t>
+  </si>
+  <si>
+    <t>Soins de Suite et de Réadaptation</t>
+  </si>
+  <si>
+    <t>0270</t>
+  </si>
+  <si>
+    <t>Soins de Longue Durée</t>
+  </si>
+  <si>
+    <t>0280</t>
+  </si>
+  <si>
+    <t>Psychiatrie Adulte</t>
+  </si>
+  <si>
+    <t>0290</t>
+  </si>
+  <si>
+    <t>Psychiatrie Infanto-juvénile</t>
+  </si>
+  <si>
+    <t>0310</t>
+  </si>
+  <si>
+    <t>Dialyse</t>
+  </si>
+  <si>
+    <t>0320</t>
+  </si>
+  <si>
+    <t>Chimiothérapie</t>
+  </si>
+  <si>
+    <t>0330</t>
+  </si>
+  <si>
+    <t>Hospitalisation de Jour en Gynéco-Obstétrique</t>
+  </si>
+  <si>
+    <t>0340</t>
+  </si>
+  <si>
+    <t>Prévention, Prophylaxie, Conseil</t>
+  </si>
+  <si>
+    <t>0350</t>
+  </si>
+  <si>
+    <t>Aide aux Insuffisants Respiratoires</t>
+  </si>
+  <si>
+    <t>0360</t>
+  </si>
+  <si>
+    <t>Autres Traitements Spécialisés à Domicile</t>
+  </si>
+  <si>
+    <t>0370</t>
+  </si>
+  <si>
+    <t>structures de psychiatrie hors carte sanitaire</t>
+  </si>
+  <si>
+    <t>0380</t>
+  </si>
+  <si>
+    <t>disciplines de cures thermales</t>
+  </si>
+  <si>
+    <t>0410</t>
+  </si>
+  <si>
+    <t>Blocs Opératoires et Obstétricaux</t>
+  </si>
+  <si>
+    <t>0420</t>
+  </si>
+  <si>
+    <t>Anesthésiologie et Réveil</t>
+  </si>
+  <si>
+    <t>0430</t>
+  </si>
+  <si>
+    <t>Imagerie</t>
+  </si>
+  <si>
+    <t>0440</t>
+  </si>
+  <si>
+    <t>Radiothérapie</t>
+  </si>
+  <si>
+    <t>0450</t>
+  </si>
+  <si>
+    <t>Exploration Fonctionnelle</t>
+  </si>
+  <si>
+    <t>0460</t>
+  </si>
+  <si>
+    <t>Techniques de Rééducation et de Réadaptation Fonctionnelle</t>
+  </si>
+  <si>
+    <t>0470</t>
+  </si>
+  <si>
+    <t>Analyses Médicales Biologiques</t>
+  </si>
+  <si>
+    <t>0480</t>
+  </si>
+  <si>
+    <t>Pharmacie et autres Biens Médicaux</t>
+  </si>
+  <si>
+    <t>0510</t>
+  </si>
+  <si>
+    <t>Urgence</t>
+  </si>
+  <si>
+    <t>0520</t>
+  </si>
+  <si>
+    <t>Urgence Chirurgicale</t>
+  </si>
+  <si>
+    <t>0530</t>
+  </si>
+  <si>
+    <t>SAMU - SMUR</t>
+  </si>
+  <si>
+    <t>0610</t>
+  </si>
+  <si>
+    <t>Services Extérieurs</t>
+  </si>
+  <si>
+    <t>0620</t>
+  </si>
+  <si>
+    <t>Transport des Malades</t>
+  </si>
+  <si>
+    <t>0630</t>
+  </si>
+  <si>
+    <t>Stockage d'Organes et de Produits Humains</t>
+  </si>
+  <si>
+    <t>0640</t>
+  </si>
+  <si>
+    <t>Enseignement et Recherche</t>
+  </si>
+  <si>
+    <t>0660</t>
+  </si>
+  <si>
+    <t>Autres Disciplines</t>
+  </si>
+  <si>
+    <t>0810</t>
+  </si>
+  <si>
+    <t>0820</t>
+  </si>
+  <si>
+    <t>Lutte contre l'Alcoolisme</t>
+  </si>
+  <si>
+    <t>0211</t>
+  </si>
+  <si>
+    <t>Médecine Générale</t>
+  </si>
+  <si>
+    <t>0212</t>
+  </si>
+  <si>
+    <t>Pédiatrie</t>
+  </si>
+  <si>
+    <t>0213</t>
+  </si>
+  <si>
+    <t>Spécialités Médicales</t>
+  </si>
+  <si>
+    <t>0214</t>
+  </si>
+  <si>
+    <t>Réanimation Médicale</t>
+  </si>
+  <si>
+    <t>0215</t>
+  </si>
+  <si>
+    <t>Surveillance Continue Médicale</t>
+  </si>
+  <si>
+    <t>0221</t>
+  </si>
+  <si>
+    <t>Chirurgie Générale</t>
+  </si>
+  <si>
+    <t>0222</t>
+  </si>
+  <si>
+    <t>Chirurgie Infantile</t>
+  </si>
+  <si>
+    <t>0223</t>
+  </si>
+  <si>
+    <t>Spécialités Chirurgicales</t>
+  </si>
+  <si>
+    <t>0224</t>
+  </si>
+  <si>
+    <t>Réanimation Chirurgicale</t>
+  </si>
+  <si>
+    <t>0225</t>
+  </si>
+  <si>
+    <t>Surveillance Continue Chirurgicale</t>
+  </si>
+  <si>
+    <t>0231</t>
+  </si>
+  <si>
+    <t>0241</t>
+  </si>
+  <si>
+    <t>0261</t>
+  </si>
+  <si>
+    <t>Maladie à Evolution Prolongée</t>
+  </si>
+  <si>
+    <t>0262</t>
+  </si>
+  <si>
+    <t>Convalescence, Repos, Régime</t>
+  </si>
+  <si>
+    <t>0263</t>
+  </si>
+  <si>
+    <t>Rééducation Fonctionnelle et Réadaptation</t>
+  </si>
+  <si>
+    <t>0264</t>
+  </si>
+  <si>
+    <t>Lutte contre la Tuberculose et les Maladies Respiratoires</t>
+  </si>
+  <si>
+    <t>0265</t>
+  </si>
+  <si>
+    <t>Cures Thermales</t>
+  </si>
+  <si>
+    <t>0266</t>
+  </si>
+  <si>
+    <t>Cures Médicales</t>
+  </si>
+  <si>
+    <t>0267</t>
+  </si>
+  <si>
+    <t>Cures Médicales pour Enfants</t>
+  </si>
+  <si>
+    <t>0268</t>
+  </si>
+  <si>
+    <t>Post-Cure pour Alcooliques</t>
+  </si>
+  <si>
+    <t>0271</t>
+  </si>
+  <si>
+    <t>0281</t>
+  </si>
+  <si>
+    <t>0291</t>
+  </si>
+  <si>
+    <t>0311</t>
+  </si>
+  <si>
+    <t>0321</t>
+  </si>
+  <si>
+    <t>0331</t>
+  </si>
+  <si>
+    <t>0341</t>
+  </si>
+  <si>
+    <t>Examens Systématique et Dépistage</t>
+  </si>
+  <si>
+    <t>0342</t>
+  </si>
+  <si>
+    <t>Prévention et Conseil</t>
+  </si>
+  <si>
+    <t>0343</t>
+  </si>
+  <si>
+    <t>Soins Divers</t>
+  </si>
+  <si>
+    <t>0351</t>
+  </si>
+  <si>
+    <t>0361</t>
+  </si>
+  <si>
+    <t>0371</t>
+  </si>
+  <si>
+    <t>structures de psychiatrie ambulatoire</t>
+  </si>
+  <si>
+    <t>0372</t>
+  </si>
+  <si>
+    <t>psychiatrie en milieu pénitentiaire</t>
+  </si>
+  <si>
+    <t>0381</t>
+  </si>
+  <si>
+    <t>0411</t>
+  </si>
+  <si>
+    <t>0421</t>
+  </si>
+  <si>
+    <t>0431</t>
+  </si>
+  <si>
+    <t>0441</t>
+  </si>
+  <si>
+    <t>0451</t>
+  </si>
+  <si>
+    <t>0461</t>
+  </si>
+  <si>
+    <t>0471</t>
+  </si>
+  <si>
+    <t>0481</t>
+  </si>
+  <si>
+    <t>Pharmacie et autres biens médicaux</t>
+  </si>
+  <si>
+    <t>0511</t>
+  </si>
+  <si>
+    <t>0521</t>
+  </si>
+  <si>
+    <t>0531</t>
+  </si>
+  <si>
+    <t>0621</t>
+  </si>
+  <si>
+    <t>0631</t>
+  </si>
+  <si>
+    <t>0641</t>
+  </si>
+  <si>
+    <t>Enseignement</t>
+  </si>
+  <si>
+    <t>0642</t>
+  </si>
+  <si>
+    <t>Recherche</t>
+  </si>
+  <si>
+    <t>0661</t>
+  </si>
+  <si>
+    <t>0811</t>
+  </si>
+  <si>
+    <t>0821</t>
+  </si>
+  <si>
+    <t>861</t>
+  </si>
+  <si>
+    <t>Accueil familial thérapeutique</t>
+  </si>
+  <si>
+    <t>862</t>
+  </si>
+  <si>
+    <t>Appartement thérapeutique</t>
+  </si>
+  <si>
+    <t>863</t>
+  </si>
+  <si>
+    <t>Accueil permanent</t>
+  </si>
+  <si>
+    <t>864</t>
+  </si>
+  <si>
+    <t>Centre d'activités thérapeutiques et de temps de groupe</t>
+  </si>
+  <si>
+    <t>865</t>
+  </si>
+  <si>
+    <t>Centre de crise</t>
+  </si>
+  <si>
+    <t>866</t>
+  </si>
+  <si>
+    <t>Centre de soins post-aigus</t>
+  </si>
+  <si>
+    <t>867</t>
+  </si>
+  <si>
+    <t>Centre médico-psychologique</t>
+  </si>
+  <si>
+    <t>868</t>
+  </si>
+  <si>
+    <t>Hôpital de jour</t>
+  </si>
+  <si>
+    <t>869</t>
+  </si>
+  <si>
+    <t>Service médico-psychologique régional</t>
+  </si>
+  <si>
+    <t>870</t>
+  </si>
+  <si>
+    <t>Soins à domicile</t>
+  </si>
+  <si>
+    <t>871</t>
+  </si>
+  <si>
+    <t>Unité hospitalière spécialement aménagée</t>
+  </si>
+  <si>
+    <t>872</t>
+  </si>
+  <si>
+    <t>Unité pour malades difficiles</t>
+  </si>
+  <si>
+    <t>873</t>
+  </si>
+  <si>
+    <t>Unité sanitaire en milieu pénitentiaire</t>
+  </si>
+  <si>
+    <t>874</t>
+  </si>
+  <si>
+    <t>Hôpital de nuit</t>
+  </si>
+  <si>
+    <t>875</t>
+  </si>
+  <si>
+    <t>Centre de consultations</t>
+  </si>
+  <si>
+    <t>876</t>
+  </si>
+  <si>
+    <t>Unité d’hospitalisation complète</t>
+  </si>
+  <si>
+    <t>877</t>
+  </si>
+  <si>
+    <t>Centre d'accueil et de crise</t>
+  </si>
+  <si>
+    <t>023</t>
+  </si>
+  <si>
+    <t>Stérilisation</t>
+  </si>
+  <si>
+    <t>034</t>
+  </si>
+  <si>
+    <t>Radiostandard</t>
+  </si>
+  <si>
+    <t>035</t>
+  </si>
+  <si>
+    <t>Scanographie X</t>
+  </si>
+  <si>
+    <t>036</t>
+  </si>
+  <si>
+    <t>Neuroradiologie</t>
+  </si>
+  <si>
+    <t>037</t>
+  </si>
+  <si>
+    <t>Hémodynamique</t>
+  </si>
+  <si>
+    <t>038</t>
+  </si>
+  <si>
+    <t>Radiothérapie de Contact</t>
+  </si>
+  <si>
+    <t>039</t>
+  </si>
+  <si>
+    <t>Radiothérapie Externe(Césium Cobalt)</t>
+  </si>
+  <si>
+    <t>041</t>
+  </si>
+  <si>
+    <t>Radiothérapie Haute Énergie</t>
+  </si>
+  <si>
+    <t>043</t>
+  </si>
+  <si>
+    <t>Curiethérapie</t>
+  </si>
+  <si>
+    <t>044</t>
+  </si>
+  <si>
+    <t>Autre Radiothérapie Spécialisée</t>
+  </si>
+  <si>
+    <t>045</t>
+  </si>
+  <si>
+    <t>Exploration Fonctionnelle Cardiovasculaire</t>
+  </si>
+  <si>
+    <t>046</t>
+  </si>
+  <si>
+    <t>Exploration Fonctionnelle Néphrologique</t>
+  </si>
+  <si>
+    <t>047</t>
+  </si>
+  <si>
+    <t>Exploration Fonctionnelle Pneumologique</t>
+  </si>
+  <si>
+    <t>048</t>
+  </si>
+  <si>
+    <t>Exploration Fonctionnelle Neurologique</t>
+  </si>
+  <si>
+    <t>049</t>
+  </si>
+  <si>
+    <t>Exploration Fonctionnelle Tube Digestif</t>
+  </si>
+  <si>
+    <t>050</t>
+  </si>
+  <si>
+    <t>Exploration Fonctionnelle Fonctionnelle Spécialisée</t>
+  </si>
+  <si>
+    <t>051</t>
+  </si>
+  <si>
+    <t>Exploration Fonctionnelle Cardiovasculaire Néphrologique</t>
+  </si>
+  <si>
+    <t>052</t>
+  </si>
+  <si>
+    <t>Exploration Fonctionnelle Cardiovasculaire Pneumologique.</t>
+  </si>
+  <si>
+    <t>053</t>
+  </si>
+  <si>
+    <t>Exploration Fonctionnelle Fonctionnelle Polyvalente</t>
+  </si>
+  <si>
+    <t>055</t>
+  </si>
+  <si>
+    <t>Réadaption-Rééducation Fonctionnelle Polyvalente</t>
+  </si>
+  <si>
+    <t>056</t>
+  </si>
+  <si>
+    <t>Ergothérapie</t>
+  </si>
+  <si>
+    <t>057</t>
+  </si>
+  <si>
+    <t>Hydrothérapie</t>
+  </si>
+  <si>
+    <t>058</t>
+  </si>
+  <si>
+    <t>Kinésithérapie</t>
+  </si>
+  <si>
+    <t>059</t>
+  </si>
+  <si>
+    <t>Orthophonie</t>
+  </si>
+  <si>
+    <t>060</t>
+  </si>
+  <si>
+    <t>Orthoptie</t>
+  </si>
+  <si>
+    <t>061</t>
+  </si>
+  <si>
+    <t>Autre Rééducation Spécialisée</t>
+  </si>
+  <si>
+    <t>062</t>
+  </si>
+  <si>
+    <t>Anatomie Cytologie Pathologiques</t>
+  </si>
+  <si>
+    <t>063</t>
+  </si>
+  <si>
+    <t>Bactériologie</t>
+  </si>
+  <si>
+    <t>064</t>
+  </si>
+  <si>
+    <t>Biochimie</t>
+  </si>
+  <si>
+    <t>065</t>
+  </si>
+  <si>
+    <t>Biophysique</t>
+  </si>
+  <si>
+    <t>067</t>
+  </si>
+  <si>
+    <t>Coprologie</t>
+  </si>
+  <si>
+    <t>068</t>
+  </si>
+  <si>
+    <t>Cytologie</t>
+  </si>
+  <si>
+    <t>069</t>
+  </si>
+  <si>
+    <t>Cytogénétique</t>
+  </si>
+  <si>
+    <t>070</t>
+  </si>
+  <si>
+    <t>Embryologie</t>
+  </si>
+  <si>
+    <t>071</t>
+  </si>
+  <si>
+    <t>Enzymologie</t>
+  </si>
+  <si>
+    <t>072</t>
+  </si>
+  <si>
+    <t>Hématologie</t>
+  </si>
+  <si>
+    <t>073</t>
+  </si>
+  <si>
+    <t>Histologie</t>
+  </si>
+  <si>
+    <t>074</t>
+  </si>
+  <si>
+    <t>Hormonologie</t>
+  </si>
+  <si>
+    <t>076</t>
+  </si>
+  <si>
+    <t>Immunologie</t>
+  </si>
+  <si>
+    <t>077</t>
+  </si>
+  <si>
+    <t>Bactériologie-Vitro Parasitologie</t>
+  </si>
+  <si>
+    <t>078</t>
+  </si>
+  <si>
+    <t>Mycologie</t>
+  </si>
+  <si>
+    <t>079</t>
+  </si>
+  <si>
+    <t>Parasitologie</t>
+  </si>
+  <si>
+    <t>080</t>
+  </si>
+  <si>
+    <t>Pharmacologie</t>
+  </si>
+  <si>
+    <t>081</t>
+  </si>
+  <si>
+    <t>Sérologie</t>
+  </si>
+  <si>
+    <t>082</t>
+  </si>
+  <si>
+    <t>Toxicologie</t>
+  </si>
+  <si>
+    <t>083</t>
+  </si>
+  <si>
+    <t>Virologie</t>
+  </si>
+  <si>
+    <t>084</t>
+  </si>
+  <si>
+    <t>Biologie Médicale</t>
+  </si>
+  <si>
+    <t>085</t>
+  </si>
+  <si>
+    <t>Autre discipline de biologie médicale spécialisée</t>
+  </si>
+  <si>
+    <t>086</t>
+  </si>
+  <si>
+    <t>Activité de vaccination gratuite</t>
+  </si>
+  <si>
+    <t>087</t>
+  </si>
+  <si>
+    <t>Consultation Anti-Tabac</t>
+  </si>
+  <si>
+    <t>088</t>
+  </si>
+  <si>
+    <t>Médecine Légale</t>
+  </si>
+  <si>
+    <t>089</t>
+  </si>
+  <si>
+    <t>Médecine Préventive Santé Publique</t>
+  </si>
+  <si>
+    <t>090</t>
+  </si>
+  <si>
+    <t>Autres Consultations Soins Externes</t>
+  </si>
+  <si>
+    <t>091</t>
+  </si>
+  <si>
+    <t>Fabrication Préparation Produits Pharmaceutiques</t>
+  </si>
+  <si>
+    <t>092</t>
+  </si>
+  <si>
+    <t>Distribution de Produits Pharmaceutiques</t>
+  </si>
+  <si>
+    <t>093</t>
+  </si>
+  <si>
+    <t>Distribution autres Biens Médicaux</t>
+  </si>
+  <si>
+    <t>094</t>
+  </si>
+  <si>
+    <t>Pharmacocinétique</t>
+  </si>
+  <si>
+    <t>095</t>
+  </si>
+  <si>
+    <t>Fabrication Autres Biens Médicaux Prothèses</t>
+  </si>
+  <si>
+    <t>096</t>
+  </si>
+  <si>
+    <t>Prélèvement Scientifique Vérification Diagnostic</t>
+  </si>
+  <si>
+    <t>097</t>
+  </si>
+  <si>
+    <t>Anesthésiologie</t>
+  </si>
+  <si>
+    <t>098</t>
+  </si>
+  <si>
+    <t>Parasitologie et Mycologie</t>
+  </si>
+  <si>
+    <t>099</t>
+  </si>
+  <si>
+    <t>Activité Pharmaco-Toxico-Vigilance</t>
+  </si>
+  <si>
+    <t>100</t>
+  </si>
+  <si>
+    <t>Radio-Immunologie</t>
+  </si>
+  <si>
+    <t>101</t>
+  </si>
+  <si>
+    <t>Médecine Générale ou Médecine Interne</t>
+  </si>
+  <si>
+    <t>102</t>
+  </si>
+  <si>
+    <t>Maladie Infectieuse et Parasitaire</t>
+  </si>
+  <si>
+    <t>103</t>
+  </si>
+  <si>
+    <t>Centre AntiPoison</t>
+  </si>
+  <si>
+    <t>104</t>
+  </si>
+  <si>
+    <t>Réanimation Médicale Adultes</t>
+  </si>
+  <si>
+    <t>105</t>
+  </si>
+  <si>
+    <t>Réanimation Polyvalente</t>
+  </si>
+  <si>
+    <t>106</t>
+  </si>
+  <si>
+    <t>107</t>
+  </si>
+  <si>
+    <t>SURVEILLANCE CONTINUE POLYV.</t>
+  </si>
+  <si>
+    <t>108</t>
+  </si>
+  <si>
+    <t>109</t>
+  </si>
+  <si>
+    <t>Médecine de l'Adolescent</t>
+  </si>
+  <si>
+    <t>111</t>
+  </si>
+  <si>
+    <t>PEDIATRIE NOURRISSONS</t>
+  </si>
+  <si>
+    <t>112</t>
+  </si>
+  <si>
+    <t>Néonatalogie</t>
+  </si>
+  <si>
+    <t>113</t>
+  </si>
+  <si>
+    <t>Médecine Gériatrique</t>
+  </si>
+  <si>
+    <t>115</t>
+  </si>
+  <si>
+    <t>ALLERGOLOGIE</t>
+  </si>
+  <si>
+    <t>117</t>
+  </si>
+  <si>
+    <t>Dermatologie-Vénérologie</t>
+  </si>
+  <si>
+    <t>119</t>
+  </si>
+  <si>
+    <t>Endocrino-Diabetologie</t>
+  </si>
+  <si>
+    <t>122</t>
+  </si>
+  <si>
+    <t>Maladies Métaboliques Nutrition</t>
+  </si>
+  <si>
+    <t>123</t>
+  </si>
+  <si>
+    <t>Hématologie Maladies du Sang</t>
+  </si>
+  <si>
+    <t>124</t>
+  </si>
+  <si>
+    <t>Hépato-Gastro-Entérologie</t>
+  </si>
+  <si>
+    <t>126</t>
+  </si>
+  <si>
+    <t>MEDECINE CARCINOLOGIQUE</t>
+  </si>
+  <si>
+    <t>127</t>
+  </si>
+  <si>
+    <t>Médecine Cardio-Vasculaire</t>
+  </si>
+  <si>
+    <t>129</t>
+  </si>
+  <si>
+    <t>Neurologie</t>
+  </si>
+  <si>
+    <t>130</t>
+  </si>
+  <si>
+    <t>Pneumologie</t>
+  </si>
+  <si>
+    <t>133</t>
+  </si>
+  <si>
+    <t>Rhumatologie</t>
+  </si>
+  <si>
+    <t>134</t>
+  </si>
+  <si>
+    <t>RADIOTHER. &amp; MEDEC. NUCLEAIRE</t>
+  </si>
+  <si>
+    <t>135</t>
+  </si>
+  <si>
+    <t>RADIOTHERAPIE</t>
+  </si>
+  <si>
+    <t>136</t>
+  </si>
+  <si>
+    <t>Médecine Nucléaire</t>
+  </si>
+  <si>
+    <t>137</t>
+  </si>
+  <si>
+    <t>138</t>
+  </si>
+  <si>
+    <t>141</t>
+  </si>
+  <si>
+    <t>Réanimation Chirurgicale Adultes</t>
+  </si>
+  <si>
+    <t>142</t>
+  </si>
+  <si>
+    <t>143</t>
+  </si>
+  <si>
+    <t>SPECIALITE CHIRURGICALE</t>
+  </si>
+  <si>
+    <t>144</t>
+  </si>
+  <si>
+    <t>Chirurgie Carcinologie</t>
+  </si>
+  <si>
+    <t>145</t>
+  </si>
+  <si>
+    <t>Traitement des Grands Brûlés</t>
+  </si>
+  <si>
+    <t>146</t>
+  </si>
+  <si>
+    <t>Chirurgie Digestive</t>
+  </si>
+  <si>
+    <t>147</t>
+  </si>
+  <si>
+    <t>Chirurgie Thoracique Cardio-Vasculaire</t>
+  </si>
+  <si>
+    <t>148</t>
+  </si>
+  <si>
+    <t>CHIRURGIE THORACO-PULMONAIRE</t>
+  </si>
+  <si>
+    <t>149</t>
+  </si>
+  <si>
+    <t>Chirurgie Vasculaire</t>
+  </si>
+  <si>
+    <t>150</t>
+  </si>
+  <si>
+    <t>CHIRURGIE CARDIO-VASCULAIRE</t>
+  </si>
+  <si>
+    <t>151</t>
+  </si>
+  <si>
+    <t>Neurochirurgie</t>
+  </si>
+  <si>
+    <t>152</t>
+  </si>
+  <si>
+    <t>Orthopédie-Traumatologie</t>
+  </si>
+  <si>
+    <t>153</t>
+  </si>
+  <si>
+    <t>Actes d'explantation de prothèses PIP</t>
+  </si>
+  <si>
+    <t>154</t>
+  </si>
+  <si>
+    <t>Chirurgie Plastique Reconstructive</t>
+  </si>
+  <si>
+    <t>155</t>
+  </si>
+  <si>
+    <t>ORL ET OPHTALMOLOGIE</t>
+  </si>
+  <si>
+    <t>156</t>
+  </si>
+  <si>
+    <t>Oto-rhino-laryngologie</t>
+  </si>
+  <si>
+    <t>157</t>
+  </si>
+  <si>
+    <t>Ophtalmologie</t>
+  </si>
+  <si>
+    <t>158</t>
+  </si>
+  <si>
+    <t>Stomatologie Chirurgie Maxillo-faciale</t>
+  </si>
+  <si>
+    <t>159</t>
+  </si>
+  <si>
+    <t>Stomatologie</t>
+  </si>
+  <si>
+    <t>161</t>
+  </si>
+  <si>
+    <t>Urologie</t>
+  </si>
+  <si>
+    <t>162</t>
+  </si>
+  <si>
+    <t>ORL-OPHTALMOLOG.&amp; STOMATOLOGIE</t>
+  </si>
+  <si>
+    <t>163</t>
+  </si>
+  <si>
+    <t>Gynéco.&amp; Obstétrique</t>
+  </si>
+  <si>
+    <t>164</t>
+  </si>
+  <si>
+    <t>Gynécologie Médicale</t>
+  </si>
+  <si>
+    <t>165</t>
+  </si>
+  <si>
+    <t>166</t>
+  </si>
+  <si>
+    <t>Chroniques Convalescence Indifférencié</t>
+  </si>
+  <si>
+    <t>167</t>
+  </si>
+  <si>
+    <t>Chroniques</t>
+  </si>
+  <si>
+    <t>168</t>
+  </si>
+  <si>
+    <t>Repos-Convalescence Régime Indifférencié</t>
+  </si>
+  <si>
+    <t>169</t>
+  </si>
+  <si>
+    <t>Repos</t>
+  </si>
+  <si>
+    <t>170</t>
+  </si>
+  <si>
+    <t>Convalescence</t>
+  </si>
+  <si>
+    <t>171</t>
+  </si>
+  <si>
+    <t>Régime</t>
+  </si>
+  <si>
+    <t>172</t>
+  </si>
+  <si>
+    <t>Rééducation Fonctionnelle Réadaptation Polyvalente</t>
+  </si>
+  <si>
+    <t>173</t>
+  </si>
+  <si>
+    <t>Cure Thermale</t>
+  </si>
+  <si>
+    <t>174</t>
+  </si>
+  <si>
+    <t>MEDEC.GEN. &amp; SPECIALITE MEDIC.</t>
+  </si>
+  <si>
+    <t>176</t>
+  </si>
+  <si>
+    <t>Long Séjour Personnes Ayant Perdu Leur Autonomie de Vie</t>
+  </si>
+  <si>
+    <t>178</t>
+  </si>
+  <si>
+    <t>Rééducation Fonctionnelle Réadaptation Motrice</t>
+  </si>
+  <si>
+    <t>179</t>
+  </si>
+  <si>
+    <t>Rééducation Fonctionnelle Réadaptation Neurologique</t>
+  </si>
+  <si>
+    <t>180</t>
+  </si>
+  <si>
+    <t>Rééducation des Affections Respiratoires</t>
+  </si>
+  <si>
+    <t>181</t>
+  </si>
+  <si>
+    <t>Chirurgie Générale Spécialités Chirurgicales</t>
+  </si>
+  <si>
+    <t>182</t>
+  </si>
+  <si>
+    <t>Rééducat. Maladies Cardio-Vasculaires</t>
+  </si>
+  <si>
+    <t>183</t>
+  </si>
+  <si>
+    <t>OBSTETRIQUE SANS CHIRURGIE</t>
+  </si>
+  <si>
+    <t>184</t>
+  </si>
+  <si>
+    <t>Rééducation des Affections Hépato-Digestives</t>
+  </si>
+  <si>
+    <t>185</t>
+  </si>
+  <si>
+    <t>Repos-Convalescence Indifférenciés</t>
+  </si>
+  <si>
+    <t>186</t>
+  </si>
+  <si>
+    <t>REEDUCATION PERSONNE AGEE</t>
+  </si>
+  <si>
+    <t>187</t>
+  </si>
+  <si>
+    <t>Rééducation Fonctionnelle Réadaptation</t>
+  </si>
+  <si>
+    <t>189</t>
+  </si>
+  <si>
+    <t>Cure Thermale des Voies Respiratoires</t>
+  </si>
+  <si>
+    <t>191</t>
+  </si>
+  <si>
+    <t>CURE THERM.AFFECT.HEPATO-DIGES</t>
+  </si>
+  <si>
+    <t>192</t>
+  </si>
+  <si>
+    <t>CURE THERM.APPAREIL URINAIRE</t>
+  </si>
+  <si>
+    <t>193</t>
+  </si>
+  <si>
+    <t>Cure Thermale Rhumatologie Séquel.Traum.Ostéo-articaires</t>
+  </si>
+  <si>
+    <t>194</t>
+  </si>
+  <si>
+    <t>Cure Thermale en Dermatologie</t>
+  </si>
+  <si>
+    <t>195</t>
+  </si>
+  <si>
+    <t>Soins aux Toxicomanes</t>
+  </si>
+  <si>
+    <t>196</t>
+  </si>
+  <si>
+    <t>Lutte Contre l'Alcoolisme</t>
+  </si>
+  <si>
+    <t>197</t>
+  </si>
+  <si>
+    <t>Activité dentaire unique</t>
+  </si>
+  <si>
+    <t>198</t>
+  </si>
+  <si>
+    <t>Oncologie</t>
+  </si>
+  <si>
+    <t>200</t>
+  </si>
+  <si>
+    <t>Transfusion Sanguine (Laboratoire)</t>
+  </si>
+  <si>
+    <t>201</t>
+  </si>
+  <si>
+    <t>Banque de Sperme</t>
+  </si>
+  <si>
+    <t>202</t>
+  </si>
+  <si>
+    <t>Banque d'Organes</t>
+  </si>
+  <si>
+    <t>203</t>
+  </si>
+  <si>
+    <t>Dispensaire de Soins</t>
+  </si>
+  <si>
+    <t>204</t>
+  </si>
+  <si>
+    <t>Activité infirmière unique</t>
+  </si>
+  <si>
+    <t>205</t>
+  </si>
+  <si>
+    <t>Act inform dépistage diag infections sexuellmnt transmissibl</t>
+  </si>
+  <si>
+    <t>206</t>
+  </si>
+  <si>
+    <t>Lutte Antihansénienne</t>
+  </si>
+  <si>
+    <t>207</t>
+  </si>
+  <si>
+    <t>S.A.M.U Centre 15</t>
+  </si>
+  <si>
+    <t>208</t>
+  </si>
+  <si>
+    <t>S.M.U.R. U.M.H.</t>
+  </si>
+  <si>
+    <t>209</t>
+  </si>
+  <si>
+    <t>Ambulances</t>
+  </si>
+  <si>
+    <t>211</t>
+  </si>
+  <si>
+    <t>Accueil et Traitement des Urgences Médico-Chirurgicales</t>
+  </si>
+  <si>
+    <t>214</t>
+  </si>
+  <si>
+    <t>Postcure pour Alcooliques</t>
+  </si>
+  <si>
+    <t>217</t>
+  </si>
+  <si>
+    <t>Lutte Contre La Tuberculose Indifférenciée</t>
+  </si>
+  <si>
+    <t>218</t>
+  </si>
+  <si>
+    <t>Activité de lutte anti tuberculose</t>
+  </si>
+  <si>
+    <t>219</t>
+  </si>
+  <si>
+    <t>Lutte Ctre la Tuberculose Pulmonaire</t>
+  </si>
+  <si>
+    <t>220</t>
+  </si>
+  <si>
+    <t>Lutte Ctre Tuberculose Extra-Pulmonaire</t>
+  </si>
+  <si>
+    <t>221</t>
+  </si>
+  <si>
+    <t>Cure et Repos en Prévention</t>
+  </si>
+  <si>
+    <t>222</t>
+  </si>
+  <si>
+    <t>Traitements Préventifs de la Tuberculose</t>
+  </si>
+  <si>
+    <t>223</t>
+  </si>
+  <si>
+    <t>Médecine Générale ou Polyvalente</t>
+  </si>
+  <si>
+    <t>224</t>
+  </si>
+  <si>
+    <t>Observation et Traitement Pneumoconioses</t>
+  </si>
+  <si>
+    <t>225</t>
+  </si>
+  <si>
+    <t>Médecine Interne Spécialités Médicales</t>
+  </si>
+  <si>
+    <t>226</t>
+  </si>
+  <si>
+    <t>Accueil Orientation. des Malades.Tuberculo Pulmonaires</t>
+  </si>
+  <si>
+    <t>227</t>
+  </si>
+  <si>
+    <t>Postcure pour Tuberculeux</t>
+  </si>
+  <si>
+    <t>230</t>
+  </si>
+  <si>
+    <t>Psychiatrie Générale</t>
+  </si>
+  <si>
+    <t>231</t>
+  </si>
+  <si>
+    <t>centre médico-psychologique adulte</t>
+  </si>
+  <si>
+    <t>232</t>
+  </si>
+  <si>
+    <t>centre médico-psychologique infanto-juvénile</t>
+  </si>
+  <si>
+    <t>233</t>
+  </si>
+  <si>
+    <t>Centre d'accueil thérapeutique à temps partiel adulte</t>
+  </si>
+  <si>
+    <t>234</t>
+  </si>
+  <si>
+    <t>Centre d'accueil thérapeutique à temps partiel infanto-juv</t>
+  </si>
+  <si>
+    <t>235</t>
+  </si>
+  <si>
+    <t>soins intensifs de néonatologie</t>
+  </si>
+  <si>
+    <t>236</t>
+  </si>
+  <si>
+    <t>Psychiatrie Infanto-Juvenile</t>
+  </si>
+  <si>
+    <t>237</t>
+  </si>
+  <si>
+    <t>centre d'accueil permanent adulte</t>
+  </si>
+  <si>
+    <t>238</t>
+  </si>
+  <si>
+    <t>centre d'accueil permanent infanto-juvénile</t>
+  </si>
+  <si>
+    <t>240</t>
+  </si>
+  <si>
+    <t>POST-CURE POUR TOXICOMANES</t>
+  </si>
+  <si>
+    <t>241</t>
+  </si>
+  <si>
+    <t>Hygiène Alimentaire</t>
+  </si>
+  <si>
+    <t>244</t>
+  </si>
+  <si>
+    <t>hospitalisation psychiatrique à domicile adulte</t>
+  </si>
+  <si>
+    <t>245</t>
+  </si>
+  <si>
+    <t>hospitalisation psychiatrique à domicile infanto-juv</t>
+  </si>
+  <si>
+    <t>252</t>
+  </si>
+  <si>
+    <t>Pouponnière à Caractère Sanitaire</t>
+  </si>
+  <si>
+    <t>263</t>
+  </si>
+  <si>
+    <t>Placement familial sanitaire</t>
+  </si>
+  <si>
+    <t>265</t>
+  </si>
+  <si>
+    <t>COLONIE A CARACTERE SANITAIRE</t>
+  </si>
+  <si>
+    <t>302</t>
+  </si>
+  <si>
+    <t>CHIMIOTHER.EN HEMATOL.&amp; CANCER</t>
+  </si>
+  <si>
+    <t>303</t>
+  </si>
+  <si>
+    <t>Urgence Médicale</t>
+  </si>
+  <si>
+    <t>307</t>
+  </si>
+  <si>
+    <t>Urgence Chirurgicale (SERV.PORTE)</t>
+  </si>
+  <si>
+    <t>308</t>
+  </si>
+  <si>
+    <t>Urgence Indifférenciée</t>
+  </si>
+  <si>
+    <t>309</t>
+  </si>
+  <si>
+    <t>Interruption Volontaire de Grossesse</t>
+  </si>
+  <si>
+    <t>310</t>
+  </si>
+  <si>
+    <t>Examens de Santé et Bilans</t>
+  </si>
+  <si>
+    <t>312</t>
+  </si>
+  <si>
+    <t>Néphrologie</t>
+  </si>
+  <si>
+    <t>362</t>
+  </si>
+  <si>
+    <t>Chirurgie Obstétrique Indifférenciées</t>
+  </si>
+  <si>
+    <t>384</t>
+  </si>
+  <si>
+    <t>Protection Maternelle &amp; Infantile</t>
+  </si>
+  <si>
+    <t>385</t>
+  </si>
+  <si>
+    <t>Consultations Prénuptiale Prénatale et Postnatale</t>
+  </si>
+  <si>
+    <t>386</t>
+  </si>
+  <si>
+    <t>Consultations Protection Infantile</t>
+  </si>
+  <si>
+    <t>387</t>
+  </si>
+  <si>
+    <t>Consultations de Nourrissons</t>
+  </si>
+  <si>
+    <t>388</t>
+  </si>
+  <si>
+    <t>Consultations de deuxième age</t>
+  </si>
+  <si>
+    <t>389</t>
+  </si>
+  <si>
+    <t>Lutte contre la Stérilité</t>
+  </si>
+  <si>
+    <t>390</t>
+  </si>
+  <si>
+    <t>Consultation en Conseil Génétique</t>
+  </si>
+  <si>
+    <t>391</t>
+  </si>
+  <si>
+    <t>Consultation de Planification ou Éducation Familiale</t>
+  </si>
+  <si>
+    <t>392</t>
+  </si>
+  <si>
+    <t>Information Consultation ou Conseil familial</t>
+  </si>
+  <si>
+    <t>394</t>
+  </si>
+  <si>
+    <t>Lactarium</t>
+  </si>
+  <si>
+    <t>395</t>
+  </si>
+  <si>
+    <t>Guidance Parentale</t>
+  </si>
+  <si>
+    <t>396</t>
+  </si>
+  <si>
+    <t>Guidance infantile</t>
+  </si>
+  <si>
+    <t>401</t>
+  </si>
+  <si>
+    <t>unité de proximité accueil traitement orientation urgences</t>
+  </si>
+  <si>
+    <t>402</t>
+  </si>
+  <si>
+    <t>service accueil et traitement urgences</t>
+  </si>
+  <si>
+    <t>403</t>
+  </si>
+  <si>
+    <t>pôle spécialisé urgence en pédiatrie</t>
+  </si>
+  <si>
+    <t>404</t>
+  </si>
+  <si>
+    <t>pôle spécialisé urgence en ophtalmologie</t>
+  </si>
+  <si>
+    <t>405</t>
+  </si>
+  <si>
+    <t>pôle spécialisé urgence en cardiologie</t>
+  </si>
+  <si>
+    <t>406</t>
+  </si>
+  <si>
+    <t>pôle spécialisé urgence en traumatologie</t>
+  </si>
+  <si>
+    <t>407</t>
+  </si>
+  <si>
+    <t>pôle spécialisé urgence en SOS main</t>
+  </si>
+  <si>
+    <t>408</t>
+  </si>
+  <si>
+    <t>pôle spécialisé urgence en neurochirurgie</t>
+  </si>
+  <si>
+    <t>409</t>
+  </si>
+  <si>
+    <t>autre pôle spécialisé urgence non dénommé ailleurs</t>
+  </si>
+  <si>
+    <t>446</t>
+  </si>
+  <si>
+    <t>Médecine Scolaire</t>
+  </si>
+  <si>
+    <t>447</t>
+  </si>
+  <si>
+    <t>Médecine Universitaire</t>
+  </si>
+  <si>
+    <t>448</t>
+  </si>
+  <si>
+    <t>Médecine Sportive</t>
+  </si>
+  <si>
+    <t>452</t>
+  </si>
+  <si>
+    <t>Aide Aux Insuffisants Respiratoires</t>
+  </si>
+  <si>
     <t>457</t>
   </si>
   <si>
-    <t>Code</t>
-  </si>
-  <si>
-    <t>Uri</t>
-  </si>
-  <si>
-    <t>Type</t>
-  </si>
-  <si>
-    <t>parent</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/concept-properties#parent</t>
-  </si>
-  <si>
-    <t>An immediate parent of the concept in the hierarchy</t>
-  </si>
-  <si>
-    <t>code</t>
-  </si>
-  <si>
-    <t>dateValid</t>
-  </si>
-  <si>
-    <t>https://smt.esante.gouv.fr/fhir/concept-properties#dateValid</t>
-  </si>
-  <si>
-    <t>date de validité d'un code concept</t>
-  </si>
-  <si>
-    <t>dateTime</t>
-  </si>
-  <si>
-    <t>dateMaj</t>
-  </si>
-  <si>
-    <t>https://smt.esante.gouv.fr/fhir/concept-properties#dateMaj</t>
-  </si>
-  <si>
-    <t>Date de mise à jour d'un code concept</t>
-  </si>
-  <si>
-    <t>dateFin</t>
-  </si>
-  <si>
-    <t>https://smt.esante.gouv.fr/fhir/concept-properties#dateFin</t>
-  </si>
-  <si>
-    <t>Date de fin d'exploitation d'un code concept</t>
-  </si>
-  <si>
-    <t>status</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/concept-properties#status</t>
-  </si>
-  <si>
-    <t>A code that indicates the status of the concept. Typical values are active, experimental, deprecated, and retired</t>
-  </si>
-  <si>
-    <t>deprecationDate</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/concept-properties#deprecationDate</t>
-  </si>
-  <si>
-    <t>The date at which a concept was deprecated. Concepts that are deprecated but not inactive can still be used, but their use is discouraged, and they should be expected to be made inactive in a future release. Property type is dateTime. Note that the status property may also be used to indicate that a concept is deprecated</t>
-  </si>
-  <si>
-    <t>retirementDate</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/concept-properties#retirementDate</t>
-  </si>
-  <si>
-    <t>The date at which a concept was retired</t>
-  </si>
-  <si>
-    <t>niveau</t>
-  </si>
-  <si>
-    <t>https://smt.esante.gouv.fr/fhir/concept-properties#niveau</t>
-  </si>
-  <si>
-    <t>Permet d'indiquer le niveau hiérarchique du code</t>
-  </si>
-  <si>
-    <t>integer</t>
-  </si>
-  <si>
-    <t>Level</t>
-  </si>
-  <si>
-    <t>Display</t>
-  </si>
-  <si>
-    <t>Definition</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>0200</t>
-  </si>
-  <si>
-    <t>Hospitalisation</t>
-  </si>
-  <si>
-    <t>0300</t>
-  </si>
-  <si>
-    <t>Disciplines Spécifiques</t>
-  </si>
-  <si>
-    <t>0400</t>
-  </si>
-  <si>
-    <t>Disciplines Médico-Techniques</t>
-  </si>
-  <si>
-    <t>0500</t>
-  </si>
-  <si>
-    <t>Accueil et Réception des Urgences</t>
-  </si>
-  <si>
-    <t>0600</t>
-  </si>
-  <si>
-    <t>Autres Disciplines Sanitaires</t>
-  </si>
-  <si>
-    <t>0800</t>
-  </si>
-  <si>
-    <t>Lutte contre les Toxicomanies</t>
-  </si>
-  <si>
-    <t>0210</t>
-  </si>
-  <si>
-    <t>Médecine</t>
-  </si>
-  <si>
-    <t>0220</t>
-  </si>
-  <si>
-    <t>Chirurgie</t>
-  </si>
-  <si>
-    <t>0230</t>
-  </si>
-  <si>
-    <t>Gynécologie Obstétrique</t>
-  </si>
-  <si>
-    <t>0240</t>
-  </si>
-  <si>
-    <t>Neuro-chirurgie</t>
-  </si>
-  <si>
-    <t>0260</t>
-  </si>
-  <si>
-    <t>Soins de Suite et de Réadaptation</t>
-  </si>
-  <si>
-    <t>0270</t>
-  </si>
-  <si>
-    <t>Soins de Longue Durée</t>
-  </si>
-  <si>
-    <t>0280</t>
-  </si>
-  <si>
-    <t>Psychiatrie Adulte</t>
-  </si>
-  <si>
-    <t>0290</t>
-  </si>
-  <si>
-    <t>Psychiatrie Infanto-juvénile</t>
-  </si>
-  <si>
-    <t>0310</t>
-  </si>
-  <si>
-    <t>Dialyse</t>
-  </si>
-  <si>
-    <t>0320</t>
-  </si>
-  <si>
-    <t>Chimiothérapie</t>
-  </si>
-  <si>
-    <t>0330</t>
-  </si>
-  <si>
-    <t>Hospitalisation de Jour en Gynéco-Obstétrique</t>
-  </si>
-  <si>
-    <t>0340</t>
-  </si>
-  <si>
-    <t>Prévention, Prophylaxie, Conseil</t>
-  </si>
-  <si>
-    <t>0350</t>
-  </si>
-  <si>
-    <t>Aide aux Insuffisants Respiratoires</t>
-  </si>
-  <si>
-    <t>0360</t>
-  </si>
-  <si>
-    <t>Autres Traitements Spécialisés à Domicile</t>
-  </si>
-  <si>
-    <t>0370</t>
-  </si>
-  <si>
-    <t>structures de psychiatrie hors carte sanitaire</t>
-  </si>
-  <si>
-    <t>0380</t>
-  </si>
-  <si>
-    <t>disciplines de cures thermales</t>
-  </si>
-  <si>
-    <t>0410</t>
-  </si>
-  <si>
-    <t>Blocs Opératoires et Obstétricaux</t>
-  </si>
-  <si>
-    <t>0420</t>
-  </si>
-  <si>
-    <t>Anesthésiologie et Réveil</t>
-  </si>
-  <si>
-    <t>0430</t>
-  </si>
-  <si>
-    <t>Imagerie</t>
-  </si>
-  <si>
-    <t>0440</t>
-  </si>
-  <si>
-    <t>Radiothérapie</t>
-  </si>
-  <si>
-    <t>0450</t>
-  </si>
-  <si>
-    <t>Exploration Fonctionnelle</t>
-  </si>
-  <si>
-    <t>0460</t>
-  </si>
-  <si>
-    <t>Techniques de Rééducation et de Réadaptation Fonctionnelle</t>
-  </si>
-  <si>
-    <t>0470</t>
-  </si>
-  <si>
-    <t>Analyses Médicales Biologiques</t>
-  </si>
-  <si>
-    <t>0480</t>
-  </si>
-  <si>
-    <t>Pharmacie et autres Biens Médicaux</t>
-  </si>
-  <si>
-    <t>0510</t>
-  </si>
-  <si>
-    <t>Urgence</t>
-  </si>
-  <si>
-    <t>0520</t>
-  </si>
-  <si>
-    <t>Urgence Chirurgicale</t>
-  </si>
-  <si>
-    <t>0530</t>
-  </si>
-  <si>
-    <t>SAMU - SMUR</t>
-  </si>
-  <si>
-    <t>0610</t>
-  </si>
-  <si>
-    <t>Services Extérieurs</t>
-  </si>
-  <si>
-    <t>0620</t>
-  </si>
-  <si>
-    <t>Transport des Malades</t>
-  </si>
-  <si>
-    <t>0630</t>
-  </si>
-  <si>
-    <t>Stockage d'Organes et de Produits Humains</t>
-  </si>
-  <si>
-    <t>0640</t>
-  </si>
-  <si>
-    <t>Enseignement et Recherche</t>
-  </si>
-  <si>
-    <t>0660</t>
-  </si>
-  <si>
-    <t>Autres Disciplines</t>
-  </si>
-  <si>
-    <t>0810</t>
-  </si>
-  <si>
-    <t>0820</t>
-  </si>
-  <si>
-    <t>Lutte contre l'Alcoolisme</t>
-  </si>
-  <si>
-    <t>0211</t>
-  </si>
-  <si>
-    <t>Médecine Générale</t>
-  </si>
-  <si>
-    <t>0212</t>
-  </si>
-  <si>
-    <t>Pédiatrie</t>
-  </si>
-  <si>
-    <t>0213</t>
-  </si>
-  <si>
-    <t>Spécialités Médicales</t>
-  </si>
-  <si>
-    <t>0214</t>
-  </si>
-  <si>
-    <t>Réanimation Médicale</t>
-  </si>
-  <si>
-    <t>0215</t>
-  </si>
-  <si>
-    <t>Surveillance Continue Médicale</t>
-  </si>
-  <si>
-    <t>0221</t>
-  </si>
-  <si>
-    <t>Chirurgie Générale</t>
-  </si>
-  <si>
-    <t>0222</t>
-  </si>
-  <si>
-    <t>Chirurgie Infantile</t>
-  </si>
-  <si>
-    <t>0223</t>
-  </si>
-  <si>
-    <t>Spécialités Chirurgicales</t>
-  </si>
-  <si>
-    <t>0224</t>
-  </si>
-  <si>
-    <t>Réanimation Chirurgicale</t>
-  </si>
-  <si>
-    <t>0225</t>
-  </si>
-  <si>
-    <t>Surveillance Continue Chirurgicale</t>
-  </si>
-  <si>
-    <t>0231</t>
-  </si>
-  <si>
-    <t>0241</t>
-  </si>
-  <si>
-    <t>0261</t>
-  </si>
-  <si>
-    <t>Maladie à Evolution Prolongée</t>
-  </si>
-  <si>
-    <t>0262</t>
-  </si>
-  <si>
-    <t>Convalescence, Repos, Régime</t>
-  </si>
-  <si>
-    <t>0263</t>
-  </si>
-  <si>
-    <t>Rééducation Fonctionnelle et Réadaptation</t>
-  </si>
-  <si>
-    <t>0264</t>
-  </si>
-  <si>
-    <t>Lutte contre la Tuberculose et les Maladies Respiratoires</t>
-  </si>
-  <si>
-    <t>0265</t>
-  </si>
-  <si>
-    <t>Cures Thermales</t>
-  </si>
-  <si>
-    <t>0266</t>
-  </si>
-  <si>
-    <t>Cures Médicales</t>
-  </si>
-  <si>
-    <t>0267</t>
-  </si>
-  <si>
-    <t>Cures Médicales pour Enfants</t>
-  </si>
-  <si>
-    <t>0268</t>
-  </si>
-  <si>
-    <t>Post-Cure pour Alcooliques</t>
-  </si>
-  <si>
-    <t>0271</t>
-  </si>
-  <si>
-    <t>0281</t>
-  </si>
-  <si>
-    <t>0291</t>
-  </si>
-  <si>
-    <t>0311</t>
-  </si>
-  <si>
-    <t>0321</t>
-  </si>
-  <si>
-    <t>0331</t>
-  </si>
-  <si>
-    <t>0341</t>
-  </si>
-  <si>
-    <t>Examens Systématique et Dépistage</t>
-  </si>
-  <si>
-    <t>0342</t>
-  </si>
-  <si>
-    <t>Prévention et Conseil</t>
-  </si>
-  <si>
-    <t>0343</t>
-  </si>
-  <si>
-    <t>Soins Divers</t>
-  </si>
-  <si>
-    <t>0351</t>
-  </si>
-  <si>
-    <t>0361</t>
-  </si>
-  <si>
-    <t>0371</t>
-  </si>
-  <si>
-    <t>structures de psychiatrie sans hébergement</t>
-  </si>
-  <si>
-    <t>0372</t>
-  </si>
-  <si>
-    <t>psychiatrie en milieu pénitentiaire</t>
-  </si>
-  <si>
-    <t>0381</t>
-  </si>
-  <si>
-    <t>0411</t>
-  </si>
-  <si>
-    <t>0421</t>
-  </si>
-  <si>
-    <t>0431</t>
-  </si>
-  <si>
-    <t>0441</t>
-  </si>
-  <si>
-    <t>0451</t>
-  </si>
-  <si>
-    <t>0461</t>
-  </si>
-  <si>
-    <t>0471</t>
-  </si>
-  <si>
-    <t>0481</t>
-  </si>
-  <si>
-    <t>Pharmacie et autres biens médicaux</t>
-  </si>
-  <si>
-    <t>0511</t>
-  </si>
-  <si>
-    <t>0521</t>
-  </si>
-  <si>
-    <t>0531</t>
-  </si>
-  <si>
-    <t>0621</t>
-  </si>
-  <si>
-    <t>0631</t>
-  </si>
-  <si>
-    <t>0641</t>
-  </si>
-  <si>
-    <t>Enseignement</t>
-  </si>
-  <si>
-    <t>0642</t>
-  </si>
-  <si>
-    <t>Recherche</t>
-  </si>
-  <si>
-    <t>0661</t>
-  </si>
-  <si>
-    <t>0811</t>
-  </si>
-  <si>
-    <t>0821</t>
-  </si>
-  <si>
-    <t>023</t>
-  </si>
-  <si>
-    <t>Stérilisation</t>
-  </si>
-  <si>
-    <t>034</t>
-  </si>
-  <si>
-    <t>Radiostandard</t>
-  </si>
-  <si>
-    <t>035</t>
-  </si>
-  <si>
-    <t>Scanographie X</t>
-  </si>
-  <si>
-    <t>036</t>
-  </si>
-  <si>
-    <t>Neuroradiologie</t>
-  </si>
-  <si>
-    <t>037</t>
-  </si>
-  <si>
-    <t>Hémodynamique</t>
-  </si>
-  <si>
-    <t>038</t>
-  </si>
-  <si>
-    <t>Radiothérapie de Contact</t>
-  </si>
-  <si>
-    <t>039</t>
-  </si>
-  <si>
-    <t>Radiothérapie Externe(Césium Cobalt)</t>
-  </si>
-  <si>
-    <t>041</t>
-  </si>
-  <si>
-    <t>Radiothérapie Haute Énergie</t>
-  </si>
-  <si>
-    <t>043</t>
-  </si>
-  <si>
-    <t>Curiethérapie</t>
-  </si>
-  <si>
-    <t>044</t>
-  </si>
-  <si>
-    <t>Autre Radiothérapie Spécialisée</t>
-  </si>
-  <si>
-    <t>045</t>
-  </si>
-  <si>
-    <t>Exploration Fonctionnelle Cardiovasculaire</t>
-  </si>
-  <si>
-    <t>046</t>
-  </si>
-  <si>
-    <t>Exploration Fonctionnelle Néphrologique</t>
-  </si>
-  <si>
-    <t>047</t>
-  </si>
-  <si>
-    <t>Exploration Fonctionnelle Pneumologique</t>
-  </si>
-  <si>
-    <t>048</t>
-  </si>
-  <si>
-    <t>Exploration Fonctionnelle Neurologique</t>
-  </si>
-  <si>
-    <t>049</t>
-  </si>
-  <si>
-    <t>Exploration Fonctionnelle Tube Digestif</t>
-  </si>
-  <si>
-    <t>050</t>
-  </si>
-  <si>
-    <t>Exploration Fonctionnelle Fonctionnelle Spécialisée</t>
-  </si>
-  <si>
-    <t>051</t>
-  </si>
-  <si>
-    <t>Exploration Fonctionnelle Cardiovasculaire Néphrologique</t>
-  </si>
-  <si>
-    <t>052</t>
-  </si>
-  <si>
-    <t>Exploration Fonctionnelle Cardiovasculaire Pneumologique.</t>
-  </si>
-  <si>
-    <t>053</t>
-  </si>
-  <si>
-    <t>Exploration Fonctionnelle Fonctionnelle Polyvalente</t>
-  </si>
-  <si>
-    <t>055</t>
-  </si>
-  <si>
-    <t>Réadaption-Rééducation Fonctionnelle Polyvalente</t>
-  </si>
-  <si>
-    <t>056</t>
-  </si>
-  <si>
-    <t>Ergothérapie</t>
-  </si>
-  <si>
-    <t>057</t>
-  </si>
-  <si>
-    <t>Hydrothérapie</t>
-  </si>
-  <si>
-    <t>058</t>
-  </si>
-  <si>
-    <t>Kinésithérapie</t>
-  </si>
-  <si>
-    <t>059</t>
-  </si>
-  <si>
-    <t>Orthophonie</t>
-  </si>
-  <si>
-    <t>060</t>
-  </si>
-  <si>
-    <t>Orthoptie</t>
-  </si>
-  <si>
-    <t>061</t>
-  </si>
-  <si>
-    <t>Autre Rééducation Spécialisée</t>
-  </si>
-  <si>
-    <t>062</t>
-  </si>
-  <si>
-    <t>Anatomie Cytologie Pathologiques</t>
-  </si>
-  <si>
-    <t>063</t>
-  </si>
-  <si>
-    <t>Bactériologie</t>
-  </si>
-  <si>
-    <t>064</t>
-  </si>
-  <si>
-    <t>Biochimie</t>
-  </si>
-  <si>
-    <t>065</t>
-  </si>
-  <si>
-    <t>Biophysique</t>
-  </si>
-  <si>
-    <t>067</t>
-  </si>
-  <si>
-    <t>Coprologie</t>
-  </si>
-  <si>
-    <t>068</t>
-  </si>
-  <si>
-    <t>Cytologie</t>
-  </si>
-  <si>
-    <t>069</t>
-  </si>
-  <si>
-    <t>Cytogénétique</t>
-  </si>
-  <si>
-    <t>070</t>
-  </si>
-  <si>
-    <t>Embryologie</t>
-  </si>
-  <si>
-    <t>071</t>
-  </si>
-  <si>
-    <t>Enzymologie</t>
-  </si>
-  <si>
-    <t>072</t>
-  </si>
-  <si>
-    <t>Hématologie</t>
-  </si>
-  <si>
-    <t>073</t>
-  </si>
-  <si>
-    <t>Histologie</t>
-  </si>
-  <si>
-    <t>074</t>
-  </si>
-  <si>
-    <t>Hormonologie</t>
-  </si>
-  <si>
-    <t>076</t>
-  </si>
-  <si>
-    <t>Immunologie</t>
-  </si>
-  <si>
-    <t>077</t>
-  </si>
-  <si>
-    <t>Bactériologie-Vitro Parasitologie</t>
-  </si>
-  <si>
-    <t>078</t>
-  </si>
-  <si>
-    <t>Mycologie</t>
-  </si>
-  <si>
-    <t>079</t>
-  </si>
-  <si>
-    <t>Parasitologie</t>
-  </si>
-  <si>
-    <t>080</t>
-  </si>
-  <si>
-    <t>Pharmacologie</t>
-  </si>
-  <si>
-    <t>081</t>
-  </si>
-  <si>
-    <t>Sérologie</t>
-  </si>
-  <si>
-    <t>082</t>
-  </si>
-  <si>
-    <t>Toxicologie</t>
-  </si>
-  <si>
-    <t>083</t>
-  </si>
-  <si>
-    <t>Virologie</t>
-  </si>
-  <si>
-    <t>084</t>
-  </si>
-  <si>
-    <t>Biologie Médicale</t>
-  </si>
-  <si>
-    <t>085</t>
-  </si>
-  <si>
-    <t>Autre discipline de biologie médicale spécialisée</t>
-  </si>
-  <si>
-    <t>086</t>
-  </si>
-  <si>
-    <t>Activité de vaccination gratuite</t>
-  </si>
-  <si>
-    <t>087</t>
-  </si>
-  <si>
-    <t>Consultation Anti-Tabac</t>
-  </si>
-  <si>
-    <t>088</t>
-  </si>
-  <si>
-    <t>Médecine Légale</t>
-  </si>
-  <si>
-    <t>089</t>
-  </si>
-  <si>
-    <t>Médecine Préventive Santé Publique</t>
-  </si>
-  <si>
-    <t>090</t>
-  </si>
-  <si>
-    <t>Autres Consultations Soins Externes</t>
-  </si>
-  <si>
-    <t>091</t>
-  </si>
-  <si>
-    <t>Fabrication Préparation Produits Pharmaceutiques</t>
-  </si>
-  <si>
-    <t>092</t>
-  </si>
-  <si>
-    <t>Distribution de Produits Pharmaceutiques</t>
-  </si>
-  <si>
-    <t>093</t>
-  </si>
-  <si>
-    <t>Distribution autres Biens Médicaux</t>
-  </si>
-  <si>
-    <t>094</t>
-  </si>
-  <si>
-    <t>Pharmacocinétique</t>
-  </si>
-  <si>
-    <t>095</t>
-  </si>
-  <si>
-    <t>Fabrication Autres Biens Médicaux Prothèses</t>
-  </si>
-  <si>
-    <t>096</t>
-  </si>
-  <si>
-    <t>Prélèvement Scientifique Vérification Diagnostic</t>
-  </si>
-  <si>
-    <t>097</t>
-  </si>
-  <si>
-    <t>Anesthésiologie</t>
-  </si>
-  <si>
-    <t>098</t>
-  </si>
-  <si>
-    <t>Parasitologie et Mycologie</t>
-  </si>
-  <si>
-    <t>099</t>
-  </si>
-  <si>
-    <t>Activité Pharmaco-Toxico-Vigilance</t>
-  </si>
-  <si>
-    <t>100</t>
-  </si>
-  <si>
-    <t>Radio-Immunologie</t>
-  </si>
-  <si>
-    <t>101</t>
-  </si>
-  <si>
-    <t>Médecine Générale ou Médecine Interne</t>
-  </si>
-  <si>
-    <t>102</t>
-  </si>
-  <si>
-    <t>Maladie Infectieuse et Parasitaire</t>
-  </si>
-  <si>
-    <t>103</t>
-  </si>
-  <si>
-    <t>Centre AntiPoison</t>
-  </si>
-  <si>
-    <t>104</t>
-  </si>
-  <si>
-    <t>Réanimation Médicale Adultes</t>
-  </si>
-  <si>
-    <t>105</t>
-  </si>
-  <si>
-    <t>Réanimation Polyvalente</t>
-  </si>
-  <si>
-    <t>106</t>
-  </si>
-  <si>
-    <t>107</t>
-  </si>
-  <si>
-    <t>SURVEILLANCE CONTINUE POLYV.</t>
-  </si>
-  <si>
-    <t>108</t>
-  </si>
-  <si>
-    <t>109</t>
-  </si>
-  <si>
-    <t>Médecine de l'Adolescent</t>
-  </si>
-  <si>
-    <t>111</t>
-  </si>
-  <si>
-    <t>PEDIATRIE NOURRISSONS</t>
-  </si>
-  <si>
-    <t>112</t>
-  </si>
-  <si>
-    <t>Néonatalogie</t>
-  </si>
-  <si>
-    <t>113</t>
-  </si>
-  <si>
-    <t>Médecine Gériatrique</t>
-  </si>
-  <si>
-    <t>115</t>
-  </si>
-  <si>
-    <t>ALLERGOLOGIE</t>
-  </si>
-  <si>
-    <t>117</t>
-  </si>
-  <si>
-    <t>Dermatologie-Vénérologie</t>
-  </si>
-  <si>
-    <t>119</t>
-  </si>
-  <si>
-    <t>Endocrino-Diabetologie</t>
-  </si>
-  <si>
-    <t>122</t>
-  </si>
-  <si>
-    <t>Maladies Métaboliques Nutrition</t>
-  </si>
-  <si>
-    <t>123</t>
-  </si>
-  <si>
-    <t>Hématologie Maladies du Sang</t>
-  </si>
-  <si>
-    <t>124</t>
-  </si>
-  <si>
-    <t>Hépato-Gastro-Entérologie</t>
-  </si>
-  <si>
-    <t>126</t>
-  </si>
-  <si>
-    <t>MEDECINE CARCINOLOGIQUE</t>
-  </si>
-  <si>
-    <t>127</t>
-  </si>
-  <si>
-    <t>Médecine Cardio-Vasculaire</t>
-  </si>
-  <si>
-    <t>129</t>
-  </si>
-  <si>
-    <t>Neurologie</t>
-  </si>
-  <si>
-    <t>130</t>
-  </si>
-  <si>
-    <t>Pneumologie</t>
-  </si>
-  <si>
-    <t>133</t>
-  </si>
-  <si>
-    <t>Rhumatologie</t>
-  </si>
-  <si>
-    <t>134</t>
-  </si>
-  <si>
-    <t>RADIOTHER. &amp; MEDEC. NUCLEAIRE</t>
-  </si>
-  <si>
-    <t>135</t>
-  </si>
-  <si>
-    <t>RADIOTHERAPIE</t>
-  </si>
-  <si>
-    <t>136</t>
-  </si>
-  <si>
-    <t>Médecine Nucléaire</t>
-  </si>
-  <si>
-    <t>137</t>
-  </si>
-  <si>
-    <t>138</t>
-  </si>
-  <si>
-    <t>141</t>
-  </si>
-  <si>
-    <t>Réanimation Chirurgicale Adultes</t>
-  </si>
-  <si>
-    <t>142</t>
-  </si>
-  <si>
-    <t>143</t>
-  </si>
-  <si>
-    <t>SPECIALITE CHIRURGICALE</t>
-  </si>
-  <si>
-    <t>144</t>
-  </si>
-  <si>
-    <t>Chirurgie Carcinologie</t>
-  </si>
-  <si>
-    <t>145</t>
-  </si>
-  <si>
-    <t>Traitement des Grands Brûlés</t>
-  </si>
-  <si>
-    <t>146</t>
-  </si>
-  <si>
-    <t>Chirurgie Digestive</t>
-  </si>
-  <si>
-    <t>147</t>
-  </si>
-  <si>
-    <t>Chirurgie Thoracique Cardio-Vasculaire</t>
-  </si>
-  <si>
-    <t>148</t>
-  </si>
-  <si>
-    <t>CHIRURGIE THORACO-PULMONAIRE</t>
-  </si>
-  <si>
-    <t>149</t>
-  </si>
-  <si>
-    <t>Chirurgie Vasculaire</t>
-  </si>
-  <si>
-    <t>150</t>
-  </si>
-  <si>
-    <t>CHIRURGIE CARDIO-VASCULAIRE</t>
-  </si>
-  <si>
-    <t>151</t>
-  </si>
-  <si>
-    <t>Neurochirurgie</t>
-  </si>
-  <si>
-    <t>152</t>
-  </si>
-  <si>
-    <t>Orthopédie-Traumatologie</t>
-  </si>
-  <si>
-    <t>153</t>
-  </si>
-  <si>
-    <t>Actes d'explantation de prothèses PIP</t>
-  </si>
-  <si>
-    <t>154</t>
-  </si>
-  <si>
-    <t>Chirurgie Plastique Reconstructive</t>
-  </si>
-  <si>
-    <t>155</t>
-  </si>
-  <si>
-    <t>ORL ET OPHTALMOLOGIE</t>
-  </si>
-  <si>
-    <t>156</t>
-  </si>
-  <si>
-    <t>Oto-rhino-laryngologie</t>
-  </si>
-  <si>
-    <t>157</t>
-  </si>
-  <si>
-    <t>Ophtalmologie</t>
-  </si>
-  <si>
-    <t>158</t>
-  </si>
-  <si>
-    <t>Stomatologie Chirurgie Maxillo-faciale</t>
-  </si>
-  <si>
-    <t>159</t>
-  </si>
-  <si>
-    <t>Stomatologie</t>
-  </si>
-  <si>
-    <t>161</t>
-  </si>
-  <si>
-    <t>Urologie</t>
-  </si>
-  <si>
-    <t>162</t>
-  </si>
-  <si>
-    <t>ORL-OPHTALMOLOG.&amp; STOMATOLOGIE</t>
-  </si>
-  <si>
-    <t>163</t>
-  </si>
-  <si>
-    <t>Gynéco.&amp; Obstétrique</t>
-  </si>
-  <si>
-    <t>164</t>
-  </si>
-  <si>
-    <t>Gynécologie Médicale</t>
-  </si>
-  <si>
-    <t>165</t>
-  </si>
-  <si>
-    <t>166</t>
-  </si>
-  <si>
-    <t>Chroniques Convalescence Indifférencié</t>
-  </si>
-  <si>
-    <t>167</t>
-  </si>
-  <si>
-    <t>Chroniques</t>
-  </si>
-  <si>
-    <t>168</t>
-  </si>
-  <si>
-    <t>Repos-Convalescence Régime Indifférencié</t>
-  </si>
-  <si>
-    <t>169</t>
-  </si>
-  <si>
-    <t>Repos</t>
-  </si>
-  <si>
-    <t>170</t>
-  </si>
-  <si>
-    <t>Convalescence</t>
-  </si>
-  <si>
-    <t>171</t>
-  </si>
-  <si>
-    <t>Régime</t>
-  </si>
-  <si>
-    <t>172</t>
-  </si>
-  <si>
-    <t>Rééducation Fonctionnelle Réadaptation Polyvalente</t>
-  </si>
-  <si>
-    <t>173</t>
-  </si>
-  <si>
-    <t>Cure Thermale</t>
-  </si>
-  <si>
-    <t>174</t>
-  </si>
-  <si>
-    <t>MEDEC.GEN. &amp; SPECIALITE MEDIC.</t>
-  </si>
-  <si>
-    <t>176</t>
-  </si>
-  <si>
-    <t>Long Séjour Personnes Ayant Perdu Leur Autonomie de Vie</t>
-  </si>
-  <si>
-    <t>178</t>
-  </si>
-  <si>
-    <t>Rééducation Fonctionnelle Réadaptation Motrice</t>
-  </si>
-  <si>
-    <t>179</t>
-  </si>
-  <si>
-    <t>Rééducation Fonctionnelle Réadaptation Neurologique</t>
-  </si>
-  <si>
-    <t>180</t>
-  </si>
-  <si>
-    <t>Rééducation des Affections Respiratoires</t>
-  </si>
-  <si>
-    <t>181</t>
-  </si>
-  <si>
-    <t>Chirurgie Générale Spécialités Chirurgicales</t>
-  </si>
-  <si>
-    <t>182</t>
-  </si>
-  <si>
-    <t>Rééducat. Maladies Cardio-Vasculaires</t>
-  </si>
-  <si>
-    <t>183</t>
-  </si>
-  <si>
-    <t>OBSTETRIQUE SANS CHIRURGIE</t>
-  </si>
-  <si>
-    <t>184</t>
-  </si>
-  <si>
-    <t>Rééducation des Affections Hépato-Digestives</t>
-  </si>
-  <si>
-    <t>185</t>
-  </si>
-  <si>
-    <t>Repos-Convalescence Indifférenciés</t>
-  </si>
-  <si>
-    <t>186</t>
-  </si>
-  <si>
-    <t>REEDUCATION PERSONNE AGEE</t>
-  </si>
-  <si>
-    <t>187</t>
-  </si>
-  <si>
-    <t>Rééducation Fonctionnelle Réadaptation</t>
-  </si>
-  <si>
-    <t>189</t>
-  </si>
-  <si>
-    <t>Cure Thermale des Voies Respiratoires</t>
-  </si>
-  <si>
-    <t>191</t>
-  </si>
-  <si>
-    <t>CURE THERM.AFFECT.HEPATO-DIGES</t>
-  </si>
-  <si>
-    <t>192</t>
-  </si>
-  <si>
-    <t>CURE THERM.APPAREIL URINAIRE</t>
-  </si>
-  <si>
-    <t>193</t>
-  </si>
-  <si>
-    <t>Cure Thermale Rhumatologie Séquel.Traum.Ostéo-articaires</t>
-  </si>
-  <si>
-    <t>194</t>
-  </si>
-  <si>
-    <t>Cure Thermale en Dermatologie</t>
-  </si>
-  <si>
-    <t>195</t>
-  </si>
-  <si>
-    <t>Soins aux Toxicomanes</t>
-  </si>
-  <si>
-    <t>196</t>
-  </si>
-  <si>
-    <t>Lutte Contre l'Alcoolisme</t>
-  </si>
-  <si>
-    <t>197</t>
-  </si>
-  <si>
-    <t>Activité dentaire unique</t>
-  </si>
-  <si>
-    <t>198</t>
-  </si>
-  <si>
-    <t>Oncologie</t>
-  </si>
-  <si>
-    <t>200</t>
-  </si>
-  <si>
-    <t>Transfusion Sanguine (Laboratoire)</t>
-  </si>
-  <si>
-    <t>201</t>
-  </si>
-  <si>
-    <t>Banque de Sperme</t>
-  </si>
-  <si>
-    <t>202</t>
-  </si>
-  <si>
-    <t>Banque d'Organes</t>
-  </si>
-  <si>
-    <t>203</t>
-  </si>
-  <si>
-    <t>Dispensaire de Soins</t>
-  </si>
-  <si>
-    <t>204</t>
-  </si>
-  <si>
-    <t>Activité infirmière unique</t>
-  </si>
-  <si>
-    <t>205</t>
-  </si>
-  <si>
-    <t>Act inform dépistage diag infections sexuellmnt transmissibl</t>
-  </si>
-  <si>
-    <t>206</t>
-  </si>
-  <si>
-    <t>Lutte Antihansénienne</t>
-  </si>
-  <si>
-    <t>207</t>
-  </si>
-  <si>
-    <t>S.A.M.U Centre 15</t>
-  </si>
-  <si>
-    <t>208</t>
-  </si>
-  <si>
-    <t>S.M.U.R. U.M.H.</t>
-  </si>
-  <si>
-    <t>209</t>
-  </si>
-  <si>
-    <t>Ambulances</t>
-  </si>
-  <si>
-    <t>211</t>
-  </si>
-  <si>
-    <t>Accueil et Traitement des Urgences Médico-Chirurgicales</t>
-  </si>
-  <si>
-    <t>214</t>
-  </si>
-  <si>
-    <t>Postcure pour Alcooliques</t>
-  </si>
-  <si>
-    <t>217</t>
-  </si>
-  <si>
-    <t>Lutte Contre La Tuberculose Indifférenciée</t>
-  </si>
-  <si>
-    <t>218</t>
-  </si>
-  <si>
-    <t>Activité de lutte anti tuberculose</t>
-  </si>
-  <si>
-    <t>219</t>
-  </si>
-  <si>
-    <t>Lutte Ctre la Tuberculose Pulmonaire</t>
-  </si>
-  <si>
-    <t>220</t>
-  </si>
-  <si>
-    <t>Lutte Ctre Tuberculose Extra-Pulmonaire</t>
-  </si>
-  <si>
-    <t>221</t>
-  </si>
-  <si>
-    <t>Cure et Repos en Prévention</t>
-  </si>
-  <si>
-    <t>222</t>
-  </si>
-  <si>
-    <t>Traitements Préventifs de la Tuberculose</t>
-  </si>
-  <si>
-    <t>223</t>
-  </si>
-  <si>
-    <t>Médecine Générale ou Polyvalente</t>
-  </si>
-  <si>
-    <t>224</t>
-  </si>
-  <si>
-    <t>Observation et Traitement Pneumoconioses</t>
-  </si>
-  <si>
-    <t>225</t>
-  </si>
-  <si>
-    <t>Médecine Interne Spécialités Médicales</t>
-  </si>
-  <si>
-    <t>226</t>
-  </si>
-  <si>
-    <t>Accueil Orientation. des Malades.Tuberculo Pulmonaires</t>
-  </si>
-  <si>
-    <t>227</t>
-  </si>
-  <si>
-    <t>Postcure pour Tuberculeux</t>
-  </si>
-  <si>
-    <t>230</t>
-  </si>
-  <si>
-    <t>Psychiatrie Générale</t>
-  </si>
-  <si>
-    <t>231</t>
-  </si>
-  <si>
-    <t>centre médico-psychologique adulte</t>
-  </si>
-  <si>
-    <t>232</t>
-  </si>
-  <si>
-    <t>centre médico-psychologique infanto-juvénile</t>
-  </si>
-  <si>
-    <t>233</t>
-  </si>
-  <si>
-    <t>Centre d'accueil thérapeutique à temps partiel adulte</t>
-  </si>
-  <si>
-    <t>234</t>
-  </si>
-  <si>
-    <t>Centre d'accueil thérapeutique à temps partiel infanto-juv</t>
-  </si>
-  <si>
-    <t>235</t>
-  </si>
-  <si>
-    <t>soins intensifs de néonatologie</t>
-  </si>
-  <si>
-    <t>236</t>
-  </si>
-  <si>
-    <t>Psychiatrie Infanto-Juvenile</t>
-  </si>
-  <si>
-    <t>237</t>
-  </si>
-  <si>
-    <t>centre d'accueil permanent adulte</t>
-  </si>
-  <si>
-    <t>238</t>
-  </si>
-  <si>
-    <t>centre d'accueil permanent infanto-juvénile</t>
-  </si>
-  <si>
-    <t>240</t>
-  </si>
-  <si>
-    <t>POST-CURE POUR TOXICOMANES</t>
-  </si>
-  <si>
-    <t>241</t>
-  </si>
-  <si>
-    <t>Hygiène Alimentaire</t>
-  </si>
-  <si>
-    <t>244</t>
-  </si>
-  <si>
-    <t>hospitalisation psychiatrique à domicile adulte</t>
-  </si>
-  <si>
-    <t>245</t>
-  </si>
-  <si>
-    <t>hospitalisation psychiatrique à domicile infanto-juv</t>
-  </si>
-  <si>
-    <t>252</t>
-  </si>
-  <si>
-    <t>Pouponnière à Caractère Sanitaire</t>
-  </si>
-  <si>
-    <t>263</t>
-  </si>
-  <si>
-    <t>Placement familial sanitaire</t>
-  </si>
-  <si>
-    <t>265</t>
-  </si>
-  <si>
-    <t>COLONIE A CARACTERE SANITAIRE</t>
-  </si>
-  <si>
-    <t>302</t>
-  </si>
-  <si>
-    <t>CHIMIOTHER.EN HEMATOL.&amp; CANCER</t>
-  </si>
-  <si>
-    <t>303</t>
-  </si>
-  <si>
-    <t>Urgence Médicale</t>
-  </si>
-  <si>
-    <t>307</t>
-  </si>
-  <si>
-    <t>Urgence Chirurgicale (SERV.PORTE)</t>
-  </si>
-  <si>
-    <t>308</t>
-  </si>
-  <si>
-    <t>Urgence Indifférenciée</t>
-  </si>
-  <si>
-    <t>309</t>
-  </si>
-  <si>
-    <t>Interruption Volontaire de Grossesse</t>
-  </si>
-  <si>
-    <t>310</t>
-  </si>
-  <si>
-    <t>Examens de Santé et Bilans</t>
-  </si>
-  <si>
-    <t>312</t>
-  </si>
-  <si>
-    <t>Néphrologie</t>
-  </si>
-  <si>
-    <t>362</t>
-  </si>
-  <si>
-    <t>Chirurgie Obstétrique Indifférenciées</t>
-  </si>
-  <si>
-    <t>384</t>
-  </si>
-  <si>
-    <t>Protection Maternelle &amp; Infantile</t>
-  </si>
-  <si>
-    <t>385</t>
-  </si>
-  <si>
-    <t>Consultations Prénuptiale Prénatale et Postnatale</t>
-  </si>
-  <si>
-    <t>386</t>
-  </si>
-  <si>
-    <t>Consultations Protection Infantile</t>
-  </si>
-  <si>
-    <t>387</t>
-  </si>
-  <si>
-    <t>Consultations de Nourrissons</t>
-  </si>
-  <si>
-    <t>388</t>
-  </si>
-  <si>
-    <t>Consultations de deuxième age</t>
-  </si>
-  <si>
-    <t>389</t>
-  </si>
-  <si>
-    <t>Lutte contre la Stérilité</t>
-  </si>
-  <si>
-    <t>390</t>
-  </si>
-  <si>
-    <t>Consultation en Conseil Génétique</t>
-  </si>
-  <si>
-    <t>391</t>
-  </si>
-  <si>
-    <t>Consultation de Planification ou Éducation Familiale</t>
-  </si>
-  <si>
-    <t>392</t>
-  </si>
-  <si>
-    <t>Information Consultation ou Conseil familial</t>
-  </si>
-  <si>
-    <t>394</t>
-  </si>
-  <si>
-    <t>Lactarium</t>
-  </si>
-  <si>
-    <t>395</t>
-  </si>
-  <si>
-    <t>Guidance Parentale</t>
-  </si>
-  <si>
-    <t>396</t>
-  </si>
-  <si>
-    <t>Guidance infantile</t>
-  </si>
-  <si>
-    <t>401</t>
-  </si>
-  <si>
-    <t>unité de proximité accueil traitement orientation urgences</t>
-  </si>
-  <si>
-    <t>402</t>
-  </si>
-  <si>
-    <t>service accueil et traitement urgences</t>
-  </si>
-  <si>
-    <t>403</t>
-  </si>
-  <si>
-    <t>pôle spécialisé urgence en pédiatrie</t>
-  </si>
-  <si>
-    <t>404</t>
-  </si>
-  <si>
-    <t>pôle spécialisé urgence en ophtalmologie</t>
-  </si>
-  <si>
-    <t>405</t>
-  </si>
-  <si>
-    <t>pôle spécialisé urgence en cardiologie</t>
-  </si>
-  <si>
-    <t>406</t>
-  </si>
-  <si>
-    <t>pôle spécialisé urgence en traumatologie</t>
-  </si>
-  <si>
-    <t>407</t>
-  </si>
-  <si>
-    <t>pôle spécialisé urgence en SOS main</t>
-  </si>
-  <si>
-    <t>408</t>
-  </si>
-  <si>
-    <t>pôle spécialisé urgence en neurochirurgie</t>
-  </si>
-  <si>
-    <t>409</t>
-  </si>
-  <si>
-    <t>autre pôle spécialisé urgence non dénommé ailleurs</t>
-  </si>
-  <si>
-    <t>446</t>
-  </si>
-  <si>
-    <t>Médecine Scolaire</t>
-  </si>
-  <si>
-    <t>447</t>
-  </si>
-  <si>
-    <t>Médecine Universitaire</t>
-  </si>
-  <si>
-    <t>448</t>
-  </si>
-  <si>
-    <t>Médecine Sportive</t>
-  </si>
-  <si>
-    <t>452</t>
-  </si>
-  <si>
-    <t>Aide Aux Insuffisants Respiratoires</t>
-  </si>
-  <si>
     <t>Cure Médic.Spécialisée Contre Tuberculose Indifférenciée</t>
   </si>
   <si>
@@ -2816,6 +2921,42 @@
   </si>
   <si>
     <t>Activité sage-femme en maison de naissance</t>
+  </si>
+  <si>
+    <t>855</t>
+  </si>
+  <si>
+    <t>Maison médicale de garde</t>
+  </si>
+  <si>
+    <t>Activités contribuant à la permanence des Soins Ambulatoires (PDSA) exercées dans le cadre d'une Maison Médicale de Garde</t>
+  </si>
+  <si>
+    <t>856</t>
+  </si>
+  <si>
+    <t>Point fixe de garde</t>
+  </si>
+  <si>
+    <t>Activités contribuant à la permanence des Soins Ambulatoires (PDSA) exercées dans le cadre d'un Point fixe de garde</t>
+  </si>
+  <si>
+    <t>857</t>
+  </si>
+  <si>
+    <t>Point fixe de consultation</t>
+  </si>
+  <si>
+    <t>Activités contribuant à la permanence des Soins Ambulatoires (PDSA) exercées dans le cadre d'un Point fixe de consultation</t>
+  </si>
+  <si>
+    <t>858</t>
+  </si>
+  <si>
+    <t>Visite à domicile</t>
+  </si>
+  <si>
+    <t>Activités contribuant à la permanence des Soins Ambulatoires (PDSA) exercées dans le cadre de visites à domicile</t>
   </si>
   <si>
     <t>949</t>
@@ -3311,7 +3452,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D458"/>
+  <dimension ref="A1:D479"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -5256,7 +5397,7 @@
         <v>364</v>
       </c>
       <c r="C162" t="s" s="2">
-        <v>159</v>
+        <v>365</v>
       </c>
       <c r="D162" s="2"/>
     </row>
@@ -5265,10 +5406,10 @@
         <v>70</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C163" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="D163" s="2"/>
     </row>
@@ -5277,10 +5418,10 @@
         <v>70</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="C164" t="s" s="2">
-        <v>153</v>
+        <v>369</v>
       </c>
       <c r="D164" s="2"/>
     </row>
@@ -5289,10 +5430,10 @@
         <v>70</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="C165" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="D165" s="2"/>
     </row>
@@ -5301,10 +5442,10 @@
         <v>70</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="C166" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="D166" s="2"/>
     </row>
@@ -5313,10 +5454,10 @@
         <v>70</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="C167" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="D167" s="2"/>
     </row>
@@ -5325,10 +5466,10 @@
         <v>70</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="C168" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="D168" s="2"/>
     </row>
@@ -5337,10 +5478,10 @@
         <v>70</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="C169" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="D169" s="2"/>
     </row>
@@ -5349,10 +5490,10 @@
         <v>70</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="C170" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="D170" s="2"/>
     </row>
@@ -5361,10 +5502,10 @@
         <v>70</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="C171" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="D171" s="2"/>
     </row>
@@ -5373,10 +5514,10 @@
         <v>70</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="C172" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="D172" s="2"/>
     </row>
@@ -5385,10 +5526,10 @@
         <v>70</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="C173" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="D173" s="2"/>
     </row>
@@ -5397,10 +5538,10 @@
         <v>70</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="C174" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="D174" s="2"/>
     </row>
@@ -5409,10 +5550,10 @@
         <v>70</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="C175" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="D175" s="2"/>
     </row>
@@ -5421,10 +5562,10 @@
         <v>70</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="C176" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="D176" s="2"/>
     </row>
@@ -5433,10 +5574,10 @@
         <v>70</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="C177" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="D177" s="2"/>
     </row>
@@ -5445,10 +5586,10 @@
         <v>70</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="C178" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="D178" s="2"/>
     </row>
@@ -5457,10 +5598,10 @@
         <v>70</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="C179" t="s" s="2">
-        <v>397</v>
+        <v>159</v>
       </c>
       <c r="D179" s="2"/>
     </row>
@@ -5469,10 +5610,10 @@
         <v>70</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="C180" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="D180" s="2"/>
     </row>
@@ -5481,10 +5622,10 @@
         <v>70</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="C181" t="s" s="2">
-        <v>401</v>
+        <v>153</v>
       </c>
       <c r="D181" s="2"/>
     </row>
@@ -5508,7 +5649,7 @@
         <v>404</v>
       </c>
       <c r="C183" t="s" s="2">
-        <v>161</v>
+        <v>405</v>
       </c>
       <c r="D183" s="2"/>
     </row>
@@ -5517,10 +5658,10 @@
         <v>70</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C184" t="s" s="2">
-        <v>163</v>
+        <v>407</v>
       </c>
       <c r="D184" s="2"/>
     </row>
@@ -5529,10 +5670,10 @@
         <v>70</v>
       </c>
       <c r="B185" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="C185" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="D185" s="2"/>
     </row>
@@ -5541,10 +5682,10 @@
         <v>70</v>
       </c>
       <c r="B186" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="C186" t="s" s="2">
-        <v>169</v>
+        <v>411</v>
       </c>
       <c r="D186" s="2"/>
     </row>
@@ -5553,10 +5694,10 @@
         <v>70</v>
       </c>
       <c r="B187" t="s" s="2">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="C187" t="s" s="2">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="D187" s="2"/>
     </row>
@@ -5565,10 +5706,10 @@
         <v>70</v>
       </c>
       <c r="B188" t="s" s="2">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="C188" t="s" s="2">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="D188" s="2"/>
     </row>
@@ -5577,10 +5718,10 @@
         <v>70</v>
       </c>
       <c r="B189" t="s" s="2">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="C189" t="s" s="2">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="D189" s="2"/>
     </row>
@@ -5589,10 +5730,10 @@
         <v>70</v>
       </c>
       <c r="B190" t="s" s="2">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="C190" t="s" s="2">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="D190" s="2"/>
     </row>
@@ -5601,10 +5742,10 @@
         <v>70</v>
       </c>
       <c r="B191" t="s" s="2">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="C191" t="s" s="2">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="D191" s="2"/>
     </row>
@@ -5613,10 +5754,10 @@
         <v>70</v>
       </c>
       <c r="B192" t="s" s="2">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="C192" t="s" s="2">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="D192" s="2"/>
     </row>
@@ -5625,10 +5766,10 @@
         <v>70</v>
       </c>
       <c r="B193" t="s" s="2">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="C193" t="s" s="2">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="D193" s="2"/>
     </row>
@@ -5637,10 +5778,10 @@
         <v>70</v>
       </c>
       <c r="B194" t="s" s="2">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="C194" t="s" s="2">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="D194" s="2"/>
     </row>
@@ -5649,10 +5790,10 @@
         <v>70</v>
       </c>
       <c r="B195" t="s" s="2">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="C195" t="s" s="2">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="D195" s="2"/>
     </row>
@@ -5661,10 +5802,10 @@
         <v>70</v>
       </c>
       <c r="B196" t="s" s="2">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="C196" t="s" s="2">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="D196" s="2"/>
     </row>
@@ -5673,10 +5814,10 @@
         <v>70</v>
       </c>
       <c r="B197" t="s" s="2">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="C197" t="s" s="2">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="D197" s="2"/>
     </row>
@@ -5685,10 +5826,10 @@
         <v>70</v>
       </c>
       <c r="B198" t="s" s="2">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="C198" t="s" s="2">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="D198" s="2"/>
     </row>
@@ -5697,10 +5838,10 @@
         <v>70</v>
       </c>
       <c r="B199" t="s" s="2">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="C199" t="s" s="2">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="D199" s="2"/>
     </row>
@@ -5709,10 +5850,10 @@
         <v>70</v>
       </c>
       <c r="B200" t="s" s="2">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="C200" t="s" s="2">
-        <v>436</v>
+        <v>161</v>
       </c>
       <c r="D200" s="2"/>
     </row>
@@ -5721,10 +5862,10 @@
         <v>70</v>
       </c>
       <c r="B201" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="C201" t="s" s="2">
-        <v>438</v>
+        <v>163</v>
       </c>
       <c r="D201" s="2"/>
     </row>
@@ -5733,10 +5874,10 @@
         <v>70</v>
       </c>
       <c r="B202" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="C202" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="D202" s="2"/>
     </row>
@@ -5745,10 +5886,10 @@
         <v>70</v>
       </c>
       <c r="B203" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="C203" t="s" s="2">
-        <v>442</v>
+        <v>169</v>
       </c>
       <c r="D203" s="2"/>
     </row>
@@ -5808,7 +5949,7 @@
         <v>451</v>
       </c>
       <c r="C208" t="s" s="2">
-        <v>88</v>
+        <v>452</v>
       </c>
       <c r="D208" s="2"/>
     </row>
@@ -5817,10 +5958,10 @@
         <v>70</v>
       </c>
       <c r="B209" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="C209" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="D209" s="2"/>
     </row>
@@ -5829,10 +5970,10 @@
         <v>70</v>
       </c>
       <c r="B210" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="C210" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="D210" s="2"/>
     </row>
@@ -5841,10 +5982,10 @@
         <v>70</v>
       </c>
       <c r="B211" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C211" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="D211" s="2"/>
     </row>
@@ -5853,10 +5994,10 @@
         <v>70</v>
       </c>
       <c r="B212" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C212" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="D212" s="2"/>
     </row>
@@ -5865,10 +6006,10 @@
         <v>70</v>
       </c>
       <c r="B213" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="C213" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="D213" s="2"/>
     </row>
@@ -5877,10 +6018,10 @@
         <v>70</v>
       </c>
       <c r="B214" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="C214" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="D214" s="2"/>
     </row>
@@ -5889,10 +6030,10 @@
         <v>70</v>
       </c>
       <c r="B215" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="C215" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="D215" s="2"/>
     </row>
@@ -5901,10 +6042,10 @@
         <v>70</v>
       </c>
       <c r="B216" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="C216" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="D216" s="2"/>
     </row>
@@ -5913,10 +6054,10 @@
         <v>70</v>
       </c>
       <c r="B217" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="C217" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="D217" s="2"/>
     </row>
@@ -5925,10 +6066,10 @@
         <v>70</v>
       </c>
       <c r="B218" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="C218" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="D218" s="2"/>
     </row>
@@ -5937,10 +6078,10 @@
         <v>70</v>
       </c>
       <c r="B219" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="C219" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="D219" s="2"/>
     </row>
@@ -5949,10 +6090,10 @@
         <v>70</v>
       </c>
       <c r="B220" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="C220" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="D220" s="2"/>
     </row>
@@ -5961,10 +6102,10 @@
         <v>70</v>
       </c>
       <c r="B221" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="C221" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="D221" s="2"/>
     </row>
@@ -5973,10 +6114,10 @@
         <v>70</v>
       </c>
       <c r="B222" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="C222" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="D222" s="2"/>
     </row>
@@ -5985,10 +6126,10 @@
         <v>70</v>
       </c>
       <c r="B223" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C223" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="D223" s="2"/>
     </row>
@@ -5997,10 +6138,10 @@
         <v>70</v>
       </c>
       <c r="B224" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="C224" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="D224" s="2"/>
     </row>
@@ -6009,10 +6150,10 @@
         <v>70</v>
       </c>
       <c r="B225" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="C225" t="s" s="2">
-        <v>485</v>
+        <v>88</v>
       </c>
       <c r="D225" s="2"/>
     </row>
@@ -7029,10 +7170,10 @@
         <v>70</v>
       </c>
       <c r="B310" t="s" s="2">
-        <v>36</v>
+        <v>654</v>
       </c>
       <c r="C310" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="D310" s="2"/>
     </row>
@@ -7041,10 +7182,10 @@
         <v>70</v>
       </c>
       <c r="B311" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="C311" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="D311" s="2"/>
     </row>
@@ -7053,10 +7194,10 @@
         <v>70</v>
       </c>
       <c r="B312" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="C312" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="D312" s="2"/>
     </row>
@@ -7065,10 +7206,10 @@
         <v>70</v>
       </c>
       <c r="B313" t="s" s="2">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="C313" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="D313" s="2"/>
     </row>
@@ -7077,10 +7218,10 @@
         <v>70</v>
       </c>
       <c r="B314" t="s" s="2">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="C314" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="D314" s="2"/>
     </row>
@@ -7089,10 +7230,10 @@
         <v>70</v>
       </c>
       <c r="B315" t="s" s="2">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="C315" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="D315" s="2"/>
     </row>
@@ -7101,10 +7242,10 @@
         <v>70</v>
       </c>
       <c r="B316" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="C316" t="s" s="2">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="D316" s="2"/>
     </row>
@@ -7113,10 +7254,10 @@
         <v>70</v>
       </c>
       <c r="B317" t="s" s="2">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="C317" t="s" s="2">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="D317" s="2"/>
     </row>
@@ -7125,10 +7266,10 @@
         <v>70</v>
       </c>
       <c r="B318" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="C318" t="s" s="2">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="D318" s="2"/>
     </row>
@@ -7137,10 +7278,10 @@
         <v>70</v>
       </c>
       <c r="B319" t="s" s="2">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="C319" t="s" s="2">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="D319" s="2"/>
     </row>
@@ -7149,10 +7290,10 @@
         <v>70</v>
       </c>
       <c r="B320" t="s" s="2">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="C320" t="s" s="2">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="D320" s="2"/>
     </row>
@@ -7161,10 +7302,10 @@
         <v>70</v>
       </c>
       <c r="B321" t="s" s="2">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="C321" t="s" s="2">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="D321" s="2"/>
     </row>
@@ -7173,10 +7314,10 @@
         <v>70</v>
       </c>
       <c r="B322" t="s" s="2">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="C322" t="s" s="2">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="D322" s="2"/>
     </row>
@@ -7185,10 +7326,10 @@
         <v>70</v>
       </c>
       <c r="B323" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="C323" t="s" s="2">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="D323" s="2"/>
     </row>
@@ -7197,10 +7338,10 @@
         <v>70</v>
       </c>
       <c r="B324" t="s" s="2">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="C324" t="s" s="2">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="D324" s="2"/>
     </row>
@@ -7209,10 +7350,10 @@
         <v>70</v>
       </c>
       <c r="B325" t="s" s="2">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="C325" t="s" s="2">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="D325" s="2"/>
     </row>
@@ -7221,10 +7362,10 @@
         <v>70</v>
       </c>
       <c r="B326" t="s" s="2">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="C326" t="s" s="2">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="D326" s="2"/>
     </row>
@@ -7233,10 +7374,10 @@
         <v>70</v>
       </c>
       <c r="B327" t="s" s="2">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="C327" t="s" s="2">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="D327" s="2"/>
     </row>
@@ -7245,10 +7386,10 @@
         <v>70</v>
       </c>
       <c r="B328" t="s" s="2">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="C328" t="s" s="2">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="D328" s="2"/>
     </row>
@@ -7257,10 +7398,10 @@
         <v>70</v>
       </c>
       <c r="B329" t="s" s="2">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="C329" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="D329" s="2"/>
     </row>
@@ -7269,10 +7410,10 @@
         <v>70</v>
       </c>
       <c r="B330" t="s" s="2">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="C330" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="D330" s="2"/>
     </row>
@@ -7281,10 +7422,10 @@
         <v>70</v>
       </c>
       <c r="B331" t="s" s="2">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="C331" t="s" s="2">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="D331" s="2"/>
     </row>
@@ -7293,10 +7434,10 @@
         <v>70</v>
       </c>
       <c r="B332" t="s" s="2">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="C332" t="s" s="2">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="D332" s="2"/>
     </row>
@@ -7305,10 +7446,10 @@
         <v>70</v>
       </c>
       <c r="B333" t="s" s="2">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="C333" t="s" s="2">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="D333" s="2"/>
     </row>
@@ -7317,10 +7458,10 @@
         <v>70</v>
       </c>
       <c r="B334" t="s" s="2">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="C334" t="s" s="2">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="D334" s="2"/>
     </row>
@@ -7329,10 +7470,10 @@
         <v>70</v>
       </c>
       <c r="B335" t="s" s="2">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="C335" t="s" s="2">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="D335" s="2"/>
     </row>
@@ -7341,10 +7482,10 @@
         <v>70</v>
       </c>
       <c r="B336" t="s" s="2">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="C336" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="D336" s="2"/>
     </row>
@@ -7353,10 +7494,10 @@
         <v>70</v>
       </c>
       <c r="B337" t="s" s="2">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="C337" t="s" s="2">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="D337" s="2"/>
     </row>
@@ -7365,10 +7506,10 @@
         <v>70</v>
       </c>
       <c r="B338" t="s" s="2">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="C338" t="s" s="2">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="D338" s="2"/>
     </row>
@@ -7377,10 +7518,10 @@
         <v>70</v>
       </c>
       <c r="B339" t="s" s="2">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="C339" t="s" s="2">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="D339" s="2"/>
     </row>
@@ -7389,10 +7530,10 @@
         <v>70</v>
       </c>
       <c r="B340" t="s" s="2">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="C340" t="s" s="2">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="D340" s="2"/>
     </row>
@@ -7401,10 +7542,10 @@
         <v>70</v>
       </c>
       <c r="B341" t="s" s="2">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="C341" t="s" s="2">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="D341" s="2"/>
     </row>
@@ -7413,10 +7554,10 @@
         <v>70</v>
       </c>
       <c r="B342" t="s" s="2">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="C342" t="s" s="2">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="D342" s="2"/>
     </row>
@@ -7425,10 +7566,10 @@
         <v>70</v>
       </c>
       <c r="B343" t="s" s="2">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="C343" t="s" s="2">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="D343" s="2"/>
     </row>
@@ -7437,10 +7578,10 @@
         <v>70</v>
       </c>
       <c r="B344" t="s" s="2">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="C344" t="s" s="2">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="D344" s="2"/>
     </row>
@@ -7449,10 +7590,10 @@
         <v>70</v>
       </c>
       <c r="B345" t="s" s="2">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="C345" t="s" s="2">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="D345" s="2"/>
     </row>
@@ -7461,10 +7602,10 @@
         <v>70</v>
       </c>
       <c r="B346" t="s" s="2">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="C346" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="D346" s="2"/>
     </row>
@@ -7473,10 +7614,10 @@
         <v>70</v>
       </c>
       <c r="B347" t="s" s="2">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="C347" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="D347" s="2"/>
     </row>
@@ -7485,10 +7626,10 @@
         <v>70</v>
       </c>
       <c r="B348" t="s" s="2">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="C348" t="s" s="2">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="D348" s="2"/>
     </row>
@@ -7497,10 +7638,10 @@
         <v>70</v>
       </c>
       <c r="B349" t="s" s="2">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="C349" t="s" s="2">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="D349" s="2"/>
     </row>
@@ -7509,10 +7650,10 @@
         <v>70</v>
       </c>
       <c r="B350" t="s" s="2">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="C350" t="s" s="2">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="D350" s="2"/>
     </row>
@@ -7521,10 +7662,10 @@
         <v>70</v>
       </c>
       <c r="B351" t="s" s="2">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="C351" t="s" s="2">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="D351" s="2"/>
     </row>
@@ -7533,10 +7674,10 @@
         <v>70</v>
       </c>
       <c r="B352" t="s" s="2">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="C352" t="s" s="2">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="D352" s="2"/>
     </row>
@@ -7545,10 +7686,10 @@
         <v>70</v>
       </c>
       <c r="B353" t="s" s="2">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="C353" t="s" s="2">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="D353" s="2"/>
     </row>
@@ -7557,10 +7698,10 @@
         <v>70</v>
       </c>
       <c r="B354" t="s" s="2">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="C354" t="s" s="2">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="D354" s="2"/>
     </row>
@@ -7569,10 +7710,10 @@
         <v>70</v>
       </c>
       <c r="B355" t="s" s="2">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="C355" t="s" s="2">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="D355" s="2"/>
     </row>
@@ -7581,10 +7722,10 @@
         <v>70</v>
       </c>
       <c r="B356" t="s" s="2">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="C356" t="s" s="2">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="D356" s="2"/>
     </row>
@@ -7593,10 +7734,10 @@
         <v>70</v>
       </c>
       <c r="B357" t="s" s="2">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="C357" t="s" s="2">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="D357" s="2"/>
     </row>
@@ -7605,10 +7746,10 @@
         <v>70</v>
       </c>
       <c r="B358" t="s" s="2">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="C358" t="s" s="2">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="D358" s="2"/>
     </row>
@@ -7617,10 +7758,10 @@
         <v>70</v>
       </c>
       <c r="B359" t="s" s="2">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="C359" t="s" s="2">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="D359" s="2"/>
     </row>
@@ -7629,10 +7770,10 @@
         <v>70</v>
       </c>
       <c r="B360" t="s" s="2">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="C360" t="s" s="2">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="D360" s="2"/>
     </row>
@@ -7641,10 +7782,10 @@
         <v>70</v>
       </c>
       <c r="B361" t="s" s="2">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="C361" t="s" s="2">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="D361" s="2"/>
     </row>
@@ -7653,10 +7794,10 @@
         <v>70</v>
       </c>
       <c r="B362" t="s" s="2">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="C362" t="s" s="2">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="D362" s="2"/>
     </row>
@@ -7665,10 +7806,10 @@
         <v>70</v>
       </c>
       <c r="B363" t="s" s="2">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="C363" t="s" s="2">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="D363" s="2"/>
     </row>
@@ -7677,10 +7818,10 @@
         <v>70</v>
       </c>
       <c r="B364" t="s" s="2">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="C364" t="s" s="2">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="D364" s="2"/>
     </row>
@@ -7689,10 +7830,10 @@
         <v>70</v>
       </c>
       <c r="B365" t="s" s="2">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="C365" t="s" s="2">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="D365" s="2"/>
     </row>
@@ -7701,10 +7842,10 @@
         <v>70</v>
       </c>
       <c r="B366" t="s" s="2">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="C366" t="s" s="2">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="D366" s="2"/>
     </row>
@@ -7713,10 +7854,10 @@
         <v>70</v>
       </c>
       <c r="B367" t="s" s="2">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="C367" t="s" s="2">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="D367" s="2"/>
     </row>
@@ -7725,10 +7866,10 @@
         <v>70</v>
       </c>
       <c r="B368" t="s" s="2">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="C368" t="s" s="2">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="D368" s="2"/>
     </row>
@@ -7737,10 +7878,10 @@
         <v>70</v>
       </c>
       <c r="B369" t="s" s="2">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="C369" t="s" s="2">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="D369" s="2"/>
     </row>
@@ -7749,10 +7890,10 @@
         <v>70</v>
       </c>
       <c r="B370" t="s" s="2">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="C370" t="s" s="2">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="D370" s="2"/>
     </row>
@@ -7761,10 +7902,10 @@
         <v>70</v>
       </c>
       <c r="B371" t="s" s="2">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="C371" t="s" s="2">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="D371" s="2"/>
     </row>
@@ -7773,10 +7914,10 @@
         <v>70</v>
       </c>
       <c r="B372" t="s" s="2">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="C372" t="s" s="2">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="D372" s="2"/>
     </row>
@@ -7785,10 +7926,10 @@
         <v>70</v>
       </c>
       <c r="B373" t="s" s="2">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="C373" t="s" s="2">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="D373" s="2"/>
     </row>
@@ -7797,10 +7938,10 @@
         <v>70</v>
       </c>
       <c r="B374" t="s" s="2">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="C374" t="s" s="2">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="D374" s="2"/>
     </row>
@@ -7809,10 +7950,10 @@
         <v>70</v>
       </c>
       <c r="B375" t="s" s="2">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="C375" t="s" s="2">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="D375" s="2"/>
     </row>
@@ -7821,10 +7962,10 @@
         <v>70</v>
       </c>
       <c r="B376" t="s" s="2">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="C376" t="s" s="2">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="D376" s="2"/>
     </row>
@@ -7833,10 +7974,10 @@
         <v>70</v>
       </c>
       <c r="B377" t="s" s="2">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="C377" t="s" s="2">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="D377" s="2"/>
     </row>
@@ -7845,10 +7986,10 @@
         <v>70</v>
       </c>
       <c r="B378" t="s" s="2">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="C378" t="s" s="2">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="D378" s="2"/>
     </row>
@@ -7857,10 +7998,10 @@
         <v>70</v>
       </c>
       <c r="B379" t="s" s="2">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="C379" t="s" s="2">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="D379" s="2"/>
     </row>
@@ -7869,10 +8010,10 @@
         <v>70</v>
       </c>
       <c r="B380" t="s" s="2">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="C380" t="s" s="2">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="D380" s="2"/>
     </row>
@@ -7881,10 +8022,10 @@
         <v>70</v>
       </c>
       <c r="B381" t="s" s="2">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="C381" t="s" s="2">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="D381" s="2"/>
     </row>
@@ -7893,10 +8034,10 @@
         <v>70</v>
       </c>
       <c r="B382" t="s" s="2">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="C382" t="s" s="2">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="D382" s="2"/>
     </row>
@@ -7905,10 +8046,10 @@
         <v>70</v>
       </c>
       <c r="B383" t="s" s="2">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="C383" t="s" s="2">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="D383" s="2"/>
     </row>
@@ -7917,10 +8058,10 @@
         <v>70</v>
       </c>
       <c r="B384" t="s" s="2">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="C384" t="s" s="2">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="D384" s="2"/>
     </row>
@@ -7929,10 +8070,10 @@
         <v>70</v>
       </c>
       <c r="B385" t="s" s="2">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="C385" t="s" s="2">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="D385" s="2"/>
     </row>
@@ -7941,10 +8082,10 @@
         <v>70</v>
       </c>
       <c r="B386" t="s" s="2">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="C386" t="s" s="2">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="D386" s="2"/>
     </row>
@@ -7953,10 +8094,10 @@
         <v>70</v>
       </c>
       <c r="B387" t="s" s="2">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="C387" t="s" s="2">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="D387" s="2"/>
     </row>
@@ -7965,10 +8106,10 @@
         <v>70</v>
       </c>
       <c r="B388" t="s" s="2">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="C388" t="s" s="2">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="D388" s="2"/>
     </row>
@@ -7977,10 +8118,10 @@
         <v>70</v>
       </c>
       <c r="B389" t="s" s="2">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="C389" t="s" s="2">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="D389" s="2"/>
     </row>
@@ -7989,10 +8130,10 @@
         <v>70</v>
       </c>
       <c r="B390" t="s" s="2">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="C390" t="s" s="2">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="D390" s="2"/>
     </row>
@@ -8001,10 +8142,10 @@
         <v>70</v>
       </c>
       <c r="B391" t="s" s="2">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="C391" t="s" s="2">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="D391" s="2"/>
     </row>
@@ -8013,10 +8154,10 @@
         <v>70</v>
       </c>
       <c r="B392" t="s" s="2">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="C392" t="s" s="2">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="D392" s="2"/>
     </row>
@@ -8025,10 +8166,10 @@
         <v>70</v>
       </c>
       <c r="B393" t="s" s="2">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="C393" t="s" s="2">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="D393" s="2"/>
     </row>
@@ -8037,10 +8178,10 @@
         <v>70</v>
       </c>
       <c r="B394" t="s" s="2">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="C394" t="s" s="2">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="D394" s="2"/>
     </row>
@@ -8049,10 +8190,10 @@
         <v>70</v>
       </c>
       <c r="B395" t="s" s="2">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="C395" t="s" s="2">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="D395" s="2"/>
     </row>
@@ -8061,10 +8202,10 @@
         <v>70</v>
       </c>
       <c r="B396" t="s" s="2">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="C396" t="s" s="2">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="D396" s="2"/>
     </row>
@@ -8073,10 +8214,10 @@
         <v>70</v>
       </c>
       <c r="B397" t="s" s="2">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="C397" t="s" s="2">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="D397" s="2"/>
     </row>
@@ -8085,10 +8226,10 @@
         <v>70</v>
       </c>
       <c r="B398" t="s" s="2">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="C398" t="s" s="2">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="D398" s="2"/>
     </row>
@@ -8097,10 +8238,10 @@
         <v>70</v>
       </c>
       <c r="B399" t="s" s="2">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="C399" t="s" s="2">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="D399" s="2"/>
     </row>
@@ -8109,10 +8250,10 @@
         <v>70</v>
       </c>
       <c r="B400" t="s" s="2">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="C400" t="s" s="2">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="D400" s="2"/>
     </row>
@@ -8121,10 +8262,10 @@
         <v>70</v>
       </c>
       <c r="B401" t="s" s="2">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="C401" t="s" s="2">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="D401" s="2"/>
     </row>
@@ -8133,10 +8274,10 @@
         <v>70</v>
       </c>
       <c r="B402" t="s" s="2">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="C402" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="D402" s="2"/>
     </row>
@@ -8145,10 +8286,10 @@
         <v>70</v>
       </c>
       <c r="B403" t="s" s="2">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="C403" t="s" s="2">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="D403" s="2"/>
     </row>
@@ -8157,10 +8298,10 @@
         <v>70</v>
       </c>
       <c r="B404" t="s" s="2">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="C404" t="s" s="2">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="D404" s="2"/>
     </row>
@@ -8169,10 +8310,10 @@
         <v>70</v>
       </c>
       <c r="B405" t="s" s="2">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="C405" t="s" s="2">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="D405" s="2"/>
     </row>
@@ -8181,10 +8322,10 @@
         <v>70</v>
       </c>
       <c r="B406" t="s" s="2">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="C406" t="s" s="2">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="D406" s="2"/>
     </row>
@@ -8193,10 +8334,10 @@
         <v>70</v>
       </c>
       <c r="B407" t="s" s="2">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="C407" t="s" s="2">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="D407" s="2"/>
     </row>
@@ -8205,10 +8346,10 @@
         <v>70</v>
       </c>
       <c r="B408" t="s" s="2">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="C408" t="s" s="2">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="D408" s="2"/>
     </row>
@@ -8217,10 +8358,10 @@
         <v>70</v>
       </c>
       <c r="B409" t="s" s="2">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="C409" t="s" s="2">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="D409" s="2"/>
     </row>
@@ -8229,10 +8370,10 @@
         <v>70</v>
       </c>
       <c r="B410" t="s" s="2">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="C410" t="s" s="2">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="D410" s="2"/>
     </row>
@@ -8241,10 +8382,10 @@
         <v>70</v>
       </c>
       <c r="B411" t="s" s="2">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="C411" t="s" s="2">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="D411" s="2"/>
     </row>
@@ -8253,10 +8394,10 @@
         <v>70</v>
       </c>
       <c r="B412" t="s" s="2">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="C412" t="s" s="2">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="D412" s="2"/>
     </row>
@@ -8265,10 +8406,10 @@
         <v>70</v>
       </c>
       <c r="B413" t="s" s="2">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="C413" t="s" s="2">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="D413" s="2"/>
     </row>
@@ -8277,10 +8418,10 @@
         <v>70</v>
       </c>
       <c r="B414" t="s" s="2">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="C414" t="s" s="2">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="D414" s="2"/>
     </row>
@@ -8289,10 +8430,10 @@
         <v>70</v>
       </c>
       <c r="B415" t="s" s="2">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="C415" t="s" s="2">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="D415" s="2"/>
     </row>
@@ -8301,10 +8442,10 @@
         <v>70</v>
       </c>
       <c r="B416" t="s" s="2">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="C416" t="s" s="2">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="D416" s="2"/>
     </row>
@@ -8313,10 +8454,10 @@
         <v>70</v>
       </c>
       <c r="B417" t="s" s="2">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="C417" t="s" s="2">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="D417" s="2"/>
     </row>
@@ -8325,10 +8466,10 @@
         <v>70</v>
       </c>
       <c r="B418" t="s" s="2">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="C418" t="s" s="2">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="D418" s="2"/>
     </row>
@@ -8337,10 +8478,10 @@
         <v>70</v>
       </c>
       <c r="B419" t="s" s="2">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="C419" t="s" s="2">
-        <v>110</v>
+        <v>873</v>
       </c>
       <c r="D419" s="2"/>
     </row>
@@ -8349,10 +8490,10 @@
         <v>70</v>
       </c>
       <c r="B420" t="s" s="2">
-        <v>872</v>
+        <v>874</v>
       </c>
       <c r="C420" t="s" s="2">
-        <v>873</v>
+        <v>875</v>
       </c>
       <c r="D420" s="2"/>
     </row>
@@ -8361,10 +8502,10 @@
         <v>70</v>
       </c>
       <c r="B421" t="s" s="2">
-        <v>874</v>
+        <v>876</v>
       </c>
       <c r="C421" t="s" s="2">
-        <v>875</v>
+        <v>877</v>
       </c>
       <c r="D421" s="2"/>
     </row>
@@ -8373,10 +8514,10 @@
         <v>70</v>
       </c>
       <c r="B422" t="s" s="2">
-        <v>876</v>
+        <v>878</v>
       </c>
       <c r="C422" t="s" s="2">
-        <v>877</v>
+        <v>879</v>
       </c>
       <c r="D422" s="2"/>
     </row>
@@ -8385,10 +8526,10 @@
         <v>70</v>
       </c>
       <c r="B423" t="s" s="2">
-        <v>878</v>
+        <v>880</v>
       </c>
       <c r="C423" t="s" s="2">
-        <v>879</v>
+        <v>881</v>
       </c>
       <c r="D423" s="2"/>
     </row>
@@ -8397,10 +8538,10 @@
         <v>70</v>
       </c>
       <c r="B424" t="s" s="2">
-        <v>880</v>
+        <v>882</v>
       </c>
       <c r="C424" t="s" s="2">
-        <v>881</v>
+        <v>883</v>
       </c>
       <c r="D424" s="2"/>
     </row>
@@ -8409,10 +8550,10 @@
         <v>70</v>
       </c>
       <c r="B425" t="s" s="2">
-        <v>882</v>
+        <v>884</v>
       </c>
       <c r="C425" t="s" s="2">
-        <v>883</v>
+        <v>885</v>
       </c>
       <c r="D425" s="2"/>
     </row>
@@ -8421,10 +8562,10 @@
         <v>70</v>
       </c>
       <c r="B426" t="s" s="2">
-        <v>884</v>
+        <v>886</v>
       </c>
       <c r="C426" t="s" s="2">
-        <v>885</v>
+        <v>887</v>
       </c>
       <c r="D426" s="2"/>
     </row>
@@ -8433,10 +8574,10 @@
         <v>70</v>
       </c>
       <c r="B427" t="s" s="2">
-        <v>886</v>
+        <v>888</v>
       </c>
       <c r="C427" t="s" s="2">
-        <v>887</v>
+        <v>889</v>
       </c>
       <c r="D427" s="2"/>
     </row>
@@ -8445,10 +8586,10 @@
         <v>70</v>
       </c>
       <c r="B428" t="s" s="2">
-        <v>888</v>
+        <v>890</v>
       </c>
       <c r="C428" t="s" s="2">
-        <v>889</v>
+        <v>891</v>
       </c>
       <c r="D428" s="2"/>
     </row>
@@ -8457,10 +8598,10 @@
         <v>70</v>
       </c>
       <c r="B429" t="s" s="2">
-        <v>890</v>
+        <v>892</v>
       </c>
       <c r="C429" t="s" s="2">
-        <v>891</v>
+        <v>893</v>
       </c>
       <c r="D429" s="2"/>
     </row>
@@ -8469,10 +8610,10 @@
         <v>70</v>
       </c>
       <c r="B430" t="s" s="2">
-        <v>892</v>
+        <v>894</v>
       </c>
       <c r="C430" t="s" s="2">
-        <v>893</v>
+        <v>895</v>
       </c>
       <c r="D430" s="2"/>
     </row>
@@ -8481,10 +8622,10 @@
         <v>70</v>
       </c>
       <c r="B431" t="s" s="2">
-        <v>894</v>
+        <v>896</v>
       </c>
       <c r="C431" t="s" s="2">
-        <v>895</v>
+        <v>897</v>
       </c>
       <c r="D431" s="2"/>
     </row>
@@ -8493,10 +8634,10 @@
         <v>70</v>
       </c>
       <c r="B432" t="s" s="2">
-        <v>896</v>
+        <v>898</v>
       </c>
       <c r="C432" t="s" s="2">
-        <v>897</v>
+        <v>899</v>
       </c>
       <c r="D432" s="2"/>
     </row>
@@ -8505,10 +8646,10 @@
         <v>70</v>
       </c>
       <c r="B433" t="s" s="2">
-        <v>898</v>
+        <v>900</v>
       </c>
       <c r="C433" t="s" s="2">
-        <v>899</v>
+        <v>901</v>
       </c>
       <c r="D433" s="2"/>
     </row>
@@ -8517,10 +8658,10 @@
         <v>70</v>
       </c>
       <c r="B434" t="s" s="2">
-        <v>900</v>
+        <v>902</v>
       </c>
       <c r="C434" t="s" s="2">
-        <v>901</v>
+        <v>903</v>
       </c>
       <c r="D434" s="2"/>
     </row>
@@ -8529,10 +8670,10 @@
         <v>70</v>
       </c>
       <c r="B435" t="s" s="2">
-        <v>902</v>
+        <v>904</v>
       </c>
       <c r="C435" t="s" s="2">
-        <v>903</v>
+        <v>905</v>
       </c>
       <c r="D435" s="2"/>
     </row>
@@ -8541,10 +8682,10 @@
         <v>70</v>
       </c>
       <c r="B436" t="s" s="2">
-        <v>904</v>
+        <v>906</v>
       </c>
       <c r="C436" t="s" s="2">
-        <v>905</v>
+        <v>110</v>
       </c>
       <c r="D436" s="2"/>
     </row>
@@ -8553,10 +8694,10 @@
         <v>70</v>
       </c>
       <c r="B437" t="s" s="2">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="C437" t="s" s="2">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="D437" s="2"/>
     </row>
@@ -8565,10 +8706,10 @@
         <v>70</v>
       </c>
       <c r="B438" t="s" s="2">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="C438" t="s" s="2">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="D438" s="2"/>
     </row>
@@ -8577,10 +8718,10 @@
         <v>70</v>
       </c>
       <c r="B439" t="s" s="2">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="C439" t="s" s="2">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="D439" s="2"/>
     </row>
@@ -8589,10 +8730,10 @@
         <v>70</v>
       </c>
       <c r="B440" t="s" s="2">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="C440" t="s" s="2">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="D440" s="2"/>
     </row>
@@ -8601,10 +8742,10 @@
         <v>70</v>
       </c>
       <c r="B441" t="s" s="2">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="C441" t="s" s="2">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="D441" s="2"/>
     </row>
@@ -8613,10 +8754,10 @@
         <v>70</v>
       </c>
       <c r="B442" t="s" s="2">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="C442" t="s" s="2">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="D442" s="2"/>
     </row>
@@ -8625,10 +8766,10 @@
         <v>70</v>
       </c>
       <c r="B443" t="s" s="2">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="C443" t="s" s="2">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="D443" s="2"/>
     </row>
@@ -8637,10 +8778,10 @@
         <v>70</v>
       </c>
       <c r="B444" t="s" s="2">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="C444" t="s" s="2">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="D444" s="2"/>
     </row>
@@ -8649,10 +8790,10 @@
         <v>70</v>
       </c>
       <c r="B445" t="s" s="2">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="C445" t="s" s="2">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="D445" s="2"/>
     </row>
@@ -8661,10 +8802,10 @@
         <v>70</v>
       </c>
       <c r="B446" t="s" s="2">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="C446" t="s" s="2">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="D446" s="2"/>
     </row>
@@ -8673,10 +8814,10 @@
         <v>70</v>
       </c>
       <c r="B447" t="s" s="2">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="C447" t="s" s="2">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="D447" s="2"/>
     </row>
@@ -8685,10 +8826,10 @@
         <v>70</v>
       </c>
       <c r="B448" t="s" s="2">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="C448" t="s" s="2">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="D448" s="2"/>
     </row>
@@ -8697,10 +8838,10 @@
         <v>70</v>
       </c>
       <c r="B449" t="s" s="2">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="C449" t="s" s="2">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="D449" s="2"/>
     </row>
@@ -8709,10 +8850,10 @@
         <v>70</v>
       </c>
       <c r="B450" t="s" s="2">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="C450" t="s" s="2">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="D450" s="2"/>
     </row>
@@ -8721,10 +8862,10 @@
         <v>70</v>
       </c>
       <c r="B451" t="s" s="2">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="C451" t="s" s="2">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="D451" s="2"/>
     </row>
@@ -8733,10 +8874,10 @@
         <v>70</v>
       </c>
       <c r="B452" t="s" s="2">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="C452" t="s" s="2">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="D452" s="2"/>
     </row>
@@ -8745,10 +8886,10 @@
         <v>70</v>
       </c>
       <c r="B453" t="s" s="2">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="C453" t="s" s="2">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="D453" s="2"/>
     </row>
@@ -8757,10 +8898,10 @@
         <v>70</v>
       </c>
       <c r="B454" t="s" s="2">
-        <v>940</v>
+        <v>941</v>
       </c>
       <c r="C454" t="s" s="2">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="D454" s="2"/>
     </row>
@@ -8769,10 +8910,10 @@
         <v>70</v>
       </c>
       <c r="B455" t="s" s="2">
-        <v>942</v>
+        <v>943</v>
       </c>
       <c r="C455" t="s" s="2">
-        <v>943</v>
+        <v>944</v>
       </c>
       <c r="D455" s="2"/>
     </row>
@@ -8781,10 +8922,10 @@
         <v>70</v>
       </c>
       <c r="B456" t="s" s="2">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="C456" t="s" s="2">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="D456" s="2"/>
     </row>
@@ -8793,10 +8934,10 @@
         <v>70</v>
       </c>
       <c r="B457" t="s" s="2">
-        <v>946</v>
+        <v>947</v>
       </c>
       <c r="C457" t="s" s="2">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="D457" s="2"/>
     </row>
@@ -8805,12 +8946,272 @@
         <v>70</v>
       </c>
       <c r="B458" t="s" s="2">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="C458" t="s" s="2">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="D458" s="2"/>
+    </row>
+    <row r="459">
+      <c r="A459" t="s" s="2">
+        <v>70</v>
+      </c>
+      <c r="B459" t="s" s="2">
+        <v>951</v>
+      </c>
+      <c r="C459" t="s" s="2">
+        <v>952</v>
+      </c>
+      <c r="D459" s="2"/>
+    </row>
+    <row r="460">
+      <c r="A460" t="s" s="2">
+        <v>70</v>
+      </c>
+      <c r="B460" t="s" s="2">
+        <v>953</v>
+      </c>
+      <c r="C460" t="s" s="2">
+        <v>954</v>
+      </c>
+      <c r="D460" s="2"/>
+    </row>
+    <row r="461">
+      <c r="A461" t="s" s="2">
+        <v>70</v>
+      </c>
+      <c r="B461" t="s" s="2">
+        <v>955</v>
+      </c>
+      <c r="C461" t="s" s="2">
+        <v>956</v>
+      </c>
+      <c r="D461" s="2"/>
+    </row>
+    <row r="462">
+      <c r="A462" t="s" s="2">
+        <v>70</v>
+      </c>
+      <c r="B462" t="s" s="2">
+        <v>957</v>
+      </c>
+      <c r="C462" t="s" s="2">
+        <v>958</v>
+      </c>
+      <c r="D462" s="2"/>
+    </row>
+    <row r="463">
+      <c r="A463" t="s" s="2">
+        <v>70</v>
+      </c>
+      <c r="B463" t="s" s="2">
+        <v>959</v>
+      </c>
+      <c r="C463" t="s" s="2">
+        <v>960</v>
+      </c>
+      <c r="D463" s="2"/>
+    </row>
+    <row r="464">
+      <c r="A464" t="s" s="2">
+        <v>70</v>
+      </c>
+      <c r="B464" t="s" s="2">
+        <v>961</v>
+      </c>
+      <c r="C464" t="s" s="2">
+        <v>962</v>
+      </c>
+      <c r="D464" s="2"/>
+    </row>
+    <row r="465">
+      <c r="A465" t="s" s="2">
+        <v>70</v>
+      </c>
+      <c r="B465" t="s" s="2">
+        <v>963</v>
+      </c>
+      <c r="C465" t="s" s="2">
+        <v>964</v>
+      </c>
+      <c r="D465" s="2"/>
+    </row>
+    <row r="466">
+      <c r="A466" t="s" s="2">
+        <v>70</v>
+      </c>
+      <c r="B466" t="s" s="2">
+        <v>965</v>
+      </c>
+      <c r="C466" t="s" s="2">
+        <v>966</v>
+      </c>
+      <c r="D466" s="2"/>
+    </row>
+    <row r="467">
+      <c r="A467" t="s" s="2">
+        <v>70</v>
+      </c>
+      <c r="B467" t="s" s="2">
+        <v>967</v>
+      </c>
+      <c r="C467" t="s" s="2">
+        <v>968</v>
+      </c>
+      <c r="D467" s="2"/>
+    </row>
+    <row r="468">
+      <c r="A468" t="s" s="2">
+        <v>70</v>
+      </c>
+      <c r="B468" t="s" s="2">
+        <v>969</v>
+      </c>
+      <c r="C468" t="s" s="2">
+        <v>970</v>
+      </c>
+      <c r="D468" t="s" s="2">
+        <v>971</v>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="s" s="2">
+        <v>70</v>
+      </c>
+      <c r="B469" t="s" s="2">
+        <v>972</v>
+      </c>
+      <c r="C469" t="s" s="2">
+        <v>973</v>
+      </c>
+      <c r="D469" t="s" s="2">
+        <v>974</v>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" t="s" s="2">
+        <v>70</v>
+      </c>
+      <c r="B470" t="s" s="2">
+        <v>975</v>
+      </c>
+      <c r="C470" t="s" s="2">
+        <v>976</v>
+      </c>
+      <c r="D470" t="s" s="2">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" t="s" s="2">
+        <v>70</v>
+      </c>
+      <c r="B471" t="s" s="2">
+        <v>978</v>
+      </c>
+      <c r="C471" t="s" s="2">
+        <v>979</v>
+      </c>
+      <c r="D471" t="s" s="2">
+        <v>980</v>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" t="s" s="2">
+        <v>70</v>
+      </c>
+      <c r="B472" t="s" s="2">
+        <v>981</v>
+      </c>
+      <c r="C472" t="s" s="2">
+        <v>982</v>
+      </c>
+      <c r="D472" s="2"/>
+    </row>
+    <row r="473">
+      <c r="A473" t="s" s="2">
+        <v>70</v>
+      </c>
+      <c r="B473" t="s" s="2">
+        <v>983</v>
+      </c>
+      <c r="C473" t="s" s="2">
+        <v>984</v>
+      </c>
+      <c r="D473" s="2"/>
+    </row>
+    <row r="474">
+      <c r="A474" t="s" s="2">
+        <v>70</v>
+      </c>
+      <c r="B474" t="s" s="2">
+        <v>985</v>
+      </c>
+      <c r="C474" t="s" s="2">
+        <v>986</v>
+      </c>
+      <c r="D474" s="2"/>
+    </row>
+    <row r="475">
+      <c r="A475" t="s" s="2">
+        <v>70</v>
+      </c>
+      <c r="B475" t="s" s="2">
+        <v>987</v>
+      </c>
+      <c r="C475" t="s" s="2">
+        <v>988</v>
+      </c>
+      <c r="D475" s="2"/>
+    </row>
+    <row r="476">
+      <c r="A476" t="s" s="2">
+        <v>70</v>
+      </c>
+      <c r="B476" t="s" s="2">
+        <v>989</v>
+      </c>
+      <c r="C476" t="s" s="2">
+        <v>990</v>
+      </c>
+      <c r="D476" s="2"/>
+    </row>
+    <row r="477">
+      <c r="A477" t="s" s="2">
+        <v>70</v>
+      </c>
+      <c r="B477" t="s" s="2">
+        <v>991</v>
+      </c>
+      <c r="C477" t="s" s="2">
+        <v>992</v>
+      </c>
+      <c r="D477" s="2"/>
+    </row>
+    <row r="478">
+      <c r="A478" t="s" s="2">
+        <v>70</v>
+      </c>
+      <c r="B478" t="s" s="2">
+        <v>993</v>
+      </c>
+      <c r="C478" t="s" s="2">
+        <v>994</v>
+      </c>
+      <c r="D478" s="2"/>
+    </row>
+    <row r="479">
+      <c r="A479" t="s" s="2">
+        <v>70</v>
+      </c>
+      <c r="B479" t="s" s="2">
+        <v>995</v>
+      </c>
+      <c r="C479" t="s" s="2">
+        <v>996</v>
+      </c>
+      <c r="D479" s="2"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>

--- a/www/terminologies/CodeSystem-tre-r347-activite-sanitaire-diverse-regulee.xlsx
+++ b/www/terminologies/CodeSystem-tre-r347-activite-sanitaire-diverse-regulee.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1516" uniqueCount="997">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1449" uniqueCount="950">
   <si>
     <t>Property</t>
   </si>
@@ -37,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260629120000</t>
+    <t>20260505120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -67,7 +67,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T12:00:00.000+00:00</t>
+    <t>2026-05-05T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -124,7 +124,7 @@
     <t>Count</t>
   </si>
   <si>
-    <t>478</t>
+    <t>457</t>
   </si>
   <si>
     <t>Code</t>
@@ -625,7 +625,7 @@
     <t>0371</t>
   </si>
   <si>
-    <t>structures de psychiatrie ambulatoire</t>
+    <t>structures de psychiatrie sans hébergement</t>
   </si>
   <si>
     <t>0372</t>
@@ -700,108 +700,6 @@
     <t>0821</t>
   </si>
   <si>
-    <t>861</t>
-  </si>
-  <si>
-    <t>Accueil familial thérapeutique</t>
-  </si>
-  <si>
-    <t>862</t>
-  </si>
-  <si>
-    <t>Appartement thérapeutique</t>
-  </si>
-  <si>
-    <t>863</t>
-  </si>
-  <si>
-    <t>Accueil permanent</t>
-  </si>
-  <si>
-    <t>864</t>
-  </si>
-  <si>
-    <t>Centre d'activités thérapeutiques et de temps de groupe</t>
-  </si>
-  <si>
-    <t>865</t>
-  </si>
-  <si>
-    <t>Centre de crise</t>
-  </si>
-  <si>
-    <t>866</t>
-  </si>
-  <si>
-    <t>Centre de soins post-aigus</t>
-  </si>
-  <si>
-    <t>867</t>
-  </si>
-  <si>
-    <t>Centre médico-psychologique</t>
-  </si>
-  <si>
-    <t>868</t>
-  </si>
-  <si>
-    <t>Hôpital de jour</t>
-  </si>
-  <si>
-    <t>869</t>
-  </si>
-  <si>
-    <t>Service médico-psychologique régional</t>
-  </si>
-  <si>
-    <t>870</t>
-  </si>
-  <si>
-    <t>Soins à domicile</t>
-  </si>
-  <si>
-    <t>871</t>
-  </si>
-  <si>
-    <t>Unité hospitalière spécialement aménagée</t>
-  </si>
-  <si>
-    <t>872</t>
-  </si>
-  <si>
-    <t>Unité pour malades difficiles</t>
-  </si>
-  <si>
-    <t>873</t>
-  </si>
-  <si>
-    <t>Unité sanitaire en milieu pénitentiaire</t>
-  </si>
-  <si>
-    <t>874</t>
-  </si>
-  <si>
-    <t>Hôpital de nuit</t>
-  </si>
-  <si>
-    <t>875</t>
-  </si>
-  <si>
-    <t>Centre de consultations</t>
-  </si>
-  <si>
-    <t>876</t>
-  </si>
-  <si>
-    <t>Unité d’hospitalisation complète</t>
-  </si>
-  <si>
-    <t>877</t>
-  </si>
-  <si>
-    <t>Centre d'accueil et de crise</t>
-  </si>
-  <si>
     <t>023</t>
   </si>
   <si>
@@ -2080,9 +1978,6 @@
     <t>Aide Aux Insuffisants Respiratoires</t>
   </si>
   <si>
-    <t>457</t>
-  </si>
-  <si>
     <t>Cure Médic.Spécialisée Contre Tuberculose Indifférenciée</t>
   </si>
   <si>
@@ -2921,42 +2816,6 @@
   </si>
   <si>
     <t>Activité sage-femme en maison de naissance</t>
-  </si>
-  <si>
-    <t>855</t>
-  </si>
-  <si>
-    <t>Maison médicale de garde</t>
-  </si>
-  <si>
-    <t>Activités contribuant à la permanence des Soins Ambulatoires (PDSA) exercées dans le cadre d'une Maison Médicale de Garde</t>
-  </si>
-  <si>
-    <t>856</t>
-  </si>
-  <si>
-    <t>Point fixe de garde</t>
-  </si>
-  <si>
-    <t>Activités contribuant à la permanence des Soins Ambulatoires (PDSA) exercées dans le cadre d'un Point fixe de garde</t>
-  </si>
-  <si>
-    <t>857</t>
-  </si>
-  <si>
-    <t>Point fixe de consultation</t>
-  </si>
-  <si>
-    <t>Activités contribuant à la permanence des Soins Ambulatoires (PDSA) exercées dans le cadre d'un Point fixe de consultation</t>
-  </si>
-  <si>
-    <t>858</t>
-  </si>
-  <si>
-    <t>Visite à domicile</t>
-  </si>
-  <si>
-    <t>Activités contribuant à la permanence des Soins Ambulatoires (PDSA) exercées dans le cadre de visites à domicile</t>
   </si>
   <si>
     <t>949</t>
@@ -3452,7 +3311,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D479"/>
+  <dimension ref="A1:D458"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -5397,7 +5256,7 @@
         <v>364</v>
       </c>
       <c r="C162" t="s" s="2">
-        <v>365</v>
+        <v>159</v>
       </c>
       <c r="D162" s="2"/>
     </row>
@@ -5406,10 +5265,10 @@
         <v>70</v>
       </c>
       <c r="B163" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="C163" t="s" s="2">
         <v>366</v>
-      </c>
-      <c r="C163" t="s" s="2">
-        <v>367</v>
       </c>
       <c r="D163" s="2"/>
     </row>
@@ -5418,10 +5277,10 @@
         <v>70</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C164" t="s" s="2">
-        <v>369</v>
+        <v>153</v>
       </c>
       <c r="D164" s="2"/>
     </row>
@@ -5430,10 +5289,10 @@
         <v>70</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="C165" t="s" s="2">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="D165" s="2"/>
     </row>
@@ -5442,10 +5301,10 @@
         <v>70</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="C166" t="s" s="2">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="D166" s="2"/>
     </row>
@@ -5454,10 +5313,10 @@
         <v>70</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="C167" t="s" s="2">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="D167" s="2"/>
     </row>
@@ -5466,10 +5325,10 @@
         <v>70</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="C168" t="s" s="2">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="D168" s="2"/>
     </row>
@@ -5478,10 +5337,10 @@
         <v>70</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="C169" t="s" s="2">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="D169" s="2"/>
     </row>
@@ -5490,10 +5349,10 @@
         <v>70</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="C170" t="s" s="2">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="D170" s="2"/>
     </row>
@@ -5502,10 +5361,10 @@
         <v>70</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="C171" t="s" s="2">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="D171" s="2"/>
     </row>
@@ -5514,10 +5373,10 @@
         <v>70</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="C172" t="s" s="2">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="D172" s="2"/>
     </row>
@@ -5526,10 +5385,10 @@
         <v>70</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="C173" t="s" s="2">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="D173" s="2"/>
     </row>
@@ -5538,10 +5397,10 @@
         <v>70</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="C174" t="s" s="2">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="D174" s="2"/>
     </row>
@@ -5550,10 +5409,10 @@
         <v>70</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="C175" t="s" s="2">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="D175" s="2"/>
     </row>
@@ -5562,10 +5421,10 @@
         <v>70</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="C176" t="s" s="2">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="D176" s="2"/>
     </row>
@@ -5574,10 +5433,10 @@
         <v>70</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="C177" t="s" s="2">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="D177" s="2"/>
     </row>
@@ -5586,10 +5445,10 @@
         <v>70</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="C178" t="s" s="2">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="D178" s="2"/>
     </row>
@@ -5598,10 +5457,10 @@
         <v>70</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="C179" t="s" s="2">
-        <v>159</v>
+        <v>397</v>
       </c>
       <c r="D179" s="2"/>
     </row>
@@ -5610,10 +5469,10 @@
         <v>70</v>
       </c>
       <c r="B180" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="C180" t="s" s="2">
         <v>399</v>
-      </c>
-      <c r="C180" t="s" s="2">
-        <v>400</v>
       </c>
       <c r="D180" s="2"/>
     </row>
@@ -5622,10 +5481,10 @@
         <v>70</v>
       </c>
       <c r="B181" t="s" s="2">
+        <v>400</v>
+      </c>
+      <c r="C181" t="s" s="2">
         <v>401</v>
-      </c>
-      <c r="C181" t="s" s="2">
-        <v>153</v>
       </c>
       <c r="D181" s="2"/>
     </row>
@@ -5649,7 +5508,7 @@
         <v>404</v>
       </c>
       <c r="C183" t="s" s="2">
-        <v>405</v>
+        <v>161</v>
       </c>
       <c r="D183" s="2"/>
     </row>
@@ -5658,10 +5517,10 @@
         <v>70</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C184" t="s" s="2">
-        <v>407</v>
+        <v>163</v>
       </c>
       <c r="D184" s="2"/>
     </row>
@@ -5670,10 +5529,10 @@
         <v>70</v>
       </c>
       <c r="B185" t="s" s="2">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="C185" t="s" s="2">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="D185" s="2"/>
     </row>
@@ -5682,10 +5541,10 @@
         <v>70</v>
       </c>
       <c r="B186" t="s" s="2">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="C186" t="s" s="2">
-        <v>411</v>
+        <v>169</v>
       </c>
       <c r="D186" s="2"/>
     </row>
@@ -5694,10 +5553,10 @@
         <v>70</v>
       </c>
       <c r="B187" t="s" s="2">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="C187" t="s" s="2">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="D187" s="2"/>
     </row>
@@ -5706,10 +5565,10 @@
         <v>70</v>
       </c>
       <c r="B188" t="s" s="2">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="C188" t="s" s="2">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="D188" s="2"/>
     </row>
@@ -5718,10 +5577,10 @@
         <v>70</v>
       </c>
       <c r="B189" t="s" s="2">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="C189" t="s" s="2">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="D189" s="2"/>
     </row>
@@ -5730,10 +5589,10 @@
         <v>70</v>
       </c>
       <c r="B190" t="s" s="2">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="C190" t="s" s="2">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="D190" s="2"/>
     </row>
@@ -5742,10 +5601,10 @@
         <v>70</v>
       </c>
       <c r="B191" t="s" s="2">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="C191" t="s" s="2">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="D191" s="2"/>
     </row>
@@ -5754,10 +5613,10 @@
         <v>70</v>
       </c>
       <c r="B192" t="s" s="2">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="C192" t="s" s="2">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="D192" s="2"/>
     </row>
@@ -5766,10 +5625,10 @@
         <v>70</v>
       </c>
       <c r="B193" t="s" s="2">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="C193" t="s" s="2">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="D193" s="2"/>
     </row>
@@ -5778,10 +5637,10 @@
         <v>70</v>
       </c>
       <c r="B194" t="s" s="2">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="C194" t="s" s="2">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="D194" s="2"/>
     </row>
@@ -5790,10 +5649,10 @@
         <v>70</v>
       </c>
       <c r="B195" t="s" s="2">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="C195" t="s" s="2">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="D195" s="2"/>
     </row>
@@ -5802,10 +5661,10 @@
         <v>70</v>
       </c>
       <c r="B196" t="s" s="2">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="C196" t="s" s="2">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="D196" s="2"/>
     </row>
@@ -5814,10 +5673,10 @@
         <v>70</v>
       </c>
       <c r="B197" t="s" s="2">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="C197" t="s" s="2">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="D197" s="2"/>
     </row>
@@ -5826,10 +5685,10 @@
         <v>70</v>
       </c>
       <c r="B198" t="s" s="2">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="C198" t="s" s="2">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="D198" s="2"/>
     </row>
@@ -5838,10 +5697,10 @@
         <v>70</v>
       </c>
       <c r="B199" t="s" s="2">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="C199" t="s" s="2">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="D199" s="2"/>
     </row>
@@ -5850,10 +5709,10 @@
         <v>70</v>
       </c>
       <c r="B200" t="s" s="2">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="C200" t="s" s="2">
-        <v>161</v>
+        <v>436</v>
       </c>
       <c r="D200" s="2"/>
     </row>
@@ -5862,10 +5721,10 @@
         <v>70</v>
       </c>
       <c r="B201" t="s" s="2">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="C201" t="s" s="2">
-        <v>163</v>
+        <v>438</v>
       </c>
       <c r="D201" s="2"/>
     </row>
@@ -5874,10 +5733,10 @@
         <v>70</v>
       </c>
       <c r="B202" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="C202" t="s" s="2">
         <v>440</v>
-      </c>
-      <c r="C202" t="s" s="2">
-        <v>441</v>
       </c>
       <c r="D202" s="2"/>
     </row>
@@ -5886,10 +5745,10 @@
         <v>70</v>
       </c>
       <c r="B203" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="C203" t="s" s="2">
         <v>442</v>
-      </c>
-      <c r="C203" t="s" s="2">
-        <v>169</v>
       </c>
       <c r="D203" s="2"/>
     </row>
@@ -5949,7 +5808,7 @@
         <v>451</v>
       </c>
       <c r="C208" t="s" s="2">
-        <v>452</v>
+        <v>88</v>
       </c>
       <c r="D208" s="2"/>
     </row>
@@ -5958,10 +5817,10 @@
         <v>70</v>
       </c>
       <c r="B209" t="s" s="2">
+        <v>452</v>
+      </c>
+      <c r="C209" t="s" s="2">
         <v>453</v>
-      </c>
-      <c r="C209" t="s" s="2">
-        <v>454</v>
       </c>
       <c r="D209" s="2"/>
     </row>
@@ -5970,10 +5829,10 @@
         <v>70</v>
       </c>
       <c r="B210" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="C210" t="s" s="2">
         <v>455</v>
-      </c>
-      <c r="C210" t="s" s="2">
-        <v>456</v>
       </c>
       <c r="D210" s="2"/>
     </row>
@@ -5982,10 +5841,10 @@
         <v>70</v>
       </c>
       <c r="B211" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="C211" t="s" s="2">
         <v>457</v>
-      </c>
-      <c r="C211" t="s" s="2">
-        <v>458</v>
       </c>
       <c r="D211" s="2"/>
     </row>
@@ -5994,10 +5853,10 @@
         <v>70</v>
       </c>
       <c r="B212" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="C212" t="s" s="2">
         <v>459</v>
-      </c>
-      <c r="C212" t="s" s="2">
-        <v>460</v>
       </c>
       <c r="D212" s="2"/>
     </row>
@@ -6006,10 +5865,10 @@
         <v>70</v>
       </c>
       <c r="B213" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="C213" t="s" s="2">
         <v>461</v>
-      </c>
-      <c r="C213" t="s" s="2">
-        <v>462</v>
       </c>
       <c r="D213" s="2"/>
     </row>
@@ -6018,10 +5877,10 @@
         <v>70</v>
       </c>
       <c r="B214" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="C214" t="s" s="2">
         <v>463</v>
-      </c>
-      <c r="C214" t="s" s="2">
-        <v>464</v>
       </c>
       <c r="D214" s="2"/>
     </row>
@@ -6030,10 +5889,10 @@
         <v>70</v>
       </c>
       <c r="B215" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="C215" t="s" s="2">
         <v>465</v>
-      </c>
-      <c r="C215" t="s" s="2">
-        <v>466</v>
       </c>
       <c r="D215" s="2"/>
     </row>
@@ -6042,10 +5901,10 @@
         <v>70</v>
       </c>
       <c r="B216" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="C216" t="s" s="2">
         <v>467</v>
-      </c>
-      <c r="C216" t="s" s="2">
-        <v>468</v>
       </c>
       <c r="D216" s="2"/>
     </row>
@@ -6054,10 +5913,10 @@
         <v>70</v>
       </c>
       <c r="B217" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="C217" t="s" s="2">
         <v>469</v>
-      </c>
-      <c r="C217" t="s" s="2">
-        <v>470</v>
       </c>
       <c r="D217" s="2"/>
     </row>
@@ -6066,10 +5925,10 @@
         <v>70</v>
       </c>
       <c r="B218" t="s" s="2">
+        <v>470</v>
+      </c>
+      <c r="C218" t="s" s="2">
         <v>471</v>
-      </c>
-      <c r="C218" t="s" s="2">
-        <v>472</v>
       </c>
       <c r="D218" s="2"/>
     </row>
@@ -6078,10 +5937,10 @@
         <v>70</v>
       </c>
       <c r="B219" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="C219" t="s" s="2">
         <v>473</v>
-      </c>
-      <c r="C219" t="s" s="2">
-        <v>474</v>
       </c>
       <c r="D219" s="2"/>
     </row>
@@ -6090,10 +5949,10 @@
         <v>70</v>
       </c>
       <c r="B220" t="s" s="2">
+        <v>474</v>
+      </c>
+      <c r="C220" t="s" s="2">
         <v>475</v>
-      </c>
-      <c r="C220" t="s" s="2">
-        <v>476</v>
       </c>
       <c r="D220" s="2"/>
     </row>
@@ -6102,10 +5961,10 @@
         <v>70</v>
       </c>
       <c r="B221" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="C221" t="s" s="2">
         <v>477</v>
-      </c>
-      <c r="C221" t="s" s="2">
-        <v>478</v>
       </c>
       <c r="D221" s="2"/>
     </row>
@@ -6114,10 +5973,10 @@
         <v>70</v>
       </c>
       <c r="B222" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="C222" t="s" s="2">
         <v>479</v>
-      </c>
-      <c r="C222" t="s" s="2">
-        <v>480</v>
       </c>
       <c r="D222" s="2"/>
     </row>
@@ -6126,10 +5985,10 @@
         <v>70</v>
       </c>
       <c r="B223" t="s" s="2">
+        <v>480</v>
+      </c>
+      <c r="C223" t="s" s="2">
         <v>481</v>
-      </c>
-      <c r="C223" t="s" s="2">
-        <v>482</v>
       </c>
       <c r="D223" s="2"/>
     </row>
@@ -6138,10 +5997,10 @@
         <v>70</v>
       </c>
       <c r="B224" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="C224" t="s" s="2">
         <v>483</v>
-      </c>
-      <c r="C224" t="s" s="2">
-        <v>484</v>
       </c>
       <c r="D224" s="2"/>
     </row>
@@ -6150,10 +6009,10 @@
         <v>70</v>
       </c>
       <c r="B225" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="C225" t="s" s="2">
         <v>485</v>
-      </c>
-      <c r="C225" t="s" s="2">
-        <v>88</v>
       </c>
       <c r="D225" s="2"/>
     </row>
@@ -7170,10 +7029,10 @@
         <v>70</v>
       </c>
       <c r="B310" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="C310" t="s" s="2">
         <v>654</v>
-      </c>
-      <c r="C310" t="s" s="2">
-        <v>655</v>
       </c>
       <c r="D310" s="2"/>
     </row>
@@ -7182,10 +7041,10 @@
         <v>70</v>
       </c>
       <c r="B311" t="s" s="2">
+        <v>655</v>
+      </c>
+      <c r="C311" t="s" s="2">
         <v>656</v>
-      </c>
-      <c r="C311" t="s" s="2">
-        <v>657</v>
       </c>
       <c r="D311" s="2"/>
     </row>
@@ -7194,10 +7053,10 @@
         <v>70</v>
       </c>
       <c r="B312" t="s" s="2">
+        <v>657</v>
+      </c>
+      <c r="C312" t="s" s="2">
         <v>658</v>
-      </c>
-      <c r="C312" t="s" s="2">
-        <v>659</v>
       </c>
       <c r="D312" s="2"/>
     </row>
@@ -7206,10 +7065,10 @@
         <v>70</v>
       </c>
       <c r="B313" t="s" s="2">
+        <v>659</v>
+      </c>
+      <c r="C313" t="s" s="2">
         <v>660</v>
-      </c>
-      <c r="C313" t="s" s="2">
-        <v>661</v>
       </c>
       <c r="D313" s="2"/>
     </row>
@@ -7218,10 +7077,10 @@
         <v>70</v>
       </c>
       <c r="B314" t="s" s="2">
+        <v>661</v>
+      </c>
+      <c r="C314" t="s" s="2">
         <v>662</v>
-      </c>
-      <c r="C314" t="s" s="2">
-        <v>663</v>
       </c>
       <c r="D314" s="2"/>
     </row>
@@ -7230,10 +7089,10 @@
         <v>70</v>
       </c>
       <c r="B315" t="s" s="2">
+        <v>663</v>
+      </c>
+      <c r="C315" t="s" s="2">
         <v>664</v>
-      </c>
-      <c r="C315" t="s" s="2">
-        <v>665</v>
       </c>
       <c r="D315" s="2"/>
     </row>
@@ -7242,10 +7101,10 @@
         <v>70</v>
       </c>
       <c r="B316" t="s" s="2">
+        <v>665</v>
+      </c>
+      <c r="C316" t="s" s="2">
         <v>666</v>
-      </c>
-      <c r="C316" t="s" s="2">
-        <v>667</v>
       </c>
       <c r="D316" s="2"/>
     </row>
@@ -7254,10 +7113,10 @@
         <v>70</v>
       </c>
       <c r="B317" t="s" s="2">
+        <v>667</v>
+      </c>
+      <c r="C317" t="s" s="2">
         <v>668</v>
-      </c>
-      <c r="C317" t="s" s="2">
-        <v>669</v>
       </c>
       <c r="D317" s="2"/>
     </row>
@@ -7266,10 +7125,10 @@
         <v>70</v>
       </c>
       <c r="B318" t="s" s="2">
+        <v>669</v>
+      </c>
+      <c r="C318" t="s" s="2">
         <v>670</v>
-      </c>
-      <c r="C318" t="s" s="2">
-        <v>671</v>
       </c>
       <c r="D318" s="2"/>
     </row>
@@ -7278,10 +7137,10 @@
         <v>70</v>
       </c>
       <c r="B319" t="s" s="2">
+        <v>671</v>
+      </c>
+      <c r="C319" t="s" s="2">
         <v>672</v>
-      </c>
-      <c r="C319" t="s" s="2">
-        <v>673</v>
       </c>
       <c r="D319" s="2"/>
     </row>
@@ -7290,10 +7149,10 @@
         <v>70</v>
       </c>
       <c r="B320" t="s" s="2">
+        <v>673</v>
+      </c>
+      <c r="C320" t="s" s="2">
         <v>674</v>
-      </c>
-      <c r="C320" t="s" s="2">
-        <v>675</v>
       </c>
       <c r="D320" s="2"/>
     </row>
@@ -7302,10 +7161,10 @@
         <v>70</v>
       </c>
       <c r="B321" t="s" s="2">
+        <v>675</v>
+      </c>
+      <c r="C321" t="s" s="2">
         <v>676</v>
-      </c>
-      <c r="C321" t="s" s="2">
-        <v>677</v>
       </c>
       <c r="D321" s="2"/>
     </row>
@@ -7314,10 +7173,10 @@
         <v>70</v>
       </c>
       <c r="B322" t="s" s="2">
+        <v>677</v>
+      </c>
+      <c r="C322" t="s" s="2">
         <v>678</v>
-      </c>
-      <c r="C322" t="s" s="2">
-        <v>679</v>
       </c>
       <c r="D322" s="2"/>
     </row>
@@ -7326,10 +7185,10 @@
         <v>70</v>
       </c>
       <c r="B323" t="s" s="2">
+        <v>679</v>
+      </c>
+      <c r="C323" t="s" s="2">
         <v>680</v>
-      </c>
-      <c r="C323" t="s" s="2">
-        <v>681</v>
       </c>
       <c r="D323" s="2"/>
     </row>
@@ -7338,10 +7197,10 @@
         <v>70</v>
       </c>
       <c r="B324" t="s" s="2">
+        <v>681</v>
+      </c>
+      <c r="C324" t="s" s="2">
         <v>682</v>
-      </c>
-      <c r="C324" t="s" s="2">
-        <v>683</v>
       </c>
       <c r="D324" s="2"/>
     </row>
@@ -7350,10 +7209,10 @@
         <v>70</v>
       </c>
       <c r="B325" t="s" s="2">
+        <v>683</v>
+      </c>
+      <c r="C325" t="s" s="2">
         <v>684</v>
-      </c>
-      <c r="C325" t="s" s="2">
-        <v>685</v>
       </c>
       <c r="D325" s="2"/>
     </row>
@@ -7362,10 +7221,10 @@
         <v>70</v>
       </c>
       <c r="B326" t="s" s="2">
+        <v>685</v>
+      </c>
+      <c r="C326" t="s" s="2">
         <v>686</v>
-      </c>
-      <c r="C326" t="s" s="2">
-        <v>687</v>
       </c>
       <c r="D326" s="2"/>
     </row>
@@ -7374,10 +7233,10 @@
         <v>70</v>
       </c>
       <c r="B327" t="s" s="2">
+        <v>687</v>
+      </c>
+      <c r="C327" t="s" s="2">
         <v>688</v>
-      </c>
-      <c r="C327" t="s" s="2">
-        <v>689</v>
       </c>
       <c r="D327" s="2"/>
     </row>
@@ -7386,10 +7245,10 @@
         <v>70</v>
       </c>
       <c r="B328" t="s" s="2">
+        <v>689</v>
+      </c>
+      <c r="C328" t="s" s="2">
         <v>690</v>
-      </c>
-      <c r="C328" t="s" s="2">
-        <v>691</v>
       </c>
       <c r="D328" s="2"/>
     </row>
@@ -7398,10 +7257,10 @@
         <v>70</v>
       </c>
       <c r="B329" t="s" s="2">
+        <v>691</v>
+      </c>
+      <c r="C329" t="s" s="2">
         <v>692</v>
-      </c>
-      <c r="C329" t="s" s="2">
-        <v>693</v>
       </c>
       <c r="D329" s="2"/>
     </row>
@@ -7410,10 +7269,10 @@
         <v>70</v>
       </c>
       <c r="B330" t="s" s="2">
+        <v>693</v>
+      </c>
+      <c r="C330" t="s" s="2">
         <v>694</v>
-      </c>
-      <c r="C330" t="s" s="2">
-        <v>695</v>
       </c>
       <c r="D330" s="2"/>
     </row>
@@ -7422,10 +7281,10 @@
         <v>70</v>
       </c>
       <c r="B331" t="s" s="2">
+        <v>695</v>
+      </c>
+      <c r="C331" t="s" s="2">
         <v>696</v>
-      </c>
-      <c r="C331" t="s" s="2">
-        <v>697</v>
       </c>
       <c r="D331" s="2"/>
     </row>
@@ -7434,10 +7293,10 @@
         <v>70</v>
       </c>
       <c r="B332" t="s" s="2">
+        <v>697</v>
+      </c>
+      <c r="C332" t="s" s="2">
         <v>698</v>
-      </c>
-      <c r="C332" t="s" s="2">
-        <v>699</v>
       </c>
       <c r="D332" s="2"/>
     </row>
@@ -7446,10 +7305,10 @@
         <v>70</v>
       </c>
       <c r="B333" t="s" s="2">
+        <v>699</v>
+      </c>
+      <c r="C333" t="s" s="2">
         <v>700</v>
-      </c>
-      <c r="C333" t="s" s="2">
-        <v>701</v>
       </c>
       <c r="D333" s="2"/>
     </row>
@@ -7458,10 +7317,10 @@
         <v>70</v>
       </c>
       <c r="B334" t="s" s="2">
+        <v>701</v>
+      </c>
+      <c r="C334" t="s" s="2">
         <v>702</v>
-      </c>
-      <c r="C334" t="s" s="2">
-        <v>703</v>
       </c>
       <c r="D334" s="2"/>
     </row>
@@ -7470,10 +7329,10 @@
         <v>70</v>
       </c>
       <c r="B335" t="s" s="2">
+        <v>703</v>
+      </c>
+      <c r="C335" t="s" s="2">
         <v>704</v>
-      </c>
-      <c r="C335" t="s" s="2">
-        <v>705</v>
       </c>
       <c r="D335" s="2"/>
     </row>
@@ -7482,10 +7341,10 @@
         <v>70</v>
       </c>
       <c r="B336" t="s" s="2">
+        <v>705</v>
+      </c>
+      <c r="C336" t="s" s="2">
         <v>706</v>
-      </c>
-      <c r="C336" t="s" s="2">
-        <v>707</v>
       </c>
       <c r="D336" s="2"/>
     </row>
@@ -7494,10 +7353,10 @@
         <v>70</v>
       </c>
       <c r="B337" t="s" s="2">
+        <v>707</v>
+      </c>
+      <c r="C337" t="s" s="2">
         <v>708</v>
-      </c>
-      <c r="C337" t="s" s="2">
-        <v>709</v>
       </c>
       <c r="D337" s="2"/>
     </row>
@@ -7506,10 +7365,10 @@
         <v>70</v>
       </c>
       <c r="B338" t="s" s="2">
+        <v>709</v>
+      </c>
+      <c r="C338" t="s" s="2">
         <v>710</v>
-      </c>
-      <c r="C338" t="s" s="2">
-        <v>711</v>
       </c>
       <c r="D338" s="2"/>
     </row>
@@ -7518,10 +7377,10 @@
         <v>70</v>
       </c>
       <c r="B339" t="s" s="2">
+        <v>711</v>
+      </c>
+      <c r="C339" t="s" s="2">
         <v>712</v>
-      </c>
-      <c r="C339" t="s" s="2">
-        <v>713</v>
       </c>
       <c r="D339" s="2"/>
     </row>
@@ -7530,10 +7389,10 @@
         <v>70</v>
       </c>
       <c r="B340" t="s" s="2">
+        <v>713</v>
+      </c>
+      <c r="C340" t="s" s="2">
         <v>714</v>
-      </c>
-      <c r="C340" t="s" s="2">
-        <v>715</v>
       </c>
       <c r="D340" s="2"/>
     </row>
@@ -7542,10 +7401,10 @@
         <v>70</v>
       </c>
       <c r="B341" t="s" s="2">
+        <v>715</v>
+      </c>
+      <c r="C341" t="s" s="2">
         <v>716</v>
-      </c>
-      <c r="C341" t="s" s="2">
-        <v>717</v>
       </c>
       <c r="D341" s="2"/>
     </row>
@@ -7554,10 +7413,10 @@
         <v>70</v>
       </c>
       <c r="B342" t="s" s="2">
+        <v>717</v>
+      </c>
+      <c r="C342" t="s" s="2">
         <v>718</v>
-      </c>
-      <c r="C342" t="s" s="2">
-        <v>719</v>
       </c>
       <c r="D342" s="2"/>
     </row>
@@ -7566,10 +7425,10 @@
         <v>70</v>
       </c>
       <c r="B343" t="s" s="2">
+        <v>719</v>
+      </c>
+      <c r="C343" t="s" s="2">
         <v>720</v>
-      </c>
-      <c r="C343" t="s" s="2">
-        <v>721</v>
       </c>
       <c r="D343" s="2"/>
     </row>
@@ -7578,10 +7437,10 @@
         <v>70</v>
       </c>
       <c r="B344" t="s" s="2">
+        <v>721</v>
+      </c>
+      <c r="C344" t="s" s="2">
         <v>722</v>
-      </c>
-      <c r="C344" t="s" s="2">
-        <v>723</v>
       </c>
       <c r="D344" s="2"/>
     </row>
@@ -7590,10 +7449,10 @@
         <v>70</v>
       </c>
       <c r="B345" t="s" s="2">
+        <v>723</v>
+      </c>
+      <c r="C345" t="s" s="2">
         <v>724</v>
-      </c>
-      <c r="C345" t="s" s="2">
-        <v>725</v>
       </c>
       <c r="D345" s="2"/>
     </row>
@@ -7602,10 +7461,10 @@
         <v>70</v>
       </c>
       <c r="B346" t="s" s="2">
+        <v>725</v>
+      </c>
+      <c r="C346" t="s" s="2">
         <v>726</v>
-      </c>
-      <c r="C346" t="s" s="2">
-        <v>727</v>
       </c>
       <c r="D346" s="2"/>
     </row>
@@ -7614,10 +7473,10 @@
         <v>70</v>
       </c>
       <c r="B347" t="s" s="2">
+        <v>727</v>
+      </c>
+      <c r="C347" t="s" s="2">
         <v>728</v>
-      </c>
-      <c r="C347" t="s" s="2">
-        <v>729</v>
       </c>
       <c r="D347" s="2"/>
     </row>
@@ -7626,10 +7485,10 @@
         <v>70</v>
       </c>
       <c r="B348" t="s" s="2">
+        <v>729</v>
+      </c>
+      <c r="C348" t="s" s="2">
         <v>730</v>
-      </c>
-      <c r="C348" t="s" s="2">
-        <v>731</v>
       </c>
       <c r="D348" s="2"/>
     </row>
@@ -7638,10 +7497,10 @@
         <v>70</v>
       </c>
       <c r="B349" t="s" s="2">
+        <v>731</v>
+      </c>
+      <c r="C349" t="s" s="2">
         <v>732</v>
-      </c>
-      <c r="C349" t="s" s="2">
-        <v>733</v>
       </c>
       <c r="D349" s="2"/>
     </row>
@@ -7650,10 +7509,10 @@
         <v>70</v>
       </c>
       <c r="B350" t="s" s="2">
+        <v>733</v>
+      </c>
+      <c r="C350" t="s" s="2">
         <v>734</v>
-      </c>
-      <c r="C350" t="s" s="2">
-        <v>735</v>
       </c>
       <c r="D350" s="2"/>
     </row>
@@ -7662,10 +7521,10 @@
         <v>70</v>
       </c>
       <c r="B351" t="s" s="2">
+        <v>735</v>
+      </c>
+      <c r="C351" t="s" s="2">
         <v>736</v>
-      </c>
-      <c r="C351" t="s" s="2">
-        <v>737</v>
       </c>
       <c r="D351" s="2"/>
     </row>
@@ -7674,10 +7533,10 @@
         <v>70</v>
       </c>
       <c r="B352" t="s" s="2">
+        <v>737</v>
+      </c>
+      <c r="C352" t="s" s="2">
         <v>738</v>
-      </c>
-      <c r="C352" t="s" s="2">
-        <v>739</v>
       </c>
       <c r="D352" s="2"/>
     </row>
@@ -7686,10 +7545,10 @@
         <v>70</v>
       </c>
       <c r="B353" t="s" s="2">
+        <v>739</v>
+      </c>
+      <c r="C353" t="s" s="2">
         <v>740</v>
-      </c>
-      <c r="C353" t="s" s="2">
-        <v>741</v>
       </c>
       <c r="D353" s="2"/>
     </row>
@@ -7698,10 +7557,10 @@
         <v>70</v>
       </c>
       <c r="B354" t="s" s="2">
+        <v>741</v>
+      </c>
+      <c r="C354" t="s" s="2">
         <v>742</v>
-      </c>
-      <c r="C354" t="s" s="2">
-        <v>743</v>
       </c>
       <c r="D354" s="2"/>
     </row>
@@ -7710,10 +7569,10 @@
         <v>70</v>
       </c>
       <c r="B355" t="s" s="2">
+        <v>743</v>
+      </c>
+      <c r="C355" t="s" s="2">
         <v>744</v>
-      </c>
-      <c r="C355" t="s" s="2">
-        <v>745</v>
       </c>
       <c r="D355" s="2"/>
     </row>
@@ -7722,10 +7581,10 @@
         <v>70</v>
       </c>
       <c r="B356" t="s" s="2">
+        <v>745</v>
+      </c>
+      <c r="C356" t="s" s="2">
         <v>746</v>
-      </c>
-      <c r="C356" t="s" s="2">
-        <v>747</v>
       </c>
       <c r="D356" s="2"/>
     </row>
@@ -7734,10 +7593,10 @@
         <v>70</v>
       </c>
       <c r="B357" t="s" s="2">
+        <v>747</v>
+      </c>
+      <c r="C357" t="s" s="2">
         <v>748</v>
-      </c>
-      <c r="C357" t="s" s="2">
-        <v>749</v>
       </c>
       <c r="D357" s="2"/>
     </row>
@@ -7746,10 +7605,10 @@
         <v>70</v>
       </c>
       <c r="B358" t="s" s="2">
+        <v>749</v>
+      </c>
+      <c r="C358" t="s" s="2">
         <v>750</v>
-      </c>
-      <c r="C358" t="s" s="2">
-        <v>751</v>
       </c>
       <c r="D358" s="2"/>
     </row>
@@ -7758,10 +7617,10 @@
         <v>70</v>
       </c>
       <c r="B359" t="s" s="2">
+        <v>751</v>
+      </c>
+      <c r="C359" t="s" s="2">
         <v>752</v>
-      </c>
-      <c r="C359" t="s" s="2">
-        <v>753</v>
       </c>
       <c r="D359" s="2"/>
     </row>
@@ -7770,10 +7629,10 @@
         <v>70</v>
       </c>
       <c r="B360" t="s" s="2">
+        <v>753</v>
+      </c>
+      <c r="C360" t="s" s="2">
         <v>754</v>
-      </c>
-      <c r="C360" t="s" s="2">
-        <v>755</v>
       </c>
       <c r="D360" s="2"/>
     </row>
@@ -7782,10 +7641,10 @@
         <v>70</v>
       </c>
       <c r="B361" t="s" s="2">
+        <v>755</v>
+      </c>
+      <c r="C361" t="s" s="2">
         <v>756</v>
-      </c>
-      <c r="C361" t="s" s="2">
-        <v>757</v>
       </c>
       <c r="D361" s="2"/>
     </row>
@@ -7794,10 +7653,10 @@
         <v>70</v>
       </c>
       <c r="B362" t="s" s="2">
+        <v>757</v>
+      </c>
+      <c r="C362" t="s" s="2">
         <v>758</v>
-      </c>
-      <c r="C362" t="s" s="2">
-        <v>759</v>
       </c>
       <c r="D362" s="2"/>
     </row>
@@ -7806,10 +7665,10 @@
         <v>70</v>
       </c>
       <c r="B363" t="s" s="2">
+        <v>759</v>
+      </c>
+      <c r="C363" t="s" s="2">
         <v>760</v>
-      </c>
-      <c r="C363" t="s" s="2">
-        <v>761</v>
       </c>
       <c r="D363" s="2"/>
     </row>
@@ -7818,10 +7677,10 @@
         <v>70</v>
       </c>
       <c r="B364" t="s" s="2">
+        <v>761</v>
+      </c>
+      <c r="C364" t="s" s="2">
         <v>762</v>
-      </c>
-      <c r="C364" t="s" s="2">
-        <v>763</v>
       </c>
       <c r="D364" s="2"/>
     </row>
@@ -7830,10 +7689,10 @@
         <v>70</v>
       </c>
       <c r="B365" t="s" s="2">
+        <v>763</v>
+      </c>
+      <c r="C365" t="s" s="2">
         <v>764</v>
-      </c>
-      <c r="C365" t="s" s="2">
-        <v>765</v>
       </c>
       <c r="D365" s="2"/>
     </row>
@@ -7842,10 +7701,10 @@
         <v>70</v>
       </c>
       <c r="B366" t="s" s="2">
+        <v>765</v>
+      </c>
+      <c r="C366" t="s" s="2">
         <v>766</v>
-      </c>
-      <c r="C366" t="s" s="2">
-        <v>767</v>
       </c>
       <c r="D366" s="2"/>
     </row>
@@ -7854,10 +7713,10 @@
         <v>70</v>
       </c>
       <c r="B367" t="s" s="2">
+        <v>767</v>
+      </c>
+      <c r="C367" t="s" s="2">
         <v>768</v>
-      </c>
-      <c r="C367" t="s" s="2">
-        <v>769</v>
       </c>
       <c r="D367" s="2"/>
     </row>
@@ -7866,10 +7725,10 @@
         <v>70</v>
       </c>
       <c r="B368" t="s" s="2">
+        <v>769</v>
+      </c>
+      <c r="C368" t="s" s="2">
         <v>770</v>
-      </c>
-      <c r="C368" t="s" s="2">
-        <v>771</v>
       </c>
       <c r="D368" s="2"/>
     </row>
@@ -7878,10 +7737,10 @@
         <v>70</v>
       </c>
       <c r="B369" t="s" s="2">
+        <v>771</v>
+      </c>
+      <c r="C369" t="s" s="2">
         <v>772</v>
-      </c>
-      <c r="C369" t="s" s="2">
-        <v>773</v>
       </c>
       <c r="D369" s="2"/>
     </row>
@@ -7890,10 +7749,10 @@
         <v>70</v>
       </c>
       <c r="B370" t="s" s="2">
+        <v>773</v>
+      </c>
+      <c r="C370" t="s" s="2">
         <v>774</v>
-      </c>
-      <c r="C370" t="s" s="2">
-        <v>775</v>
       </c>
       <c r="D370" s="2"/>
     </row>
@@ -7902,10 +7761,10 @@
         <v>70</v>
       </c>
       <c r="B371" t="s" s="2">
+        <v>775</v>
+      </c>
+      <c r="C371" t="s" s="2">
         <v>776</v>
-      </c>
-      <c r="C371" t="s" s="2">
-        <v>777</v>
       </c>
       <c r="D371" s="2"/>
     </row>
@@ -7914,10 +7773,10 @@
         <v>70</v>
       </c>
       <c r="B372" t="s" s="2">
+        <v>777</v>
+      </c>
+      <c r="C372" t="s" s="2">
         <v>778</v>
-      </c>
-      <c r="C372" t="s" s="2">
-        <v>779</v>
       </c>
       <c r="D372" s="2"/>
     </row>
@@ -7926,10 +7785,10 @@
         <v>70</v>
       </c>
       <c r="B373" t="s" s="2">
+        <v>779</v>
+      </c>
+      <c r="C373" t="s" s="2">
         <v>780</v>
-      </c>
-      <c r="C373" t="s" s="2">
-        <v>781</v>
       </c>
       <c r="D373" s="2"/>
     </row>
@@ -7938,10 +7797,10 @@
         <v>70</v>
       </c>
       <c r="B374" t="s" s="2">
+        <v>781</v>
+      </c>
+      <c r="C374" t="s" s="2">
         <v>782</v>
-      </c>
-      <c r="C374" t="s" s="2">
-        <v>783</v>
       </c>
       <c r="D374" s="2"/>
     </row>
@@ -7950,10 +7809,10 @@
         <v>70</v>
       </c>
       <c r="B375" t="s" s="2">
+        <v>783</v>
+      </c>
+      <c r="C375" t="s" s="2">
         <v>784</v>
-      </c>
-      <c r="C375" t="s" s="2">
-        <v>785</v>
       </c>
       <c r="D375" s="2"/>
     </row>
@@ -7962,10 +7821,10 @@
         <v>70</v>
       </c>
       <c r="B376" t="s" s="2">
+        <v>785</v>
+      </c>
+      <c r="C376" t="s" s="2">
         <v>786</v>
-      </c>
-      <c r="C376" t="s" s="2">
-        <v>787</v>
       </c>
       <c r="D376" s="2"/>
     </row>
@@ -7974,10 +7833,10 @@
         <v>70</v>
       </c>
       <c r="B377" t="s" s="2">
+        <v>787</v>
+      </c>
+      <c r="C377" t="s" s="2">
         <v>788</v>
-      </c>
-      <c r="C377" t="s" s="2">
-        <v>789</v>
       </c>
       <c r="D377" s="2"/>
     </row>
@@ -7986,10 +7845,10 @@
         <v>70</v>
       </c>
       <c r="B378" t="s" s="2">
+        <v>789</v>
+      </c>
+      <c r="C378" t="s" s="2">
         <v>790</v>
-      </c>
-      <c r="C378" t="s" s="2">
-        <v>791</v>
       </c>
       <c r="D378" s="2"/>
     </row>
@@ -7998,10 +7857,10 @@
         <v>70</v>
       </c>
       <c r="B379" t="s" s="2">
+        <v>791</v>
+      </c>
+      <c r="C379" t="s" s="2">
         <v>792</v>
-      </c>
-      <c r="C379" t="s" s="2">
-        <v>793</v>
       </c>
       <c r="D379" s="2"/>
     </row>
@@ -8010,10 +7869,10 @@
         <v>70</v>
       </c>
       <c r="B380" t="s" s="2">
+        <v>793</v>
+      </c>
+      <c r="C380" t="s" s="2">
         <v>794</v>
-      </c>
-      <c r="C380" t="s" s="2">
-        <v>795</v>
       </c>
       <c r="D380" s="2"/>
     </row>
@@ -8022,10 +7881,10 @@
         <v>70</v>
       </c>
       <c r="B381" t="s" s="2">
+        <v>795</v>
+      </c>
+      <c r="C381" t="s" s="2">
         <v>796</v>
-      </c>
-      <c r="C381" t="s" s="2">
-        <v>797</v>
       </c>
       <c r="D381" s="2"/>
     </row>
@@ -8034,10 +7893,10 @@
         <v>70</v>
       </c>
       <c r="B382" t="s" s="2">
+        <v>797</v>
+      </c>
+      <c r="C382" t="s" s="2">
         <v>798</v>
-      </c>
-      <c r="C382" t="s" s="2">
-        <v>799</v>
       </c>
       <c r="D382" s="2"/>
     </row>
@@ -8046,10 +7905,10 @@
         <v>70</v>
       </c>
       <c r="B383" t="s" s="2">
+        <v>799</v>
+      </c>
+      <c r="C383" t="s" s="2">
         <v>800</v>
-      </c>
-      <c r="C383" t="s" s="2">
-        <v>801</v>
       </c>
       <c r="D383" s="2"/>
     </row>
@@ -8058,10 +7917,10 @@
         <v>70</v>
       </c>
       <c r="B384" t="s" s="2">
+        <v>801</v>
+      </c>
+      <c r="C384" t="s" s="2">
         <v>802</v>
-      </c>
-      <c r="C384" t="s" s="2">
-        <v>803</v>
       </c>
       <c r="D384" s="2"/>
     </row>
@@ -8070,10 +7929,10 @@
         <v>70</v>
       </c>
       <c r="B385" t="s" s="2">
+        <v>803</v>
+      </c>
+      <c r="C385" t="s" s="2">
         <v>804</v>
-      </c>
-      <c r="C385" t="s" s="2">
-        <v>805</v>
       </c>
       <c r="D385" s="2"/>
     </row>
@@ -8082,10 +7941,10 @@
         <v>70</v>
       </c>
       <c r="B386" t="s" s="2">
+        <v>805</v>
+      </c>
+      <c r="C386" t="s" s="2">
         <v>806</v>
-      </c>
-      <c r="C386" t="s" s="2">
-        <v>807</v>
       </c>
       <c r="D386" s="2"/>
     </row>
@@ -8094,10 +7953,10 @@
         <v>70</v>
       </c>
       <c r="B387" t="s" s="2">
+        <v>807</v>
+      </c>
+      <c r="C387" t="s" s="2">
         <v>808</v>
-      </c>
-      <c r="C387" t="s" s="2">
-        <v>809</v>
       </c>
       <c r="D387" s="2"/>
     </row>
@@ -8106,10 +7965,10 @@
         <v>70</v>
       </c>
       <c r="B388" t="s" s="2">
+        <v>809</v>
+      </c>
+      <c r="C388" t="s" s="2">
         <v>810</v>
-      </c>
-      <c r="C388" t="s" s="2">
-        <v>811</v>
       </c>
       <c r="D388" s="2"/>
     </row>
@@ -8118,10 +7977,10 @@
         <v>70</v>
       </c>
       <c r="B389" t="s" s="2">
+        <v>811</v>
+      </c>
+      <c r="C389" t="s" s="2">
         <v>812</v>
-      </c>
-      <c r="C389" t="s" s="2">
-        <v>813</v>
       </c>
       <c r="D389" s="2"/>
     </row>
@@ -8130,10 +7989,10 @@
         <v>70</v>
       </c>
       <c r="B390" t="s" s="2">
+        <v>813</v>
+      </c>
+      <c r="C390" t="s" s="2">
         <v>814</v>
-      </c>
-      <c r="C390" t="s" s="2">
-        <v>815</v>
       </c>
       <c r="D390" s="2"/>
     </row>
@@ -8142,10 +8001,10 @@
         <v>70</v>
       </c>
       <c r="B391" t="s" s="2">
+        <v>815</v>
+      </c>
+      <c r="C391" t="s" s="2">
         <v>816</v>
-      </c>
-      <c r="C391" t="s" s="2">
-        <v>817</v>
       </c>
       <c r="D391" s="2"/>
     </row>
@@ -8154,10 +8013,10 @@
         <v>70</v>
       </c>
       <c r="B392" t="s" s="2">
+        <v>817</v>
+      </c>
+      <c r="C392" t="s" s="2">
         <v>818</v>
-      </c>
-      <c r="C392" t="s" s="2">
-        <v>819</v>
       </c>
       <c r="D392" s="2"/>
     </row>
@@ -8166,10 +8025,10 @@
         <v>70</v>
       </c>
       <c r="B393" t="s" s="2">
+        <v>819</v>
+      </c>
+      <c r="C393" t="s" s="2">
         <v>820</v>
-      </c>
-      <c r="C393" t="s" s="2">
-        <v>821</v>
       </c>
       <c r="D393" s="2"/>
     </row>
@@ -8178,10 +8037,10 @@
         <v>70</v>
       </c>
       <c r="B394" t="s" s="2">
+        <v>821</v>
+      </c>
+      <c r="C394" t="s" s="2">
         <v>822</v>
-      </c>
-      <c r="C394" t="s" s="2">
-        <v>823</v>
       </c>
       <c r="D394" s="2"/>
     </row>
@@ -8190,10 +8049,10 @@
         <v>70</v>
       </c>
       <c r="B395" t="s" s="2">
+        <v>823</v>
+      </c>
+      <c r="C395" t="s" s="2">
         <v>824</v>
-      </c>
-      <c r="C395" t="s" s="2">
-        <v>825</v>
       </c>
       <c r="D395" s="2"/>
     </row>
@@ -8202,10 +8061,10 @@
         <v>70</v>
       </c>
       <c r="B396" t="s" s="2">
+        <v>825</v>
+      </c>
+      <c r="C396" t="s" s="2">
         <v>826</v>
-      </c>
-      <c r="C396" t="s" s="2">
-        <v>827</v>
       </c>
       <c r="D396" s="2"/>
     </row>
@@ -8214,10 +8073,10 @@
         <v>70</v>
       </c>
       <c r="B397" t="s" s="2">
+        <v>827</v>
+      </c>
+      <c r="C397" t="s" s="2">
         <v>828</v>
-      </c>
-      <c r="C397" t="s" s="2">
-        <v>829</v>
       </c>
       <c r="D397" s="2"/>
     </row>
@@ -8226,10 +8085,10 @@
         <v>70</v>
       </c>
       <c r="B398" t="s" s="2">
+        <v>829</v>
+      </c>
+      <c r="C398" t="s" s="2">
         <v>830</v>
-      </c>
-      <c r="C398" t="s" s="2">
-        <v>831</v>
       </c>
       <c r="D398" s="2"/>
     </row>
@@ -8238,10 +8097,10 @@
         <v>70</v>
       </c>
       <c r="B399" t="s" s="2">
+        <v>831</v>
+      </c>
+      <c r="C399" t="s" s="2">
         <v>832</v>
-      </c>
-      <c r="C399" t="s" s="2">
-        <v>833</v>
       </c>
       <c r="D399" s="2"/>
     </row>
@@ -8250,10 +8109,10 @@
         <v>70</v>
       </c>
       <c r="B400" t="s" s="2">
+        <v>833</v>
+      </c>
+      <c r="C400" t="s" s="2">
         <v>834</v>
-      </c>
-      <c r="C400" t="s" s="2">
-        <v>835</v>
       </c>
       <c r="D400" s="2"/>
     </row>
@@ -8262,10 +8121,10 @@
         <v>70</v>
       </c>
       <c r="B401" t="s" s="2">
+        <v>835</v>
+      </c>
+      <c r="C401" t="s" s="2">
         <v>836</v>
-      </c>
-      <c r="C401" t="s" s="2">
-        <v>837</v>
       </c>
       <c r="D401" s="2"/>
     </row>
@@ -8274,10 +8133,10 @@
         <v>70</v>
       </c>
       <c r="B402" t="s" s="2">
+        <v>837</v>
+      </c>
+      <c r="C402" t="s" s="2">
         <v>838</v>
-      </c>
-      <c r="C402" t="s" s="2">
-        <v>839</v>
       </c>
       <c r="D402" s="2"/>
     </row>
@@ -8286,10 +8145,10 @@
         <v>70</v>
       </c>
       <c r="B403" t="s" s="2">
+        <v>839</v>
+      </c>
+      <c r="C403" t="s" s="2">
         <v>840</v>
-      </c>
-      <c r="C403" t="s" s="2">
-        <v>841</v>
       </c>
       <c r="D403" s="2"/>
     </row>
@@ -8298,10 +8157,10 @@
         <v>70</v>
       </c>
       <c r="B404" t="s" s="2">
+        <v>841</v>
+      </c>
+      <c r="C404" t="s" s="2">
         <v>842</v>
-      </c>
-      <c r="C404" t="s" s="2">
-        <v>843</v>
       </c>
       <c r="D404" s="2"/>
     </row>
@@ -8310,10 +8169,10 @@
         <v>70</v>
       </c>
       <c r="B405" t="s" s="2">
+        <v>843</v>
+      </c>
+      <c r="C405" t="s" s="2">
         <v>844</v>
-      </c>
-      <c r="C405" t="s" s="2">
-        <v>845</v>
       </c>
       <c r="D405" s="2"/>
     </row>
@@ -8322,10 +8181,10 @@
         <v>70</v>
       </c>
       <c r="B406" t="s" s="2">
+        <v>845</v>
+      </c>
+      <c r="C406" t="s" s="2">
         <v>846</v>
-      </c>
-      <c r="C406" t="s" s="2">
-        <v>847</v>
       </c>
       <c r="D406" s="2"/>
     </row>
@@ -8334,10 +8193,10 @@
         <v>70</v>
       </c>
       <c r="B407" t="s" s="2">
+        <v>847</v>
+      </c>
+      <c r="C407" t="s" s="2">
         <v>848</v>
-      </c>
-      <c r="C407" t="s" s="2">
-        <v>849</v>
       </c>
       <c r="D407" s="2"/>
     </row>
@@ -8346,10 +8205,10 @@
         <v>70</v>
       </c>
       <c r="B408" t="s" s="2">
+        <v>849</v>
+      </c>
+      <c r="C408" t="s" s="2">
         <v>850</v>
-      </c>
-      <c r="C408" t="s" s="2">
-        <v>851</v>
       </c>
       <c r="D408" s="2"/>
     </row>
@@ -8358,10 +8217,10 @@
         <v>70</v>
       </c>
       <c r="B409" t="s" s="2">
+        <v>851</v>
+      </c>
+      <c r="C409" t="s" s="2">
         <v>852</v>
-      </c>
-      <c r="C409" t="s" s="2">
-        <v>853</v>
       </c>
       <c r="D409" s="2"/>
     </row>
@@ -8370,10 +8229,10 @@
         <v>70</v>
       </c>
       <c r="B410" t="s" s="2">
+        <v>853</v>
+      </c>
+      <c r="C410" t="s" s="2">
         <v>854</v>
-      </c>
-      <c r="C410" t="s" s="2">
-        <v>855</v>
       </c>
       <c r="D410" s="2"/>
     </row>
@@ -8382,10 +8241,10 @@
         <v>70</v>
       </c>
       <c r="B411" t="s" s="2">
+        <v>855</v>
+      </c>
+      <c r="C411" t="s" s="2">
         <v>856</v>
-      </c>
-      <c r="C411" t="s" s="2">
-        <v>857</v>
       </c>
       <c r="D411" s="2"/>
     </row>
@@ -8394,10 +8253,10 @@
         <v>70</v>
       </c>
       <c r="B412" t="s" s="2">
+        <v>857</v>
+      </c>
+      <c r="C412" t="s" s="2">
         <v>858</v>
-      </c>
-      <c r="C412" t="s" s="2">
-        <v>859</v>
       </c>
       <c r="D412" s="2"/>
     </row>
@@ -8406,10 +8265,10 @@
         <v>70</v>
       </c>
       <c r="B413" t="s" s="2">
+        <v>859</v>
+      </c>
+      <c r="C413" t="s" s="2">
         <v>860</v>
-      </c>
-      <c r="C413" t="s" s="2">
-        <v>861</v>
       </c>
       <c r="D413" s="2"/>
     </row>
@@ -8418,10 +8277,10 @@
         <v>70</v>
       </c>
       <c r="B414" t="s" s="2">
+        <v>861</v>
+      </c>
+      <c r="C414" t="s" s="2">
         <v>862</v>
-      </c>
-      <c r="C414" t="s" s="2">
-        <v>863</v>
       </c>
       <c r="D414" s="2"/>
     </row>
@@ -8430,10 +8289,10 @@
         <v>70</v>
       </c>
       <c r="B415" t="s" s="2">
+        <v>863</v>
+      </c>
+      <c r="C415" t="s" s="2">
         <v>864</v>
-      </c>
-      <c r="C415" t="s" s="2">
-        <v>865</v>
       </c>
       <c r="D415" s="2"/>
     </row>
@@ -8442,10 +8301,10 @@
         <v>70</v>
       </c>
       <c r="B416" t="s" s="2">
+        <v>865</v>
+      </c>
+      <c r="C416" t="s" s="2">
         <v>866</v>
-      </c>
-      <c r="C416" t="s" s="2">
-        <v>867</v>
       </c>
       <c r="D416" s="2"/>
     </row>
@@ -8454,10 +8313,10 @@
         <v>70</v>
       </c>
       <c r="B417" t="s" s="2">
+        <v>867</v>
+      </c>
+      <c r="C417" t="s" s="2">
         <v>868</v>
-      </c>
-      <c r="C417" t="s" s="2">
-        <v>869</v>
       </c>
       <c r="D417" s="2"/>
     </row>
@@ -8466,10 +8325,10 @@
         <v>70</v>
       </c>
       <c r="B418" t="s" s="2">
+        <v>869</v>
+      </c>
+      <c r="C418" t="s" s="2">
         <v>870</v>
-      </c>
-      <c r="C418" t="s" s="2">
-        <v>871</v>
       </c>
       <c r="D418" s="2"/>
     </row>
@@ -8478,10 +8337,10 @@
         <v>70</v>
       </c>
       <c r="B419" t="s" s="2">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="C419" t="s" s="2">
-        <v>873</v>
+        <v>110</v>
       </c>
       <c r="D419" s="2"/>
     </row>
@@ -8490,10 +8349,10 @@
         <v>70</v>
       </c>
       <c r="B420" t="s" s="2">
-        <v>874</v>
+        <v>872</v>
       </c>
       <c r="C420" t="s" s="2">
-        <v>875</v>
+        <v>873</v>
       </c>
       <c r="D420" s="2"/>
     </row>
@@ -8502,10 +8361,10 @@
         <v>70</v>
       </c>
       <c r="B421" t="s" s="2">
-        <v>876</v>
+        <v>874</v>
       </c>
       <c r="C421" t="s" s="2">
-        <v>877</v>
+        <v>875</v>
       </c>
       <c r="D421" s="2"/>
     </row>
@@ -8514,10 +8373,10 @@
         <v>70</v>
       </c>
       <c r="B422" t="s" s="2">
-        <v>878</v>
+        <v>876</v>
       </c>
       <c r="C422" t="s" s="2">
-        <v>879</v>
+        <v>877</v>
       </c>
       <c r="D422" s="2"/>
     </row>
@@ -8526,10 +8385,10 @@
         <v>70</v>
       </c>
       <c r="B423" t="s" s="2">
-        <v>880</v>
+        <v>878</v>
       </c>
       <c r="C423" t="s" s="2">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="D423" s="2"/>
     </row>
@@ -8538,10 +8397,10 @@
         <v>70</v>
       </c>
       <c r="B424" t="s" s="2">
-        <v>882</v>
+        <v>880</v>
       </c>
       <c r="C424" t="s" s="2">
-        <v>883</v>
+        <v>881</v>
       </c>
       <c r="D424" s="2"/>
     </row>
@@ -8550,10 +8409,10 @@
         <v>70</v>
       </c>
       <c r="B425" t="s" s="2">
-        <v>884</v>
+        <v>882</v>
       </c>
       <c r="C425" t="s" s="2">
-        <v>885</v>
+        <v>883</v>
       </c>
       <c r="D425" s="2"/>
     </row>
@@ -8562,10 +8421,10 @@
         <v>70</v>
       </c>
       <c r="B426" t="s" s="2">
-        <v>886</v>
+        <v>884</v>
       </c>
       <c r="C426" t="s" s="2">
-        <v>887</v>
+        <v>885</v>
       </c>
       <c r="D426" s="2"/>
     </row>
@@ -8574,10 +8433,10 @@
         <v>70</v>
       </c>
       <c r="B427" t="s" s="2">
-        <v>888</v>
+        <v>886</v>
       </c>
       <c r="C427" t="s" s="2">
-        <v>889</v>
+        <v>887</v>
       </c>
       <c r="D427" s="2"/>
     </row>
@@ -8586,10 +8445,10 @@
         <v>70</v>
       </c>
       <c r="B428" t="s" s="2">
-        <v>890</v>
+        <v>888</v>
       </c>
       <c r="C428" t="s" s="2">
-        <v>891</v>
+        <v>889</v>
       </c>
       <c r="D428" s="2"/>
     </row>
@@ -8598,10 +8457,10 @@
         <v>70</v>
       </c>
       <c r="B429" t="s" s="2">
-        <v>892</v>
+        <v>890</v>
       </c>
       <c r="C429" t="s" s="2">
-        <v>893</v>
+        <v>891</v>
       </c>
       <c r="D429" s="2"/>
     </row>
@@ -8610,10 +8469,10 @@
         <v>70</v>
       </c>
       <c r="B430" t="s" s="2">
-        <v>894</v>
+        <v>892</v>
       </c>
       <c r="C430" t="s" s="2">
-        <v>895</v>
+        <v>893</v>
       </c>
       <c r="D430" s="2"/>
     </row>
@@ -8622,10 +8481,10 @@
         <v>70</v>
       </c>
       <c r="B431" t="s" s="2">
-        <v>896</v>
+        <v>894</v>
       </c>
       <c r="C431" t="s" s="2">
-        <v>897</v>
+        <v>895</v>
       </c>
       <c r="D431" s="2"/>
     </row>
@@ -8634,10 +8493,10 @@
         <v>70</v>
       </c>
       <c r="B432" t="s" s="2">
-        <v>898</v>
+        <v>896</v>
       </c>
       <c r="C432" t="s" s="2">
-        <v>899</v>
+        <v>897</v>
       </c>
       <c r="D432" s="2"/>
     </row>
@@ -8646,10 +8505,10 @@
         <v>70</v>
       </c>
       <c r="B433" t="s" s="2">
-        <v>900</v>
+        <v>898</v>
       </c>
       <c r="C433" t="s" s="2">
-        <v>901</v>
+        <v>899</v>
       </c>
       <c r="D433" s="2"/>
     </row>
@@ -8658,10 +8517,10 @@
         <v>70</v>
       </c>
       <c r="B434" t="s" s="2">
-        <v>902</v>
+        <v>900</v>
       </c>
       <c r="C434" t="s" s="2">
-        <v>903</v>
+        <v>901</v>
       </c>
       <c r="D434" s="2"/>
     </row>
@@ -8670,10 +8529,10 @@
         <v>70</v>
       </c>
       <c r="B435" t="s" s="2">
-        <v>904</v>
+        <v>902</v>
       </c>
       <c r="C435" t="s" s="2">
-        <v>905</v>
+        <v>903</v>
       </c>
       <c r="D435" s="2"/>
     </row>
@@ -8682,10 +8541,10 @@
         <v>70</v>
       </c>
       <c r="B436" t="s" s="2">
-        <v>906</v>
+        <v>904</v>
       </c>
       <c r="C436" t="s" s="2">
-        <v>110</v>
+        <v>905</v>
       </c>
       <c r="D436" s="2"/>
     </row>
@@ -8694,10 +8553,10 @@
         <v>70</v>
       </c>
       <c r="B437" t="s" s="2">
+        <v>906</v>
+      </c>
+      <c r="C437" t="s" s="2">
         <v>907</v>
-      </c>
-      <c r="C437" t="s" s="2">
-        <v>908</v>
       </c>
       <c r="D437" s="2"/>
     </row>
@@ -8706,10 +8565,10 @@
         <v>70</v>
       </c>
       <c r="B438" t="s" s="2">
+        <v>908</v>
+      </c>
+      <c r="C438" t="s" s="2">
         <v>909</v>
-      </c>
-      <c r="C438" t="s" s="2">
-        <v>910</v>
       </c>
       <c r="D438" s="2"/>
     </row>
@@ -8718,10 +8577,10 @@
         <v>70</v>
       </c>
       <c r="B439" t="s" s="2">
+        <v>910</v>
+      </c>
+      <c r="C439" t="s" s="2">
         <v>911</v>
-      </c>
-      <c r="C439" t="s" s="2">
-        <v>912</v>
       </c>
       <c r="D439" s="2"/>
     </row>
@@ -8730,10 +8589,10 @@
         <v>70</v>
       </c>
       <c r="B440" t="s" s="2">
+        <v>912</v>
+      </c>
+      <c r="C440" t="s" s="2">
         <v>913</v>
-      </c>
-      <c r="C440" t="s" s="2">
-        <v>914</v>
       </c>
       <c r="D440" s="2"/>
     </row>
@@ -8742,10 +8601,10 @@
         <v>70</v>
       </c>
       <c r="B441" t="s" s="2">
+        <v>914</v>
+      </c>
+      <c r="C441" t="s" s="2">
         <v>915</v>
-      </c>
-      <c r="C441" t="s" s="2">
-        <v>916</v>
       </c>
       <c r="D441" s="2"/>
     </row>
@@ -8754,10 +8613,10 @@
         <v>70</v>
       </c>
       <c r="B442" t="s" s="2">
+        <v>916</v>
+      </c>
+      <c r="C442" t="s" s="2">
         <v>917</v>
-      </c>
-      <c r="C442" t="s" s="2">
-        <v>918</v>
       </c>
       <c r="D442" s="2"/>
     </row>
@@ -8766,10 +8625,10 @@
         <v>70</v>
       </c>
       <c r="B443" t="s" s="2">
+        <v>918</v>
+      </c>
+      <c r="C443" t="s" s="2">
         <v>919</v>
-      </c>
-      <c r="C443" t="s" s="2">
-        <v>920</v>
       </c>
       <c r="D443" s="2"/>
     </row>
@@ -8778,10 +8637,10 @@
         <v>70</v>
       </c>
       <c r="B444" t="s" s="2">
+        <v>920</v>
+      </c>
+      <c r="C444" t="s" s="2">
         <v>921</v>
-      </c>
-      <c r="C444" t="s" s="2">
-        <v>922</v>
       </c>
       <c r="D444" s="2"/>
     </row>
@@ -8790,10 +8649,10 @@
         <v>70</v>
       </c>
       <c r="B445" t="s" s="2">
+        <v>922</v>
+      </c>
+      <c r="C445" t="s" s="2">
         <v>923</v>
-      </c>
-      <c r="C445" t="s" s="2">
-        <v>924</v>
       </c>
       <c r="D445" s="2"/>
     </row>
@@ -8802,10 +8661,10 @@
         <v>70</v>
       </c>
       <c r="B446" t="s" s="2">
+        <v>924</v>
+      </c>
+      <c r="C446" t="s" s="2">
         <v>925</v>
-      </c>
-      <c r="C446" t="s" s="2">
-        <v>926</v>
       </c>
       <c r="D446" s="2"/>
     </row>
@@ -8814,10 +8673,10 @@
         <v>70</v>
       </c>
       <c r="B447" t="s" s="2">
+        <v>926</v>
+      </c>
+      <c r="C447" t="s" s="2">
         <v>927</v>
-      </c>
-      <c r="C447" t="s" s="2">
-        <v>928</v>
       </c>
       <c r="D447" s="2"/>
     </row>
@@ -8826,10 +8685,10 @@
         <v>70</v>
       </c>
       <c r="B448" t="s" s="2">
+        <v>928</v>
+      </c>
+      <c r="C448" t="s" s="2">
         <v>929</v>
-      </c>
-      <c r="C448" t="s" s="2">
-        <v>930</v>
       </c>
       <c r="D448" s="2"/>
     </row>
@@ -8838,10 +8697,10 @@
         <v>70</v>
       </c>
       <c r="B449" t="s" s="2">
+        <v>930</v>
+      </c>
+      <c r="C449" t="s" s="2">
         <v>931</v>
-      </c>
-      <c r="C449" t="s" s="2">
-        <v>932</v>
       </c>
       <c r="D449" s="2"/>
     </row>
@@ -8850,10 +8709,10 @@
         <v>70</v>
       </c>
       <c r="B450" t="s" s="2">
+        <v>932</v>
+      </c>
+      <c r="C450" t="s" s="2">
         <v>933</v>
-      </c>
-      <c r="C450" t="s" s="2">
-        <v>934</v>
       </c>
       <c r="D450" s="2"/>
     </row>
@@ -8862,10 +8721,10 @@
         <v>70</v>
       </c>
       <c r="B451" t="s" s="2">
+        <v>934</v>
+      </c>
+      <c r="C451" t="s" s="2">
         <v>935</v>
-      </c>
-      <c r="C451" t="s" s="2">
-        <v>936</v>
       </c>
       <c r="D451" s="2"/>
     </row>
@@ -8874,10 +8733,10 @@
         <v>70</v>
       </c>
       <c r="B452" t="s" s="2">
+        <v>936</v>
+      </c>
+      <c r="C452" t="s" s="2">
         <v>937</v>
-      </c>
-      <c r="C452" t="s" s="2">
-        <v>938</v>
       </c>
       <c r="D452" s="2"/>
     </row>
@@ -8886,10 +8745,10 @@
         <v>70</v>
       </c>
       <c r="B453" t="s" s="2">
+        <v>938</v>
+      </c>
+      <c r="C453" t="s" s="2">
         <v>939</v>
-      </c>
-      <c r="C453" t="s" s="2">
-        <v>940</v>
       </c>
       <c r="D453" s="2"/>
     </row>
@@ -8898,10 +8757,10 @@
         <v>70</v>
       </c>
       <c r="B454" t="s" s="2">
+        <v>940</v>
+      </c>
+      <c r="C454" t="s" s="2">
         <v>941</v>
-      </c>
-      <c r="C454" t="s" s="2">
-        <v>942</v>
       </c>
       <c r="D454" s="2"/>
     </row>
@@ -8910,10 +8769,10 @@
         <v>70</v>
       </c>
       <c r="B455" t="s" s="2">
+        <v>942</v>
+      </c>
+      <c r="C455" t="s" s="2">
         <v>943</v>
-      </c>
-      <c r="C455" t="s" s="2">
-        <v>944</v>
       </c>
       <c r="D455" s="2"/>
     </row>
@@ -8922,10 +8781,10 @@
         <v>70</v>
       </c>
       <c r="B456" t="s" s="2">
+        <v>944</v>
+      </c>
+      <c r="C456" t="s" s="2">
         <v>945</v>
-      </c>
-      <c r="C456" t="s" s="2">
-        <v>946</v>
       </c>
       <c r="D456" s="2"/>
     </row>
@@ -8934,10 +8793,10 @@
         <v>70</v>
       </c>
       <c r="B457" t="s" s="2">
+        <v>946</v>
+      </c>
+      <c r="C457" t="s" s="2">
         <v>947</v>
-      </c>
-      <c r="C457" t="s" s="2">
-        <v>948</v>
       </c>
       <c r="D457" s="2"/>
     </row>
@@ -8946,272 +8805,12 @@
         <v>70</v>
       </c>
       <c r="B458" t="s" s="2">
+        <v>948</v>
+      </c>
+      <c r="C458" t="s" s="2">
         <v>949</v>
       </c>
-      <c r="C458" t="s" s="2">
-        <v>950</v>
-      </c>
       <c r="D458" s="2"/>
-    </row>
-    <row r="459">
-      <c r="A459" t="s" s="2">
-        <v>70</v>
-      </c>
-      <c r="B459" t="s" s="2">
-        <v>951</v>
-      </c>
-      <c r="C459" t="s" s="2">
-        <v>952</v>
-      </c>
-      <c r="D459" s="2"/>
-    </row>
-    <row r="460">
-      <c r="A460" t="s" s="2">
-        <v>70</v>
-      </c>
-      <c r="B460" t="s" s="2">
-        <v>953</v>
-      </c>
-      <c r="C460" t="s" s="2">
-        <v>954</v>
-      </c>
-      <c r="D460" s="2"/>
-    </row>
-    <row r="461">
-      <c r="A461" t="s" s="2">
-        <v>70</v>
-      </c>
-      <c r="B461" t="s" s="2">
-        <v>955</v>
-      </c>
-      <c r="C461" t="s" s="2">
-        <v>956</v>
-      </c>
-      <c r="D461" s="2"/>
-    </row>
-    <row r="462">
-      <c r="A462" t="s" s="2">
-        <v>70</v>
-      </c>
-      <c r="B462" t="s" s="2">
-        <v>957</v>
-      </c>
-      <c r="C462" t="s" s="2">
-        <v>958</v>
-      </c>
-      <c r="D462" s="2"/>
-    </row>
-    <row r="463">
-      <c r="A463" t="s" s="2">
-        <v>70</v>
-      </c>
-      <c r="B463" t="s" s="2">
-        <v>959</v>
-      </c>
-      <c r="C463" t="s" s="2">
-        <v>960</v>
-      </c>
-      <c r="D463" s="2"/>
-    </row>
-    <row r="464">
-      <c r="A464" t="s" s="2">
-        <v>70</v>
-      </c>
-      <c r="B464" t="s" s="2">
-        <v>961</v>
-      </c>
-      <c r="C464" t="s" s="2">
-        <v>962</v>
-      </c>
-      <c r="D464" s="2"/>
-    </row>
-    <row r="465">
-      <c r="A465" t="s" s="2">
-        <v>70</v>
-      </c>
-      <c r="B465" t="s" s="2">
-        <v>963</v>
-      </c>
-      <c r="C465" t="s" s="2">
-        <v>964</v>
-      </c>
-      <c r="D465" s="2"/>
-    </row>
-    <row r="466">
-      <c r="A466" t="s" s="2">
-        <v>70</v>
-      </c>
-      <c r="B466" t="s" s="2">
-        <v>965</v>
-      </c>
-      <c r="C466" t="s" s="2">
-        <v>966</v>
-      </c>
-      <c r="D466" s="2"/>
-    </row>
-    <row r="467">
-      <c r="A467" t="s" s="2">
-        <v>70</v>
-      </c>
-      <c r="B467" t="s" s="2">
-        <v>967</v>
-      </c>
-      <c r="C467" t="s" s="2">
-        <v>968</v>
-      </c>
-      <c r="D467" s="2"/>
-    </row>
-    <row r="468">
-      <c r="A468" t="s" s="2">
-        <v>70</v>
-      </c>
-      <c r="B468" t="s" s="2">
-        <v>969</v>
-      </c>
-      <c r="C468" t="s" s="2">
-        <v>970</v>
-      </c>
-      <c r="D468" t="s" s="2">
-        <v>971</v>
-      </c>
-    </row>
-    <row r="469">
-      <c r="A469" t="s" s="2">
-        <v>70</v>
-      </c>
-      <c r="B469" t="s" s="2">
-        <v>972</v>
-      </c>
-      <c r="C469" t="s" s="2">
-        <v>973</v>
-      </c>
-      <c r="D469" t="s" s="2">
-        <v>974</v>
-      </c>
-    </row>
-    <row r="470">
-      <c r="A470" t="s" s="2">
-        <v>70</v>
-      </c>
-      <c r="B470" t="s" s="2">
-        <v>975</v>
-      </c>
-      <c r="C470" t="s" s="2">
-        <v>976</v>
-      </c>
-      <c r="D470" t="s" s="2">
-        <v>977</v>
-      </c>
-    </row>
-    <row r="471">
-      <c r="A471" t="s" s="2">
-        <v>70</v>
-      </c>
-      <c r="B471" t="s" s="2">
-        <v>978</v>
-      </c>
-      <c r="C471" t="s" s="2">
-        <v>979</v>
-      </c>
-      <c r="D471" t="s" s="2">
-        <v>980</v>
-      </c>
-    </row>
-    <row r="472">
-      <c r="A472" t="s" s="2">
-        <v>70</v>
-      </c>
-      <c r="B472" t="s" s="2">
-        <v>981</v>
-      </c>
-      <c r="C472" t="s" s="2">
-        <v>982</v>
-      </c>
-      <c r="D472" s="2"/>
-    </row>
-    <row r="473">
-      <c r="A473" t="s" s="2">
-        <v>70</v>
-      </c>
-      <c r="B473" t="s" s="2">
-        <v>983</v>
-      </c>
-      <c r="C473" t="s" s="2">
-        <v>984</v>
-      </c>
-      <c r="D473" s="2"/>
-    </row>
-    <row r="474">
-      <c r="A474" t="s" s="2">
-        <v>70</v>
-      </c>
-      <c r="B474" t="s" s="2">
-        <v>985</v>
-      </c>
-      <c r="C474" t="s" s="2">
-        <v>986</v>
-      </c>
-      <c r="D474" s="2"/>
-    </row>
-    <row r="475">
-      <c r="A475" t="s" s="2">
-        <v>70</v>
-      </c>
-      <c r="B475" t="s" s="2">
-        <v>987</v>
-      </c>
-      <c r="C475" t="s" s="2">
-        <v>988</v>
-      </c>
-      <c r="D475" s="2"/>
-    </row>
-    <row r="476">
-      <c r="A476" t="s" s="2">
-        <v>70</v>
-      </c>
-      <c r="B476" t="s" s="2">
-        <v>989</v>
-      </c>
-      <c r="C476" t="s" s="2">
-        <v>990</v>
-      </c>
-      <c r="D476" s="2"/>
-    </row>
-    <row r="477">
-      <c r="A477" t="s" s="2">
-        <v>70</v>
-      </c>
-      <c r="B477" t="s" s="2">
-        <v>991</v>
-      </c>
-      <c r="C477" t="s" s="2">
-        <v>992</v>
-      </c>
-      <c r="D477" s="2"/>
-    </row>
-    <row r="478">
-      <c r="A478" t="s" s="2">
-        <v>70</v>
-      </c>
-      <c r="B478" t="s" s="2">
-        <v>993</v>
-      </c>
-      <c r="C478" t="s" s="2">
-        <v>994</v>
-      </c>
-      <c r="D478" s="2"/>
-    </row>
-    <row r="479">
-      <c r="A479" t="s" s="2">
-        <v>70</v>
-      </c>
-      <c r="B479" t="s" s="2">
-        <v>995</v>
-      </c>
-      <c r="C479" t="s" s="2">
-        <v>996</v>
-      </c>
-      <c r="D479" s="2"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
